--- a/vignettes/vignette-2/distribution_plot_data.xlsx
+++ b/vignettes/vignette-2/distribution_plot_data.xlsx
@@ -6644,7 +6644,7 @@
         <v>477</v>
       </c>
       <c r="C479" t="n">
-        <v>0.056487</v>
+        <v>0.056702</v>
       </c>
     </row>
     <row r="480">
@@ -6657,7 +6657,7 @@
         <v>478</v>
       </c>
       <c r="C480" t="n">
-        <v>0.056702</v>
+        <v>0.056785</v>
       </c>
     </row>
     <row r="481">
@@ -6670,7 +6670,7 @@
         <v>479</v>
       </c>
       <c r="C481" t="n">
-        <v>0.056785</v>
+        <v>0.057942</v>
       </c>
     </row>
     <row r="482">
@@ -6683,7 +6683,7 @@
         <v>480</v>
       </c>
       <c r="C482" t="n">
-        <v>0.057942</v>
+        <v>0.05854</v>
       </c>
     </row>
     <row r="483">
@@ -6696,7 +6696,7 @@
         <v>481</v>
       </c>
       <c r="C483" t="n">
-        <v>0.05854</v>
+        <v>0.058745</v>
       </c>
     </row>
     <row r="484">
@@ -6709,7 +6709,7 @@
         <v>482</v>
       </c>
       <c r="C484" t="n">
-        <v>0.058745</v>
+        <v>0.058836</v>
       </c>
     </row>
     <row r="485">
@@ -6722,7 +6722,7 @@
         <v>483</v>
       </c>
       <c r="C485" t="n">
-        <v>0.058836</v>
+        <v>0.059279</v>
       </c>
     </row>
     <row r="486">
@@ -6735,7 +6735,7 @@
         <v>484</v>
       </c>
       <c r="C486" t="n">
-        <v>0.059279</v>
+        <v>0.059367</v>
       </c>
     </row>
     <row r="487">
@@ -6748,7 +6748,7 @@
         <v>485</v>
       </c>
       <c r="C487" t="n">
-        <v>0.059367</v>
+        <v>0.059553</v>
       </c>
     </row>
     <row r="488">
@@ -6761,7 +6761,7 @@
         <v>486</v>
       </c>
       <c r="C488" t="n">
-        <v>0.059553</v>
+        <v>0.059579</v>
       </c>
     </row>
     <row r="489">
@@ -6774,7 +6774,7 @@
         <v>487</v>
       </c>
       <c r="C489" t="n">
-        <v>0.059579</v>
+        <v>0.060111</v>
       </c>
     </row>
     <row r="490">
@@ -6787,7 +6787,7 @@
         <v>488</v>
       </c>
       <c r="C490" t="n">
-        <v>0.060111</v>
+        <v>0.060827</v>
       </c>
     </row>
     <row r="491">
@@ -6800,7 +6800,7 @@
         <v>489</v>
       </c>
       <c r="C491" t="n">
-        <v>0.060827</v>
+        <v>0.060882</v>
       </c>
     </row>
     <row r="492">
@@ -6813,7 +6813,7 @@
         <v>490</v>
       </c>
       <c r="C492" t="n">
-        <v>0.060882</v>
+        <v>0.061437</v>
       </c>
     </row>
     <row r="493">
@@ -6826,7 +6826,7 @@
         <v>491</v>
       </c>
       <c r="C493" t="n">
-        <v>0.061437</v>
+        <v>0.061712</v>
       </c>
     </row>
     <row r="494">
@@ -6839,7 +6839,7 @@
         <v>492</v>
       </c>
       <c r="C494" t="n">
-        <v>0.061712</v>
+        <v>0.061784</v>
       </c>
     </row>
     <row r="495">
@@ -6852,7 +6852,7 @@
         <v>493</v>
       </c>
       <c r="C495" t="n">
-        <v>0.061784</v>
+        <v>0.06179</v>
       </c>
     </row>
     <row r="496">
@@ -6865,7 +6865,7 @@
         <v>494</v>
       </c>
       <c r="C496" t="n">
-        <v>0.06179</v>
+        <v>0.061969</v>
       </c>
     </row>
     <row r="497">
@@ -6878,7 +6878,7 @@
         <v>495</v>
       </c>
       <c r="C497" t="n">
-        <v>0.061969</v>
+        <v>0.062129</v>
       </c>
     </row>
     <row r="498">
@@ -6891,7 +6891,7 @@
         <v>496</v>
       </c>
       <c r="C498" t="n">
-        <v>0.062129</v>
+        <v>0.062168</v>
       </c>
     </row>
     <row r="499">
@@ -6904,7 +6904,7 @@
         <v>497</v>
       </c>
       <c r="C499" t="n">
-        <v>0.062168</v>
+        <v>0.06263299999999999</v>
       </c>
     </row>
     <row r="500">
@@ -6917,7 +6917,7 @@
         <v>498</v>
       </c>
       <c r="C500" t="n">
-        <v>0.06263299999999999</v>
+        <v>0.062844</v>
       </c>
     </row>
     <row r="501">
@@ -6930,7 +6930,7 @@
         <v>499</v>
       </c>
       <c r="C501" t="n">
-        <v>0.062844</v>
+        <v>0.063808</v>
       </c>
     </row>
     <row r="502">
@@ -6943,7 +6943,7 @@
         <v>500</v>
       </c>
       <c r="C502" t="n">
-        <v>0.063808</v>
+        <v>0.064842</v>
       </c>
     </row>
     <row r="503">
@@ -6956,7 +6956,7 @@
         <v>501</v>
       </c>
       <c r="C503" t="n">
-        <v>0.064842</v>
+        <v>0.06555900000000001</v>
       </c>
     </row>
     <row r="504">
@@ -6969,7 +6969,7 @@
         <v>502</v>
       </c>
       <c r="C504" t="n">
-        <v>0.06555900000000001</v>
+        <v>0.067176</v>
       </c>
     </row>
     <row r="505">
@@ -6982,7 +6982,7 @@
         <v>503</v>
       </c>
       <c r="C505" t="n">
-        <v>0.067176</v>
+        <v>0.06736399999999999</v>
       </c>
     </row>
     <row r="506">
@@ -6995,7 +6995,7 @@
         <v>504</v>
       </c>
       <c r="C506" t="n">
-        <v>0.06736399999999999</v>
+        <v>0.067375</v>
       </c>
     </row>
     <row r="507">
@@ -7008,7 +7008,7 @@
         <v>505</v>
       </c>
       <c r="C507" t="n">
-        <v>0.067375</v>
+        <v>0.067555</v>
       </c>
     </row>
     <row r="508">
@@ -7021,7 +7021,7 @@
         <v>506</v>
       </c>
       <c r="C508" t="n">
-        <v>0.067555</v>
+        <v>0.067604</v>
       </c>
     </row>
     <row r="509">
@@ -7034,7 +7034,7 @@
         <v>507</v>
       </c>
       <c r="C509" t="n">
-        <v>0.067604</v>
+        <v>0.067644</v>
       </c>
     </row>
     <row r="510">
@@ -7047,7 +7047,7 @@
         <v>508</v>
       </c>
       <c r="C510" t="n">
-        <v>0.067644</v>
+        <v>0.068111</v>
       </c>
     </row>
     <row r="511">
@@ -7060,7 +7060,7 @@
         <v>509</v>
       </c>
       <c r="C511" t="n">
-        <v>0.068111</v>
+        <v>0.068538</v>
       </c>
     </row>
     <row r="512">
@@ -7073,7 +7073,7 @@
         <v>510</v>
       </c>
       <c r="C512" t="n">
-        <v>0.068538</v>
+        <v>0.068601</v>
       </c>
     </row>
     <row r="513">
@@ -7086,7 +7086,7 @@
         <v>511</v>
       </c>
       <c r="C513" t="n">
-        <v>0.068601</v>
+        <v>0.068845</v>
       </c>
     </row>
     <row r="514">
@@ -7099,7 +7099,7 @@
         <v>512</v>
       </c>
       <c r="C514" t="n">
-        <v>0.068845</v>
+        <v>0.068939</v>
       </c>
     </row>
     <row r="515">
@@ -7112,7 +7112,7 @@
         <v>513</v>
       </c>
       <c r="C515" t="n">
-        <v>0.068939</v>
+        <v>0.06909</v>
       </c>
     </row>
     <row r="516">
@@ -7125,7 +7125,7 @@
         <v>514</v>
       </c>
       <c r="C516" t="n">
-        <v>0.06909</v>
+        <v>0.069253</v>
       </c>
     </row>
     <row r="517">
@@ -7138,7 +7138,7 @@
         <v>515</v>
       </c>
       <c r="C517" t="n">
-        <v>0.069253</v>
+        <v>0.070214</v>
       </c>
     </row>
     <row r="518">
@@ -7151,7 +7151,7 @@
         <v>516</v>
       </c>
       <c r="C518" t="n">
-        <v>0.070214</v>
+        <v>0.070659</v>
       </c>
     </row>
     <row r="519">
@@ -7164,7 +7164,7 @@
         <v>517</v>
       </c>
       <c r="C519" t="n">
-        <v>0.070659</v>
+        <v>0.071449</v>
       </c>
     </row>
     <row r="520">
@@ -8802,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.244724</v>
+        <v>-0.244907</v>
       </c>
     </row>
     <row r="646">
@@ -8815,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.154884</v>
+        <v>-0.154908</v>
       </c>
     </row>
     <row r="647">
@@ -8828,7 +8828,7 @@
         <v>2</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.15196</v>
+        <v>-0.151961</v>
       </c>
     </row>
     <row r="648">
@@ -8841,7 +8841,7 @@
         <v>3</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.128012</v>
+        <v>-0.128032</v>
       </c>
     </row>
     <row r="649">
@@ -8854,7 +8854,7 @@
         <v>4</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.110332</v>
+        <v>-0.110363</v>
       </c>
     </row>
     <row r="650">
@@ -8867,7 +8867,7 @@
         <v>5</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.106278</v>
+        <v>-0.106292</v>
       </c>
     </row>
     <row r="651">
@@ -8880,7 +8880,7 @@
         <v>6</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.103792</v>
+        <v>-0.103791</v>
       </c>
     </row>
     <row r="652">
@@ -8893,7 +8893,7 @@
         <v>7</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.100571</v>
+        <v>-0.100585</v>
       </c>
     </row>
     <row r="653">
@@ -8906,7 +8906,7 @@
         <v>8</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.099805</v>
+        <v>-0.09980600000000001</v>
       </c>
     </row>
     <row r="654">
@@ -8919,7 +8919,7 @@
         <v>9</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.096641</v>
+        <v>-0.096647</v>
       </c>
     </row>
     <row r="655">
@@ -8932,7 +8932,7 @@
         <v>10</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.094655</v>
+        <v>-0.094654</v>
       </c>
     </row>
     <row r="656">
@@ -8958,7 +8958,7 @@
         <v>12</v>
       </c>
       <c r="C657" t="n">
-        <v>-0.094024</v>
+        <v>-0.094031</v>
       </c>
     </row>
     <row r="658">
@@ -8971,7 +8971,7 @@
         <v>13</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.093053</v>
+        <v>-0.093059</v>
       </c>
     </row>
     <row r="659">
@@ -8984,7 +8984,7 @@
         <v>14</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.09275600000000001</v>
+        <v>-0.09275799999999999</v>
       </c>
     </row>
     <row r="660">
@@ -8997,7 +8997,7 @@
         <v>15</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.09263299999999999</v>
+        <v>-0.092726</v>
       </c>
     </row>
     <row r="661">
@@ -9010,7 +9010,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.090223</v>
+        <v>-0.09025</v>
       </c>
     </row>
     <row r="662">
@@ -9023,7 +9023,7 @@
         <v>17</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.08716400000000001</v>
+        <v>-0.087162</v>
       </c>
     </row>
     <row r="663">
@@ -9036,7 +9036,7 @@
         <v>18</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.087158</v>
+        <v>-0.08716</v>
       </c>
     </row>
     <row r="664">
@@ -9049,7 +9049,7 @@
         <v>19</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.086053</v>
+        <v>-0.08605500000000001</v>
       </c>
     </row>
     <row r="665">
@@ -9062,7 +9062,7 @@
         <v>20</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.084749</v>
+        <v>-0.08475199999999999</v>
       </c>
     </row>
     <row r="666">
@@ -9075,7 +9075,7 @@
         <v>21</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.084533</v>
       </c>
     </row>
     <row r="667">
@@ -9088,7 +9088,7 @@
         <v>22</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.084395</v>
+        <v>-0.084394</v>
       </c>
     </row>
     <row r="668">
@@ -9114,7 +9114,7 @@
         <v>24</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.082354</v>
+        <v>-0.082445</v>
       </c>
     </row>
     <row r="670">
@@ -9127,7 +9127,7 @@
         <v>25</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.081718</v>
+        <v>-0.08181099999999999</v>
       </c>
     </row>
     <row r="671">
@@ -9140,7 +9140,7 @@
         <v>26</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.081085</v>
+        <v>-0.08108600000000001</v>
       </c>
     </row>
     <row r="672">
@@ -9153,7 +9153,7 @@
         <v>27</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.080369</v>
+        <v>-0.080373</v>
       </c>
     </row>
     <row r="673">
@@ -9166,7 +9166,7 @@
         <v>28</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.079999</v>
+        <v>-0.080003</v>
       </c>
     </row>
     <row r="674">
@@ -9179,7 +9179,7 @@
         <v>29</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.078346</v>
+        <v>-0.07843700000000001</v>
       </c>
     </row>
     <row r="675">
@@ -9192,7 +9192,7 @@
         <v>30</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.07675</v>
+        <v>-0.076749</v>
       </c>
     </row>
     <row r="676">
@@ -9205,7 +9205,7 @@
         <v>31</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.07611900000000001</v>
+        <v>-0.07620499999999999</v>
       </c>
     </row>
     <row r="677">
@@ -9218,7 +9218,7 @@
         <v>32</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.074976</v>
+        <v>-0.07506</v>
       </c>
     </row>
     <row r="678">
@@ -9231,7 +9231,7 @@
         <v>33</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.074754</v>
+        <v>-0.07475800000000001</v>
       </c>
     </row>
     <row r="679">
@@ -9244,7 +9244,7 @@
         <v>34</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.07151100000000001</v>
+        <v>-0.071536</v>
       </c>
     </row>
     <row r="680">
@@ -9257,7 +9257,7 @@
         <v>35</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.071161</v>
+        <v>-0.07119499999999999</v>
       </c>
     </row>
     <row r="681">
@@ -9270,7 +9270,7 @@
         <v>36</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.070703</v>
+        <v>-0.070743</v>
       </c>
     </row>
     <row r="682">
@@ -9283,7 +9283,7 @@
         <v>37</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.069421</v>
+        <v>-0.069454</v>
       </c>
     </row>
     <row r="683">
@@ -9296,7 +9296,7 @@
         <v>38</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.06755800000000001</v>
+        <v>-0.067568</v>
       </c>
     </row>
     <row r="684">
@@ -9309,7 +9309,7 @@
         <v>39</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.065223</v>
+        <v>-0.065222</v>
       </c>
     </row>
     <row r="685">
@@ -9322,7 +9322,7 @@
         <v>40</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.064877</v>
+        <v>-0.064945</v>
       </c>
     </row>
     <row r="686">
@@ -9335,7 +9335,7 @@
         <v>41</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.064667</v>
+        <v>-0.064669</v>
       </c>
     </row>
     <row r="687">
@@ -9348,7 +9348,7 @@
         <v>42</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.06293600000000001</v>
+        <v>-0.062962</v>
       </c>
     </row>
     <row r="688">
@@ -9361,7 +9361,7 @@
         <v>43</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.062068</v>
+        <v>-0.062069</v>
       </c>
     </row>
     <row r="689">
@@ -9374,7 +9374,7 @@
         <v>44</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.061856</v>
+        <v>-0.061887</v>
       </c>
     </row>
     <row r="690">
@@ -9387,7 +9387,7 @@
         <v>45</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.060448</v>
+        <v>-0.060451</v>
       </c>
     </row>
     <row r="691">
@@ -9400,7 +9400,7 @@
         <v>46</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.060172</v>
+        <v>-0.060173</v>
       </c>
     </row>
     <row r="692">
@@ -9413,7 +9413,7 @@
         <v>47</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.059871</v>
+        <v>-0.05987</v>
       </c>
     </row>
     <row r="693">
@@ -9426,7 +9426,7 @@
         <v>48</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.059728</v>
+        <v>-0.059747</v>
       </c>
     </row>
     <row r="694">
@@ -9439,7 +9439,7 @@
         <v>49</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.059683</v>
+        <v>-0.059728</v>
       </c>
     </row>
     <row r="695">
@@ -9452,7 +9452,7 @@
         <v>50</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.058847</v>
+        <v>-0.05889</v>
       </c>
     </row>
     <row r="696">
@@ -9465,7 +9465,7 @@
         <v>51</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.058094</v>
+        <v>-0.058121</v>
       </c>
     </row>
     <row r="697">
@@ -9478,7 +9478,7 @@
         <v>52</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.057664</v>
+        <v>-0.057782</v>
       </c>
     </row>
     <row r="698">
@@ -9504,7 +9504,7 @@
         <v>54</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.056677</v>
+        <v>-0.056681</v>
       </c>
     </row>
     <row r="700">
@@ -9517,7 +9517,7 @@
         <v>55</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.056362</v>
+        <v>-0.056371</v>
       </c>
     </row>
     <row r="701">
@@ -9530,7 +9530,7 @@
         <v>56</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.055509</v>
+        <v>-0.055511</v>
       </c>
     </row>
     <row r="702">
@@ -9543,7 +9543,7 @@
         <v>57</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.05535</v>
+        <v>-0.055359</v>
       </c>
     </row>
     <row r="703">
@@ -9556,7 +9556,7 @@
         <v>58</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.054974</v>
+        <v>-0.054973</v>
       </c>
     </row>
     <row r="704">
@@ -9569,7 +9569,7 @@
         <v>59</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.054402</v>
+        <v>-0.054405</v>
       </c>
     </row>
     <row r="705">
@@ -9582,7 +9582,7 @@
         <v>60</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.054145</v>
+        <v>-0.054169</v>
       </c>
     </row>
     <row r="706">
@@ -9595,7 +9595,7 @@
         <v>61</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.05396</v>
+        <v>-0.053965</v>
       </c>
     </row>
     <row r="707">
@@ -9608,7 +9608,7 @@
         <v>62</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.053468</v>
+        <v>-0.053475</v>
       </c>
     </row>
     <row r="708">
@@ -9634,7 +9634,7 @@
         <v>64</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.05323</v>
+        <v>-0.053252</v>
       </c>
     </row>
     <row r="710">
@@ -9660,7 +9660,7 @@
         <v>66</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.051009</v>
+        <v>-0.051008</v>
       </c>
     </row>
     <row r="712">
@@ -9686,7 +9686,7 @@
         <v>68</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.049435</v>
+        <v>-0.049467</v>
       </c>
     </row>
     <row r="714">
@@ -9699,7 +9699,7 @@
         <v>69</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.049171</v>
+        <v>-0.04917</v>
       </c>
     </row>
     <row r="715">
@@ -9712,7 +9712,7 @@
         <v>70</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.049047</v>
+        <v>-0.04906</v>
       </c>
     </row>
     <row r="716">
@@ -9725,7 +9725,7 @@
         <v>71</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.048987</v>
+        <v>-0.049006</v>
       </c>
     </row>
     <row r="717">
@@ -9738,7 +9738,7 @@
         <v>72</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.048682</v>
+        <v>-0.048684</v>
       </c>
     </row>
     <row r="718">
@@ -9751,7 +9751,7 @@
         <v>73</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.047918</v>
+        <v>-0.047929</v>
       </c>
     </row>
     <row r="719">
@@ -9764,7 +9764,7 @@
         <v>74</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.047404</v>
+        <v>-0.047407</v>
       </c>
     </row>
     <row r="720">
@@ -9777,7 +9777,7 @@
         <v>75</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.047216</v>
+        <v>-0.047229</v>
       </c>
     </row>
     <row r="721">
@@ -9790,7 +9790,7 @@
         <v>76</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.047212</v>
+        <v>-0.047213</v>
       </c>
     </row>
     <row r="722">
@@ -9816,7 +9816,7 @@
         <v>78</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.046579</v>
+        <v>-0.046607</v>
       </c>
     </row>
     <row r="724">
@@ -9829,7 +9829,7 @@
         <v>79</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.046168</v>
+        <v>-0.046198</v>
       </c>
     </row>
     <row r="725">
@@ -9842,7 +9842,7 @@
         <v>80</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.046006</v>
+        <v>-0.046023</v>
       </c>
     </row>
     <row r="726">
@@ -9855,7 +9855,7 @@
         <v>81</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.045695</v>
+        <v>-0.045694</v>
       </c>
     </row>
     <row r="727">
@@ -9868,7 +9868,7 @@
         <v>82</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.045644</v>
+        <v>-0.045645</v>
       </c>
     </row>
     <row r="728">
@@ -9894,7 +9894,7 @@
         <v>84</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.04545</v>
+        <v>-0.045472</v>
       </c>
     </row>
     <row r="730">
@@ -9907,7 +9907,7 @@
         <v>85</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.045201</v>
+        <v>-0.0452</v>
       </c>
     </row>
     <row r="731">
@@ -9920,7 +9920,7 @@
         <v>86</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.044663</v>
+        <v>-0.044708</v>
       </c>
     </row>
     <row r="732">
@@ -9933,7 +9933,7 @@
         <v>87</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.044231</v>
+        <v>-0.044241</v>
       </c>
     </row>
     <row r="733">
@@ -9946,7 +9946,7 @@
         <v>88</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.044078</v>
+        <v>-0.04408</v>
       </c>
     </row>
     <row r="734">
@@ -9959,7 +9959,7 @@
         <v>89</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.04377</v>
+        <v>-0.043838</v>
       </c>
     </row>
     <row r="735">
@@ -9972,7 +9972,7 @@
         <v>90</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.043614</v>
+        <v>-0.043617</v>
       </c>
     </row>
     <row r="736">
@@ -9985,7 +9985,7 @@
         <v>91</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.043249</v>
+        <v>-0.043254</v>
       </c>
     </row>
     <row r="737">
@@ -9998,7 +9998,7 @@
         <v>92</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.043127</v>
+        <v>-0.043138</v>
       </c>
     </row>
     <row r="738">
@@ -10024,7 +10024,7 @@
         <v>94</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.042482</v>
+        <v>-0.042492</v>
       </c>
     </row>
     <row r="740">
@@ -10037,7 +10037,7 @@
         <v>95</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.041947</v>
+        <v>-0.041957</v>
       </c>
     </row>
     <row r="741">
@@ -10050,7 +10050,7 @@
         <v>96</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.041872</v>
+        <v>-0.041923</v>
       </c>
     </row>
     <row r="742">
@@ -10063,7 +10063,7 @@
         <v>97</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.041829</v>
+        <v>-0.041837</v>
       </c>
     </row>
     <row r="743">
@@ -10076,7 +10076,7 @@
         <v>98</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.040861</v>
+        <v>-0.040896</v>
       </c>
     </row>
     <row r="744">
@@ -10102,7 +10102,7 @@
         <v>100</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.040631</v>
+        <v>-0.040634</v>
       </c>
     </row>
     <row r="746">
@@ -10115,7 +10115,7 @@
         <v>101</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.040619</v>
+        <v>-0.040625</v>
       </c>
     </row>
     <row r="747">
@@ -10141,7 +10141,7 @@
         <v>103</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.04037</v>
+        <v>-0.040401</v>
       </c>
     </row>
     <row r="749">
@@ -10154,7 +10154,7 @@
         <v>104</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.039725</v>
+        <v>-0.039735</v>
       </c>
     </row>
     <row r="750">
@@ -10167,7 +10167,7 @@
         <v>105</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.039518</v>
+        <v>-0.039528</v>
       </c>
     </row>
     <row r="751">
@@ -10206,7 +10206,7 @@
         <v>108</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.039224</v>
+        <v>-0.039226</v>
       </c>
     </row>
     <row r="754">
@@ -10232,7 +10232,7 @@
         <v>110</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.035762</v>
+        <v>-0.035766</v>
       </c>
     </row>
     <row r="756">
@@ -10258,7 +10258,7 @@
         <v>112</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.035606</v>
+        <v>-0.035608</v>
       </c>
     </row>
     <row r="758">
@@ -10271,7 +10271,7 @@
         <v>113</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.034342</v>
+        <v>-0.034341</v>
       </c>
     </row>
     <row r="759">
@@ -10284,7 +10284,7 @@
         <v>114</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.034218</v>
+        <v>-0.034266</v>
       </c>
     </row>
     <row r="760">
@@ -10297,7 +10297,7 @@
         <v>115</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.033916</v>
+        <v>-0.033924</v>
       </c>
     </row>
     <row r="761">
@@ -10323,7 +10323,7 @@
         <v>117</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.033354</v>
+        <v>-0.033367</v>
       </c>
     </row>
     <row r="763">
@@ -10336,7 +10336,7 @@
         <v>118</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.032454</v>
+        <v>-0.032453</v>
       </c>
     </row>
     <row r="764">
@@ -10349,7 +10349,7 @@
         <v>119</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.032415</v>
+        <v>-0.032443</v>
       </c>
     </row>
     <row r="765">
@@ -10362,7 +10362,7 @@
         <v>120</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.032409</v>
+        <v>-0.032429</v>
       </c>
     </row>
     <row r="766">
@@ -10375,7 +10375,7 @@
         <v>121</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.032267</v>
+        <v>-0.032288</v>
       </c>
     </row>
     <row r="767">
@@ -10388,7 +10388,7 @@
         <v>122</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.03146</v>
+        <v>-0.031465</v>
       </c>
     </row>
     <row r="768">
@@ -10401,7 +10401,7 @@
         <v>123</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.030463</v>
+        <v>-0.030472</v>
       </c>
     </row>
     <row r="769">
@@ -10414,7 +10414,7 @@
         <v>124</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.030266</v>
+        <v>-0.030302</v>
       </c>
     </row>
     <row r="770">
@@ -10427,7 +10427,7 @@
         <v>125</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.030122</v>
+        <v>-0.030154</v>
       </c>
     </row>
     <row r="771">
@@ -10440,7 +10440,7 @@
         <v>126</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.030092</v>
+        <v>-0.030091</v>
       </c>
     </row>
     <row r="772">
@@ -10453,7 +10453,7 @@
         <v>127</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.029323</v>
+        <v>-0.029332</v>
       </c>
     </row>
     <row r="773">
@@ -10466,7 +10466,7 @@
         <v>128</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.028722</v>
+        <v>-0.028773</v>
       </c>
     </row>
     <row r="774">
@@ -10492,7 +10492,7 @@
         <v>130</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.028564</v>
+        <v>-0.028567</v>
       </c>
     </row>
     <row r="776">
@@ -10505,7 +10505,7 @@
         <v>131</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.028289</v>
+        <v>-0.028295</v>
       </c>
     </row>
     <row r="777">
@@ -10518,7 +10518,7 @@
         <v>132</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.027832</v>
+        <v>-0.027892</v>
       </c>
     </row>
     <row r="778">
@@ -10531,7 +10531,7 @@
         <v>133</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.027266</v>
+        <v>-0.027285</v>
       </c>
     </row>
     <row r="779">
@@ -10544,7 +10544,7 @@
         <v>134</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.026739</v>
+        <v>-0.026742</v>
       </c>
     </row>
     <row r="780">
@@ -10557,7 +10557,7 @@
         <v>135</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.026721</v>
+        <v>-0.026724</v>
       </c>
     </row>
     <row r="781">
@@ -10570,7 +10570,7 @@
         <v>136</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.026191</v>
+        <v>-0.026195</v>
       </c>
     </row>
     <row r="782">
@@ -10583,7 +10583,7 @@
         <v>137</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.025918</v>
+        <v>-0.025931</v>
       </c>
     </row>
     <row r="783">
@@ -10596,7 +10596,7 @@
         <v>138</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.025632</v>
+        <v>-0.025636</v>
       </c>
     </row>
     <row r="784">
@@ -10609,7 +10609,7 @@
         <v>139</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.025107</v>
+        <v>-0.025108</v>
       </c>
     </row>
     <row r="785">
@@ -10661,7 +10661,7 @@
         <v>143</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.024603</v>
+        <v>-0.024617</v>
       </c>
     </row>
     <row r="789">
@@ -10674,7 +10674,7 @@
         <v>144</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.024559</v>
+        <v>-0.024562</v>
       </c>
     </row>
     <row r="790">
@@ -10700,7 +10700,7 @@
         <v>146</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.023383</v>
+        <v>-0.023384</v>
       </c>
     </row>
     <row r="792">
@@ -10713,7 +10713,7 @@
         <v>147</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.022661</v>
+        <v>-0.02266</v>
       </c>
     </row>
     <row r="793">
@@ -10726,7 +10726,7 @@
         <v>148</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.022562</v>
+        <v>-0.022565</v>
       </c>
     </row>
     <row r="794">
@@ -10752,7 +10752,7 @@
         <v>150</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.021512</v>
+        <v>-0.021513</v>
       </c>
     </row>
     <row r="796">
@@ -10765,7 +10765,7 @@
         <v>151</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.021367</v>
+        <v>-0.021374</v>
       </c>
     </row>
     <row r="797">
@@ -10791,7 +10791,7 @@
         <v>153</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.021127</v>
+        <v>-0.021134</v>
       </c>
     </row>
     <row r="799">
@@ -10804,7 +10804,7 @@
         <v>154</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.021001</v>
+        <v>-0.021007</v>
       </c>
     </row>
     <row r="800">
@@ -10817,7 +10817,7 @@
         <v>155</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.019667</v>
+        <v>-0.019676</v>
       </c>
     </row>
     <row r="801">
@@ -10830,7 +10830,7 @@
         <v>156</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.019599</v>
+        <v>-0.0196</v>
       </c>
     </row>
     <row r="802">
@@ -10843,7 +10843,7 @@
         <v>157</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.019569</v>
+        <v>-0.01957</v>
       </c>
     </row>
     <row r="803">
@@ -10856,7 +10856,7 @@
         <v>158</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.019403</v>
+        <v>-0.019411</v>
       </c>
     </row>
     <row r="804">
@@ -10869,7 +10869,7 @@
         <v>159</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.019149</v>
+        <v>-0.019151</v>
       </c>
     </row>
     <row r="805">
@@ -10908,7 +10908,7 @@
         <v>162</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.018361</v>
+        <v>-0.018391</v>
       </c>
     </row>
     <row r="808">
@@ -10921,7 +10921,7 @@
         <v>163</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.018003</v>
+        <v>-0.018004</v>
       </c>
     </row>
     <row r="809">
@@ -10973,7 +10973,7 @@
         <v>167</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.017255</v>
+        <v>-0.017259</v>
       </c>
     </row>
     <row r="813">
@@ -10986,7 +10986,7 @@
         <v>168</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.017159</v>
+        <v>-0.017165</v>
       </c>
     </row>
     <row r="814">
@@ -10999,7 +10999,7 @@
         <v>169</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.017112</v>
+        <v>-0.017113</v>
       </c>
     </row>
     <row r="815">
@@ -11051,7 +11051,7 @@
         <v>173</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.016338</v>
+        <v>-0.016342</v>
       </c>
     </row>
     <row r="819">
@@ -11064,7 +11064,7 @@
         <v>174</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.016002</v>
+        <v>-0.016004</v>
       </c>
     </row>
     <row r="820">
@@ -11103,7 +11103,7 @@
         <v>177</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.015449</v>
+        <v>-0.015454</v>
       </c>
     </row>
     <row r="823">
@@ -11116,7 +11116,7 @@
         <v>178</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.015361</v>
+        <v>-0.015362</v>
       </c>
     </row>
     <row r="824">
@@ -11129,7 +11129,7 @@
         <v>179</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.015289</v>
+        <v>-0.015302</v>
       </c>
     </row>
     <row r="825">
@@ -11142,7 +11142,7 @@
         <v>180</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.014897</v>
+        <v>-0.0149</v>
       </c>
     </row>
     <row r="826">
@@ -11155,7 +11155,7 @@
         <v>181</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.014237</v>
+        <v>-0.014238</v>
       </c>
     </row>
     <row r="827">
@@ -11181,7 +11181,7 @@
         <v>183</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.013297</v>
+        <v>-0.013311</v>
       </c>
     </row>
     <row r="829">
@@ -11194,7 +11194,7 @@
         <v>184</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.013108</v>
+        <v>-0.01312</v>
       </c>
     </row>
     <row r="830">
@@ -11207,7 +11207,7 @@
         <v>185</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.012357</v>
+        <v>-0.012362</v>
       </c>
     </row>
     <row r="831">
@@ -11220,7 +11220,7 @@
         <v>186</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.012261</v>
+        <v>-0.012266</v>
       </c>
     </row>
     <row r="832">
@@ -11272,7 +11272,7 @@
         <v>190</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.0112</v>
+        <v>-0.011203</v>
       </c>
     </row>
     <row r="836">
@@ -11285,7 +11285,7 @@
         <v>191</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.01107</v>
+        <v>-0.011071</v>
       </c>
     </row>
     <row r="837">
@@ -11298,7 +11298,7 @@
         <v>192</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.010876</v>
+        <v>-0.010878</v>
       </c>
     </row>
     <row r="838">
@@ -11311,7 +11311,7 @@
         <v>193</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.010853</v>
+        <v>-0.010855</v>
       </c>
     </row>
     <row r="839">
@@ -11324,7 +11324,7 @@
         <v>194</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.010705</v>
+        <v>-0.010707</v>
       </c>
     </row>
     <row r="840">
@@ -11337,7 +11337,7 @@
         <v>195</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.010514</v>
+        <v>-0.010521</v>
       </c>
     </row>
     <row r="841">
@@ -11350,7 +11350,7 @@
         <v>196</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.010427</v>
+        <v>-0.010441</v>
       </c>
     </row>
     <row r="842">
@@ -11363,7 +11363,7 @@
         <v>197</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.010231</v>
+        <v>-0.010237</v>
       </c>
     </row>
     <row r="843">
@@ -11376,7 +11376,7 @@
         <v>198</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.009679</v>
+        <v>-0.009679999999999999</v>
       </c>
     </row>
     <row r="844">
@@ -11389,7 +11389,7 @@
         <v>199</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.009416000000000001</v>
+        <v>-0.009417999999999999</v>
       </c>
     </row>
     <row r="845">
@@ -11415,7 +11415,7 @@
         <v>201</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.008605</v>
+        <v>-0.008619999999999999</v>
       </c>
     </row>
     <row r="847">
@@ -11441,7 +11441,7 @@
         <v>203</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.008154</v>
+        <v>-0.008156</v>
       </c>
     </row>
     <row r="849">
@@ -11454,7 +11454,7 @@
         <v>204</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.008121</v>
+        <v>-0.008123999999999999</v>
       </c>
     </row>
     <row r="850">
@@ -11467,7 +11467,7 @@
         <v>205</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.007906</v>
+        <v>-0.007908</v>
       </c>
     </row>
     <row r="851">
@@ -11506,7 +11506,7 @@
         <v>208</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.00704</v>
+        <v>-0.007044</v>
       </c>
     </row>
     <row r="854">
@@ -11519,7 +11519,7 @@
         <v>209</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.006964</v>
+        <v>-0.006965</v>
       </c>
     </row>
     <row r="855">
@@ -11532,7 +11532,7 @@
         <v>210</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.006618</v>
+        <v>-0.006619</v>
       </c>
     </row>
     <row r="856">
@@ -11558,7 +11558,7 @@
         <v>212</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.00638</v>
+        <v>-0.006383</v>
       </c>
     </row>
     <row r="858">
@@ -11571,7 +11571,7 @@
         <v>213</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.006276</v>
+        <v>-0.006277</v>
       </c>
     </row>
     <row r="859">
@@ -11584,7 +11584,7 @@
         <v>214</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.006172</v>
+        <v>-0.006174</v>
       </c>
     </row>
     <row r="860">
@@ -11597,7 +11597,7 @@
         <v>215</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.005728</v>
+        <v>-0.005735</v>
       </c>
     </row>
     <row r="861">
@@ -11610,7 +11610,7 @@
         <v>216</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.005665</v>
+        <v>-0.005666</v>
       </c>
     </row>
     <row r="862">
@@ -11623,7 +11623,7 @@
         <v>217</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.005246</v>
+        <v>-0.005247</v>
       </c>
     </row>
     <row r="863">
@@ -11636,7 +11636,7 @@
         <v>218</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.005091</v>
+        <v>-0.005097</v>
       </c>
     </row>
     <row r="864">
@@ -11649,7 +11649,7 @@
         <v>219</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.005044</v>
+        <v>-0.005045</v>
       </c>
     </row>
     <row r="865">
@@ -11662,7 +11662,7 @@
         <v>220</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.004999</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="866">
@@ -11688,7 +11688,7 @@
         <v>222</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.004283</v>
+        <v>-0.004285</v>
       </c>
     </row>
     <row r="868">
@@ -11701,7 +11701,7 @@
         <v>223</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.004178</v>
+        <v>-0.004179</v>
       </c>
     </row>
     <row r="869">
@@ -11714,7 +11714,7 @@
         <v>224</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.004068</v>
+        <v>-0.004069</v>
       </c>
     </row>
     <row r="870">
@@ -11727,7 +11727,7 @@
         <v>225</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.003798</v>
+        <v>-0.003799</v>
       </c>
     </row>
     <row r="871">
@@ -11740,7 +11740,7 @@
         <v>226</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.003795</v>
+        <v>-0.003798</v>
       </c>
     </row>
     <row r="872">
@@ -11766,7 +11766,7 @@
         <v>228</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.003743</v>
+        <v>-0.003744</v>
       </c>
     </row>
     <row r="874">
@@ -11779,7 +11779,7 @@
         <v>229</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.003643</v>
+        <v>-0.003644</v>
       </c>
     </row>
     <row r="875">
@@ -11792,7 +11792,7 @@
         <v>230</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.003397</v>
+        <v>-0.003401</v>
       </c>
     </row>
     <row r="876">
@@ -11805,7 +11805,7 @@
         <v>231</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.00292</v>
+        <v>-0.002921</v>
       </c>
     </row>
     <row r="877">
@@ -11844,7 +11844,7 @@
         <v>234</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.002456</v>
+        <v>-0.002459</v>
       </c>
     </row>
     <row r="880">
@@ -11883,7 +11883,7 @@
         <v>237</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.001987</v>
+        <v>-0.001992</v>
       </c>
     </row>
     <row r="883">
@@ -11909,7 +11909,7 @@
         <v>239</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.001553</v>
+        <v>-0.001556</v>
       </c>
     </row>
     <row r="885">
@@ -11961,7 +11961,7 @@
         <v>243</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.001236</v>
+        <v>-0.001239</v>
       </c>
     </row>
     <row r="889">
@@ -12104,7 +12104,7 @@
         <v>254</v>
       </c>
       <c r="C899" t="n">
-        <v>0.001658</v>
+        <v>0.001659</v>
       </c>
     </row>
     <row r="900">
@@ -12130,7 +12130,7 @@
         <v>256</v>
       </c>
       <c r="C901" t="n">
-        <v>0.001997</v>
+        <v>0.001998</v>
       </c>
     </row>
     <row r="902">
@@ -12156,7 +12156,7 @@
         <v>258</v>
       </c>
       <c r="C903" t="n">
-        <v>0.00227</v>
+        <v>0.002273</v>
       </c>
     </row>
     <row r="904">
@@ -12169,7 +12169,7 @@
         <v>259</v>
       </c>
       <c r="C904" t="n">
-        <v>0.002335</v>
+        <v>0.002336</v>
       </c>
     </row>
     <row r="905">
@@ -12221,7 +12221,7 @@
         <v>263</v>
       </c>
       <c r="C908" t="n">
-        <v>0.003011</v>
+        <v>0.003013</v>
       </c>
     </row>
     <row r="909">
@@ -12247,7 +12247,7 @@
         <v>265</v>
       </c>
       <c r="C910" t="n">
-        <v>0.003504</v>
+        <v>0.003508</v>
       </c>
     </row>
     <row r="911">
@@ -12299,7 +12299,7 @@
         <v>269</v>
       </c>
       <c r="C914" t="n">
-        <v>0.004407</v>
+        <v>0.004408</v>
       </c>
     </row>
     <row r="915">
@@ -12325,7 +12325,7 @@
         <v>271</v>
       </c>
       <c r="C916" t="n">
-        <v>0.004553</v>
+        <v>0.004554</v>
       </c>
     </row>
     <row r="917">
@@ -12338,7 +12338,7 @@
         <v>272</v>
       </c>
       <c r="C917" t="n">
-        <v>0.004678</v>
+        <v>0.004679</v>
       </c>
     </row>
     <row r="918">
@@ -12364,7 +12364,7 @@
         <v>274</v>
       </c>
       <c r="C919" t="n">
-        <v>0.005048</v>
+        <v>0.005056</v>
       </c>
     </row>
     <row r="920">
@@ -12377,7 +12377,7 @@
         <v>275</v>
       </c>
       <c r="C920" t="n">
-        <v>0.005068</v>
+        <v>0.005072</v>
       </c>
     </row>
     <row r="921">
@@ -12390,7 +12390,7 @@
         <v>276</v>
       </c>
       <c r="C921" t="n">
-        <v>0.005201</v>
+        <v>0.005202</v>
       </c>
     </row>
     <row r="922">
@@ -12403,7 +12403,7 @@
         <v>277</v>
       </c>
       <c r="C922" t="n">
-        <v>0.005368</v>
+        <v>0.005371</v>
       </c>
     </row>
     <row r="923">
@@ -12416,7 +12416,7 @@
         <v>278</v>
       </c>
       <c r="C923" t="n">
-        <v>0.005413</v>
+        <v>0.005422</v>
       </c>
     </row>
     <row r="924">
@@ -12429,7 +12429,7 @@
         <v>279</v>
       </c>
       <c r="C924" t="n">
-        <v>0.005889</v>
+        <v>0.005891</v>
       </c>
     </row>
     <row r="925">
@@ -12442,7 +12442,7 @@
         <v>280</v>
       </c>
       <c r="C925" t="n">
-        <v>0.006147</v>
+        <v>0.006149</v>
       </c>
     </row>
     <row r="926">
@@ -12455,7 +12455,7 @@
         <v>281</v>
       </c>
       <c r="C926" t="n">
-        <v>0.006633</v>
+        <v>0.006634</v>
       </c>
     </row>
     <row r="927">
@@ -12468,7 +12468,7 @@
         <v>282</v>
       </c>
       <c r="C927" t="n">
-        <v>0.007458</v>
+        <v>0.00746</v>
       </c>
     </row>
     <row r="928">
@@ -12507,7 +12507,7 @@
         <v>285</v>
       </c>
       <c r="C930" t="n">
-        <v>0.007906</v>
+        <v>0.007913999999999999</v>
       </c>
     </row>
     <row r="931">
@@ -12520,7 +12520,7 @@
         <v>286</v>
       </c>
       <c r="C931" t="n">
-        <v>0.008007999999999999</v>
+        <v>0.00801</v>
       </c>
     </row>
     <row r="932">
@@ -12546,7 +12546,7 @@
         <v>288</v>
       </c>
       <c r="C933" t="n">
-        <v>0.008201</v>
+        <v>0.008203</v>
       </c>
     </row>
     <row r="934">
@@ -12559,7 +12559,7 @@
         <v>289</v>
       </c>
       <c r="C934" t="n">
-        <v>0.008324</v>
+        <v>0.008336</v>
       </c>
     </row>
     <row r="935">
@@ -12572,7 +12572,7 @@
         <v>290</v>
       </c>
       <c r="C935" t="n">
-        <v>0.008463</v>
+        <v>0.008465</v>
       </c>
     </row>
     <row r="936">
@@ -12598,7 +12598,7 @@
         <v>292</v>
       </c>
       <c r="C937" t="n">
-        <v>0.008812</v>
+        <v>0.008817999999999999</v>
       </c>
     </row>
     <row r="938">
@@ -12611,7 +12611,7 @@
         <v>293</v>
       </c>
       <c r="C938" t="n">
-        <v>0.009029000000000001</v>
+        <v>0.009042</v>
       </c>
     </row>
     <row r="939">
@@ -12624,7 +12624,7 @@
         <v>294</v>
       </c>
       <c r="C939" t="n">
-        <v>0.009472</v>
+        <v>0.009473000000000001</v>
       </c>
     </row>
     <row r="940">
@@ -12637,7 +12637,7 @@
         <v>295</v>
       </c>
       <c r="C940" t="n">
-        <v>0.009769999999999999</v>
+        <v>0.009776999999999999</v>
       </c>
     </row>
     <row r="941">
@@ -12650,7 +12650,7 @@
         <v>296</v>
       </c>
       <c r="C941" t="n">
-        <v>0.009778</v>
+        <v>0.009782000000000001</v>
       </c>
     </row>
     <row r="942">
@@ -12676,7 +12676,7 @@
         <v>298</v>
       </c>
       <c r="C943" t="n">
-        <v>0.010004</v>
+        <v>0.010005</v>
       </c>
     </row>
     <row r="944">
@@ -12689,7 +12689,7 @@
         <v>299</v>
       </c>
       <c r="C944" t="n">
-        <v>0.01007</v>
+        <v>0.010072</v>
       </c>
     </row>
     <row r="945">
@@ -12702,7 +12702,7 @@
         <v>300</v>
       </c>
       <c r="C945" t="n">
-        <v>0.010247</v>
+        <v>0.010261</v>
       </c>
     </row>
     <row r="946">
@@ -12715,7 +12715,7 @@
         <v>301</v>
       </c>
       <c r="C946" t="n">
-        <v>0.010301</v>
+        <v>0.010302</v>
       </c>
     </row>
     <row r="947">
@@ -12754,7 +12754,7 @@
         <v>304</v>
       </c>
       <c r="C949" t="n">
-        <v>0.011022</v>
+        <v>0.011024</v>
       </c>
     </row>
     <row r="950">
@@ -12780,7 +12780,7 @@
         <v>306</v>
       </c>
       <c r="C951" t="n">
-        <v>0.011203</v>
+        <v>0.011205</v>
       </c>
     </row>
     <row r="952">
@@ -12793,7 +12793,7 @@
         <v>307</v>
       </c>
       <c r="C952" t="n">
-        <v>0.011271</v>
+        <v>0.011272</v>
       </c>
     </row>
     <row r="953">
@@ -12806,7 +12806,7 @@
         <v>308</v>
       </c>
       <c r="C953" t="n">
-        <v>0.011576</v>
+        <v>0.011577</v>
       </c>
     </row>
     <row r="954">
@@ -12819,7 +12819,7 @@
         <v>309</v>
       </c>
       <c r="C954" t="n">
-        <v>0.011673</v>
+        <v>0.011675</v>
       </c>
     </row>
     <row r="955">
@@ -12845,7 +12845,7 @@
         <v>311</v>
       </c>
       <c r="C956" t="n">
-        <v>0.012186</v>
+        <v>0.012192</v>
       </c>
     </row>
     <row r="957">
@@ -12858,7 +12858,7 @@
         <v>312</v>
       </c>
       <c r="C957" t="n">
-        <v>0.012305</v>
+        <v>0.012309</v>
       </c>
     </row>
     <row r="958">
@@ -12871,7 +12871,7 @@
         <v>313</v>
       </c>
       <c r="C958" t="n">
-        <v>0.012645</v>
+        <v>0.012647</v>
       </c>
     </row>
     <row r="959">
@@ -12897,7 +12897,7 @@
         <v>315</v>
       </c>
       <c r="C960" t="n">
-        <v>0.012757</v>
+        <v>0.012756</v>
       </c>
     </row>
     <row r="961">
@@ -12910,7 +12910,7 @@
         <v>316</v>
       </c>
       <c r="C961" t="n">
-        <v>0.012835</v>
+        <v>0.012839</v>
       </c>
     </row>
     <row r="962">
@@ -12923,7 +12923,7 @@
         <v>317</v>
       </c>
       <c r="C962" t="n">
-        <v>0.012912</v>
+        <v>0.012918</v>
       </c>
     </row>
     <row r="963">
@@ -12936,7 +12936,7 @@
         <v>318</v>
       </c>
       <c r="C963" t="n">
-        <v>0.013093</v>
+        <v>0.013101</v>
       </c>
     </row>
     <row r="964">
@@ -12988,7 +12988,7 @@
         <v>322</v>
       </c>
       <c r="C967" t="n">
-        <v>0.0135</v>
+        <v>0.013523</v>
       </c>
     </row>
     <row r="968">
@@ -13001,7 +13001,7 @@
         <v>323</v>
       </c>
       <c r="C968" t="n">
-        <v>0.013873</v>
+        <v>0.013874</v>
       </c>
     </row>
     <row r="969">
@@ -13027,7 +13027,7 @@
         <v>325</v>
       </c>
       <c r="C970" t="n">
-        <v>0.014671</v>
+        <v>0.014672</v>
       </c>
     </row>
     <row r="971">
@@ -13066,7 +13066,7 @@
         <v>328</v>
       </c>
       <c r="C973" t="n">
-        <v>0.014934</v>
+        <v>0.014941</v>
       </c>
     </row>
     <row r="974">
@@ -13079,7 +13079,7 @@
         <v>329</v>
       </c>
       <c r="C974" t="n">
-        <v>0.015136</v>
+        <v>0.015137</v>
       </c>
     </row>
     <row r="975">
@@ -13105,7 +13105,7 @@
         <v>331</v>
       </c>
       <c r="C976" t="n">
-        <v>0.015402</v>
+        <v>0.01542</v>
       </c>
     </row>
     <row r="977">
@@ -13118,7 +13118,7 @@
         <v>332</v>
       </c>
       <c r="C977" t="n">
-        <v>0.01578</v>
+        <v>0.015781</v>
       </c>
     </row>
     <row r="978">
@@ -13131,7 +13131,7 @@
         <v>333</v>
       </c>
       <c r="C978" t="n">
-        <v>0.015839</v>
+        <v>0.01584</v>
       </c>
     </row>
     <row r="979">
@@ -13144,7 +13144,7 @@
         <v>334</v>
       </c>
       <c r="C979" t="n">
-        <v>0.015937</v>
+        <v>0.015946</v>
       </c>
     </row>
     <row r="980">
@@ -13157,7 +13157,7 @@
         <v>335</v>
       </c>
       <c r="C980" t="n">
-        <v>0.016174</v>
+        <v>0.016184</v>
       </c>
     </row>
     <row r="981">
@@ -13170,7 +13170,7 @@
         <v>336</v>
       </c>
       <c r="C981" t="n">
-        <v>0.016541</v>
+        <v>0.01654</v>
       </c>
     </row>
     <row r="982">
@@ -13183,7 +13183,7 @@
         <v>337</v>
       </c>
       <c r="C982" t="n">
-        <v>0.016803</v>
+        <v>0.016809</v>
       </c>
     </row>
     <row r="983">
@@ -13196,7 +13196,7 @@
         <v>338</v>
       </c>
       <c r="C983" t="n">
-        <v>0.017025</v>
+        <v>0.017031</v>
       </c>
     </row>
     <row r="984">
@@ -13209,7 +13209,7 @@
         <v>339</v>
       </c>
       <c r="C984" t="n">
-        <v>0.017292</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="985">
@@ -13222,7 +13222,7 @@
         <v>340</v>
       </c>
       <c r="C985" t="n">
-        <v>0.017323</v>
+        <v>0.017326</v>
       </c>
     </row>
     <row r="986">
@@ -13235,7 +13235,7 @@
         <v>341</v>
       </c>
       <c r="C986" t="n">
-        <v>0.017333</v>
+        <v>0.017335</v>
       </c>
     </row>
     <row r="987">
@@ -13248,7 +13248,7 @@
         <v>342</v>
       </c>
       <c r="C987" t="n">
-        <v>0.017451</v>
+        <v>0.017453</v>
       </c>
     </row>
     <row r="988">
@@ -13274,7 +13274,7 @@
         <v>344</v>
       </c>
       <c r="C989" t="n">
-        <v>0.017567</v>
+        <v>0.017571</v>
       </c>
     </row>
     <row r="990">
@@ -13287,7 +13287,7 @@
         <v>345</v>
       </c>
       <c r="C990" t="n">
-        <v>0.018023</v>
+        <v>0.01804</v>
       </c>
     </row>
     <row r="991">
@@ -13300,7 +13300,7 @@
         <v>346</v>
       </c>
       <c r="C991" t="n">
-        <v>0.018147</v>
+        <v>0.018155</v>
       </c>
     </row>
     <row r="992">
@@ -13313,7 +13313,7 @@
         <v>347</v>
       </c>
       <c r="C992" t="n">
-        <v>0.018718</v>
+        <v>0.018721</v>
       </c>
     </row>
     <row r="993">
@@ -13339,7 +13339,7 @@
         <v>349</v>
       </c>
       <c r="C994" t="n">
-        <v>0.019139</v>
+        <v>0.019142</v>
       </c>
     </row>
     <row r="995">
@@ -13352,7 +13352,7 @@
         <v>350</v>
       </c>
       <c r="C995" t="n">
-        <v>0.019158</v>
+        <v>0.019159</v>
       </c>
     </row>
     <row r="996">
@@ -13391,7 +13391,7 @@
         <v>353</v>
       </c>
       <c r="C998" t="n">
-        <v>0.02031</v>
+        <v>0.020315</v>
       </c>
     </row>
     <row r="999">
@@ -13404,7 +13404,7 @@
         <v>354</v>
       </c>
       <c r="C999" t="n">
-        <v>0.020586</v>
+        <v>0.020599</v>
       </c>
     </row>
     <row r="1000">
@@ -13430,7 +13430,7 @@
         <v>356</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.020698</v>
+        <v>0.020743</v>
       </c>
     </row>
     <row r="1002">
@@ -13456,7 +13456,7 @@
         <v>358</v>
       </c>
       <c r="C1003" t="n">
-        <v>0.021202</v>
+        <v>0.021207</v>
       </c>
     </row>
     <row r="1004">
@@ -13469,7 +13469,7 @@
         <v>359</v>
       </c>
       <c r="C1004" t="n">
-        <v>0.021299</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="1005">
@@ -13508,7 +13508,7 @@
         <v>362</v>
       </c>
       <c r="C1007" t="n">
-        <v>0.021812</v>
+        <v>0.021821</v>
       </c>
     </row>
     <row r="1008">
@@ -13534,7 +13534,7 @@
         <v>364</v>
       </c>
       <c r="C1009" t="n">
-        <v>0.02199</v>
+        <v>0.021992</v>
       </c>
     </row>
     <row r="1010">
@@ -13547,7 +13547,7 @@
         <v>365</v>
       </c>
       <c r="C1010" t="n">
-        <v>0.022159</v>
+        <v>0.02216</v>
       </c>
     </row>
     <row r="1011">
@@ -13560,7 +13560,7 @@
         <v>366</v>
       </c>
       <c r="C1011" t="n">
-        <v>0.022338</v>
+        <v>0.022339</v>
       </c>
     </row>
     <row r="1012">
@@ -13573,7 +13573,7 @@
         <v>367</v>
       </c>
       <c r="C1012" t="n">
-        <v>0.022578</v>
+        <v>0.022579</v>
       </c>
     </row>
     <row r="1013">
@@ -13586,7 +13586,7 @@
         <v>368</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.02305</v>
+        <v>0.023052</v>
       </c>
     </row>
     <row r="1014">
@@ -13599,7 +13599,7 @@
         <v>369</v>
       </c>
       <c r="C1014" t="n">
-        <v>0.02312</v>
+        <v>0.023129</v>
       </c>
     </row>
     <row r="1015">
@@ -13612,7 +13612,7 @@
         <v>370</v>
       </c>
       <c r="C1015" t="n">
-        <v>0.023219</v>
+        <v>0.023222</v>
       </c>
     </row>
     <row r="1016">
@@ -13625,7 +13625,7 @@
         <v>371</v>
       </c>
       <c r="C1016" t="n">
-        <v>0.023296</v>
+        <v>0.023306</v>
       </c>
     </row>
     <row r="1017">
@@ -13638,7 +13638,7 @@
         <v>372</v>
       </c>
       <c r="C1017" t="n">
-        <v>0.023493</v>
+        <v>0.023494</v>
       </c>
     </row>
     <row r="1018">
@@ -13664,7 +13664,7 @@
         <v>374</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.023633</v>
+        <v>0.023635</v>
       </c>
     </row>
     <row r="1020">
@@ -13690,7 +13690,7 @@
         <v>376</v>
       </c>
       <c r="C1021" t="n">
-        <v>0.023904</v>
+        <v>0.023903</v>
       </c>
     </row>
     <row r="1022">
@@ -13703,7 +13703,7 @@
         <v>377</v>
       </c>
       <c r="C1022" t="n">
-        <v>0.024117</v>
+        <v>0.024133</v>
       </c>
     </row>
     <row r="1023">
@@ -13716,7 +13716,7 @@
         <v>378</v>
       </c>
       <c r="C1023" t="n">
-        <v>0.025525</v>
+        <v>0.025529</v>
       </c>
     </row>
     <row r="1024">
@@ -13729,7 +13729,7 @@
         <v>379</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.02559</v>
+        <v>0.025599</v>
       </c>
     </row>
     <row r="1025">
@@ -13742,7 +13742,7 @@
         <v>380</v>
       </c>
       <c r="C1025" t="n">
-        <v>0.025815</v>
+        <v>0.025831</v>
       </c>
     </row>
     <row r="1026">
@@ -13755,7 +13755,7 @@
         <v>381</v>
       </c>
       <c r="C1026" t="n">
-        <v>0.025922</v>
+        <v>0.025921</v>
       </c>
     </row>
     <row r="1027">
@@ -13781,7 +13781,7 @@
         <v>383</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.025984</v>
+        <v>0.025987</v>
       </c>
     </row>
     <row r="1029">
@@ -13794,7 +13794,7 @@
         <v>384</v>
       </c>
       <c r="C1029" t="n">
-        <v>0.026068</v>
+        <v>0.026079</v>
       </c>
     </row>
     <row r="1030">
@@ -13820,7 +13820,7 @@
         <v>386</v>
       </c>
       <c r="C1031" t="n">
-        <v>0.026652</v>
+        <v>0.026663</v>
       </c>
     </row>
     <row r="1032">
@@ -13833,7 +13833,7 @@
         <v>387</v>
       </c>
       <c r="C1032" t="n">
-        <v>0.026715</v>
+        <v>0.026716</v>
       </c>
     </row>
     <row r="1033">
@@ -13846,7 +13846,7 @@
         <v>388</v>
       </c>
       <c r="C1033" t="n">
-        <v>0.027067</v>
+        <v>0.027085</v>
       </c>
     </row>
     <row r="1034">
@@ -13859,7 +13859,7 @@
         <v>389</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.027243</v>
+        <v>0.027249</v>
       </c>
     </row>
     <row r="1035">
@@ -13872,7 +13872,7 @@
         <v>390</v>
       </c>
       <c r="C1035" t="n">
-        <v>0.027411</v>
+        <v>0.027421</v>
       </c>
     </row>
     <row r="1036">
@@ -13885,7 +13885,7 @@
         <v>391</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.027684</v>
+        <v>0.027685</v>
       </c>
     </row>
     <row r="1037">
@@ -13898,7 +13898,7 @@
         <v>392</v>
       </c>
       <c r="C1037" t="n">
-        <v>0.027765</v>
+        <v>0.027766</v>
       </c>
     </row>
     <row r="1038">
@@ -13911,7 +13911,7 @@
         <v>393</v>
       </c>
       <c r="C1038" t="n">
-        <v>0.027897</v>
+        <v>0.027899</v>
       </c>
     </row>
     <row r="1039">
@@ -13924,7 +13924,7 @@
         <v>394</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.028206</v>
+        <v>0.028209</v>
       </c>
     </row>
     <row r="1040">
@@ -13937,7 +13937,7 @@
         <v>395</v>
       </c>
       <c r="C1040" t="n">
-        <v>0.028502</v>
+        <v>0.028506</v>
       </c>
     </row>
     <row r="1041">
@@ -13950,7 +13950,7 @@
         <v>396</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.028641</v>
+        <v>0.028688</v>
       </c>
     </row>
     <row r="1042">
@@ -13963,7 +13963,7 @@
         <v>397</v>
       </c>
       <c r="C1042" t="n">
-        <v>0.028947</v>
+        <v>0.028948</v>
       </c>
     </row>
     <row r="1043">
@@ -14002,7 +14002,7 @@
         <v>400</v>
       </c>
       <c r="C1045" t="n">
-        <v>0.029467</v>
+        <v>0.029495</v>
       </c>
     </row>
     <row r="1046">
@@ -14015,7 +14015,7 @@
         <v>401</v>
       </c>
       <c r="C1046" t="n">
-        <v>0.029638</v>
+        <v>0.029639</v>
       </c>
     </row>
     <row r="1047">
@@ -14028,7 +14028,7 @@
         <v>402</v>
       </c>
       <c r="C1047" t="n">
-        <v>0.029643</v>
+        <v>0.029651</v>
       </c>
     </row>
     <row r="1048">
@@ -14054,7 +14054,7 @@
         <v>404</v>
       </c>
       <c r="C1049" t="n">
-        <v>0.030121</v>
+        <v>0.030137</v>
       </c>
     </row>
     <row r="1050">
@@ -14080,7 +14080,7 @@
         <v>406</v>
       </c>
       <c r="C1051" t="n">
-        <v>0.030186</v>
+        <v>0.030206</v>
       </c>
     </row>
     <row r="1052">
@@ -14093,7 +14093,7 @@
         <v>407</v>
       </c>
       <c r="C1052" t="n">
-        <v>0.030204</v>
+        <v>0.030207</v>
       </c>
     </row>
     <row r="1053">
@@ -14106,7 +14106,7 @@
         <v>408</v>
       </c>
       <c r="C1053" t="n">
-        <v>0.030346</v>
+        <v>0.030345</v>
       </c>
     </row>
     <row r="1054">
@@ -14119,7 +14119,7 @@
         <v>409</v>
       </c>
       <c r="C1054" t="n">
-        <v>0.030714</v>
+        <v>0.030726</v>
       </c>
     </row>
     <row r="1055">
@@ -14145,7 +14145,7 @@
         <v>411</v>
       </c>
       <c r="C1056" t="n">
-        <v>0.031344</v>
+        <v>0.031349</v>
       </c>
     </row>
     <row r="1057">
@@ -14158,7 +14158,7 @@
         <v>412</v>
       </c>
       <c r="C1057" t="n">
-        <v>0.031728</v>
+        <v>0.031735</v>
       </c>
     </row>
     <row r="1058">
@@ -14171,7 +14171,7 @@
         <v>413</v>
       </c>
       <c r="C1058" t="n">
-        <v>0.031961</v>
+        <v>0.031983</v>
       </c>
     </row>
     <row r="1059">
@@ -14184,7 +14184,7 @@
         <v>414</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.032085</v>
+        <v>0.032087</v>
       </c>
     </row>
     <row r="1060">
@@ -14197,7 +14197,7 @@
         <v>415</v>
       </c>
       <c r="C1060" t="n">
-        <v>0.03217</v>
+        <v>0.032175</v>
       </c>
     </row>
     <row r="1061">
@@ -14210,7 +14210,7 @@
         <v>416</v>
       </c>
       <c r="C1061" t="n">
-        <v>0.032242</v>
+        <v>0.032266</v>
       </c>
     </row>
     <row r="1062">
@@ -14223,7 +14223,7 @@
         <v>417</v>
       </c>
       <c r="C1062" t="n">
-        <v>0.032506</v>
+        <v>0.032536</v>
       </c>
     </row>
     <row r="1063">
@@ -14249,7 +14249,7 @@
         <v>419</v>
       </c>
       <c r="C1064" t="n">
-        <v>0.032984</v>
+        <v>0.033001</v>
       </c>
     </row>
     <row r="1065">
@@ -14262,7 +14262,7 @@
         <v>420</v>
       </c>
       <c r="C1065" t="n">
-        <v>0.033098</v>
+        <v>0.033122</v>
       </c>
     </row>
     <row r="1066">
@@ -14288,7 +14288,7 @@
         <v>422</v>
       </c>
       <c r="C1067" t="n">
-        <v>0.033265</v>
+        <v>0.033268</v>
       </c>
     </row>
     <row r="1068">
@@ -14314,7 +14314,7 @@
         <v>424</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.034469</v>
+        <v>0.034472</v>
       </c>
     </row>
     <row r="1070">
@@ -14327,7 +14327,7 @@
         <v>425</v>
       </c>
       <c r="C1070" t="n">
-        <v>0.034513</v>
+        <v>0.034521</v>
       </c>
     </row>
     <row r="1071">
@@ -14340,7 +14340,7 @@
         <v>426</v>
       </c>
       <c r="C1071" t="n">
-        <v>0.034687</v>
+        <v>0.034688</v>
       </c>
     </row>
     <row r="1072">
@@ -14353,7 +14353,7 @@
         <v>427</v>
       </c>
       <c r="C1072" t="n">
-        <v>0.035224</v>
+        <v>0.035225</v>
       </c>
     </row>
     <row r="1073">
@@ -14379,7 +14379,7 @@
         <v>429</v>
       </c>
       <c r="C1074" t="n">
-        <v>0.035462</v>
+        <v>0.035465</v>
       </c>
     </row>
     <row r="1075">
@@ -14392,7 +14392,7 @@
         <v>430</v>
       </c>
       <c r="C1075" t="n">
-        <v>0.035667</v>
+        <v>0.035668</v>
       </c>
     </row>
     <row r="1076">
@@ -14405,7 +14405,7 @@
         <v>431</v>
       </c>
       <c r="C1076" t="n">
-        <v>0.03569</v>
+        <v>0.035711</v>
       </c>
     </row>
     <row r="1077">
@@ -14418,7 +14418,7 @@
         <v>432</v>
       </c>
       <c r="C1077" t="n">
-        <v>0.035936</v>
+        <v>0.035951</v>
       </c>
     </row>
     <row r="1078">
@@ -14431,7 +14431,7 @@
         <v>433</v>
       </c>
       <c r="C1078" t="n">
-        <v>0.036313</v>
+        <v>0.036312</v>
       </c>
     </row>
     <row r="1079">
@@ -14444,7 +14444,7 @@
         <v>434</v>
       </c>
       <c r="C1079" t="n">
-        <v>0.036482</v>
+        <v>0.036485</v>
       </c>
     </row>
     <row r="1080">
@@ -14457,7 +14457,7 @@
         <v>435</v>
       </c>
       <c r="C1080" t="n">
-        <v>0.036651</v>
+        <v>0.03666</v>
       </c>
     </row>
     <row r="1081">
@@ -14470,7 +14470,7 @@
         <v>436</v>
       </c>
       <c r="C1081" t="n">
-        <v>0.036706</v>
+        <v>0.036721</v>
       </c>
     </row>
     <row r="1082">
@@ -14483,7 +14483,7 @@
         <v>437</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.036765</v>
+        <v>0.036777</v>
       </c>
     </row>
     <row r="1083">
@@ -14496,7 +14496,7 @@
         <v>438</v>
       </c>
       <c r="C1083" t="n">
-        <v>0.038157</v>
+        <v>0.038159</v>
       </c>
     </row>
     <row r="1084">
@@ -14509,7 +14509,7 @@
         <v>439</v>
       </c>
       <c r="C1084" t="n">
-        <v>0.038282</v>
+        <v>0.038304</v>
       </c>
     </row>
     <row r="1085">
@@ -14522,7 +14522,7 @@
         <v>440</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.038479</v>
+        <v>0.038482</v>
       </c>
     </row>
     <row r="1086">
@@ -14548,7 +14548,7 @@
         <v>442</v>
       </c>
       <c r="C1087" t="n">
-        <v>0.038871</v>
+        <v>0.038872</v>
       </c>
     </row>
     <row r="1088">
@@ -14561,7 +14561,7 @@
         <v>443</v>
       </c>
       <c r="C1088" t="n">
-        <v>0.038947</v>
+        <v>0.038949</v>
       </c>
     </row>
     <row r="1089">
@@ -14574,7 +14574,7 @@
         <v>444</v>
       </c>
       <c r="C1089" t="n">
-        <v>0.039113</v>
+        <v>0.039117</v>
       </c>
     </row>
     <row r="1090">
@@ -14587,7 +14587,7 @@
         <v>445</v>
       </c>
       <c r="C1090" t="n">
-        <v>0.039481</v>
+        <v>0.039503</v>
       </c>
     </row>
     <row r="1091">
@@ -14600,7 +14600,7 @@
         <v>446</v>
       </c>
       <c r="C1091" t="n">
-        <v>0.039499</v>
+        <v>0.039504</v>
       </c>
     </row>
     <row r="1092">
@@ -14626,7 +14626,7 @@
         <v>448</v>
       </c>
       <c r="C1093" t="n">
-        <v>0.03986</v>
+        <v>0.039866</v>
       </c>
     </row>
     <row r="1094">
@@ -14639,7 +14639,7 @@
         <v>449</v>
       </c>
       <c r="C1094" t="n">
-        <v>0.040032</v>
+        <v>0.040054</v>
       </c>
     </row>
     <row r="1095">
@@ -14652,7 +14652,7 @@
         <v>450</v>
       </c>
       <c r="C1095" t="n">
-        <v>0.040032</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="1096">
@@ -14665,7 +14665,7 @@
         <v>451</v>
       </c>
       <c r="C1096" t="n">
-        <v>0.040171</v>
+        <v>0.040391</v>
       </c>
     </row>
     <row r="1097">
@@ -14678,7 +14678,7 @@
         <v>452</v>
       </c>
       <c r="C1097" t="n">
-        <v>0.04037</v>
+        <v>0.040546</v>
       </c>
     </row>
     <row r="1098">
@@ -14691,7 +14691,7 @@
         <v>453</v>
       </c>
       <c r="C1098" t="n">
-        <v>0.040523</v>
+        <v>0.040574</v>
       </c>
     </row>
     <row r="1099">
@@ -14704,7 +14704,7 @@
         <v>454</v>
       </c>
       <c r="C1099" t="n">
-        <v>0.040566</v>
+        <v>0.040724</v>
       </c>
     </row>
     <row r="1100">
@@ -14717,7 +14717,7 @@
         <v>455</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.040692</v>
+        <v>0.040813</v>
       </c>
     </row>
     <row r="1101">
@@ -14730,7 +14730,7 @@
         <v>456</v>
       </c>
       <c r="C1101" t="n">
-        <v>0.040808</v>
+        <v>0.040894</v>
       </c>
     </row>
     <row r="1102">
@@ -14743,7 +14743,7 @@
         <v>457</v>
       </c>
       <c r="C1102" t="n">
-        <v>0.040878</v>
+        <v>0.041301</v>
       </c>
     </row>
     <row r="1103">
@@ -14756,7 +14756,7 @@
         <v>458</v>
       </c>
       <c r="C1103" t="n">
-        <v>0.041294</v>
+        <v>0.041786</v>
       </c>
     </row>
     <row r="1104">
@@ -14769,7 +14769,7 @@
         <v>459</v>
       </c>
       <c r="C1104" t="n">
-        <v>0.041781</v>
+        <v>0.041976</v>
       </c>
     </row>
     <row r="1105">
@@ -14782,7 +14782,7 @@
         <v>460</v>
       </c>
       <c r="C1105" t="n">
-        <v>0.041931</v>
+        <v>0.04217</v>
       </c>
     </row>
     <row r="1106">
@@ -14795,7 +14795,7 @@
         <v>461</v>
       </c>
       <c r="C1106" t="n">
-        <v>0.042157</v>
+        <v>0.042316</v>
       </c>
     </row>
     <row r="1107">
@@ -14808,7 +14808,7 @@
         <v>462</v>
       </c>
       <c r="C1107" t="n">
-        <v>0.042276</v>
+        <v>0.042488</v>
       </c>
     </row>
     <row r="1108">
@@ -14821,7 +14821,7 @@
         <v>463</v>
       </c>
       <c r="C1108" t="n">
-        <v>0.042486</v>
+        <v>0.042618</v>
       </c>
     </row>
     <row r="1109">
@@ -14834,7 +14834,7 @@
         <v>464</v>
       </c>
       <c r="C1109" t="n">
-        <v>0.042606</v>
+        <v>0.043463</v>
       </c>
     </row>
     <row r="1110">
@@ -14847,7 +14847,7 @@
         <v>465</v>
       </c>
       <c r="C1110" t="n">
-        <v>0.043457</v>
+        <v>0.043838</v>
       </c>
     </row>
     <row r="1111">
@@ -14860,7 +14860,7 @@
         <v>466</v>
       </c>
       <c r="C1111" t="n">
-        <v>0.043819</v>
+        <v>0.043858</v>
       </c>
     </row>
     <row r="1112">
@@ -14873,7 +14873,7 @@
         <v>467</v>
       </c>
       <c r="C1112" t="n">
-        <v>0.043856</v>
+        <v>0.044544</v>
       </c>
     </row>
     <row r="1113">
@@ -14886,7 +14886,7 @@
         <v>468</v>
       </c>
       <c r="C1113" t="n">
-        <v>0.044538</v>
+        <v>0.044569</v>
       </c>
     </row>
     <row r="1114">
@@ -14899,7 +14899,7 @@
         <v>469</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.044566</v>
+        <v>0.044799</v>
       </c>
     </row>
     <row r="1115">
@@ -14912,7 +14912,7 @@
         <v>470</v>
       </c>
       <c r="C1115" t="n">
-        <v>0.044797</v>
+        <v>0.045129</v>
       </c>
     </row>
     <row r="1116">
@@ -14925,7 +14925,7 @@
         <v>471</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.045101</v>
+        <v>0.045383</v>
       </c>
     </row>
     <row r="1117">
@@ -14938,7 +14938,7 @@
         <v>472</v>
       </c>
       <c r="C1117" t="n">
-        <v>0.04538</v>
+        <v>0.04568</v>
       </c>
     </row>
     <row r="1118">
@@ -14951,7 +14951,7 @@
         <v>473</v>
       </c>
       <c r="C1118" t="n">
-        <v>0.045662</v>
+        <v>0.045815</v>
       </c>
     </row>
     <row r="1119">
@@ -14964,7 +14964,7 @@
         <v>474</v>
       </c>
       <c r="C1119" t="n">
-        <v>0.045813</v>
+        <v>0.046961</v>
       </c>
     </row>
     <row r="1120">
@@ -14977,7 +14977,7 @@
         <v>475</v>
       </c>
       <c r="C1120" t="n">
-        <v>0.046962</v>
+        <v>0.047055</v>
       </c>
     </row>
     <row r="1121">
@@ -14990,7 +14990,7 @@
         <v>476</v>
       </c>
       <c r="C1121" t="n">
-        <v>0.047055</v>
+        <v>0.0472</v>
       </c>
     </row>
     <row r="1122">
@@ -15003,7 +15003,7 @@
         <v>477</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.047199</v>
+        <v>0.047362</v>
       </c>
     </row>
     <row r="1123">
@@ -15016,7 +15016,7 @@
         <v>478</v>
       </c>
       <c r="C1123" t="n">
-        <v>0.047324</v>
+        <v>0.047392</v>
       </c>
     </row>
     <row r="1124">
@@ -15029,7 +15029,7 @@
         <v>479</v>
       </c>
       <c r="C1124" t="n">
-        <v>0.047388</v>
+        <v>0.048047</v>
       </c>
     </row>
     <row r="1125">
@@ -15042,7 +15042,7 @@
         <v>480</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.04804</v>
+        <v>0.04816</v>
       </c>
     </row>
     <row r="1126">
@@ -15055,7 +15055,7 @@
         <v>481</v>
       </c>
       <c r="C1126" t="n">
-        <v>0.04816</v>
+        <v>0.048188</v>
       </c>
     </row>
     <row r="1127">
@@ -15068,7 +15068,7 @@
         <v>482</v>
       </c>
       <c r="C1127" t="n">
-        <v>0.048185</v>
+        <v>0.048499</v>
       </c>
     </row>
     <row r="1128">
@@ -15081,7 +15081,7 @@
         <v>483</v>
       </c>
       <c r="C1128" t="n">
-        <v>0.048498</v>
+        <v>0.048531</v>
       </c>
     </row>
     <row r="1129">
@@ -15094,7 +15094,7 @@
         <v>484</v>
       </c>
       <c r="C1129" t="n">
-        <v>0.04853</v>
+        <v>0.048677</v>
       </c>
     </row>
     <row r="1130">
@@ -15107,7 +15107,7 @@
         <v>485</v>
       </c>
       <c r="C1130" t="n">
-        <v>0.048675</v>
+        <v>0.048793</v>
       </c>
     </row>
     <row r="1131">
@@ -15120,7 +15120,7 @@
         <v>486</v>
       </c>
       <c r="C1131" t="n">
-        <v>0.048776</v>
+        <v>0.048829</v>
       </c>
     </row>
     <row r="1132">
@@ -15133,7 +15133,7 @@
         <v>487</v>
       </c>
       <c r="C1132" t="n">
-        <v>0.048805</v>
+        <v>0.048863</v>
       </c>
     </row>
     <row r="1133">
@@ -15146,7 +15146,7 @@
         <v>488</v>
       </c>
       <c r="C1133" t="n">
-        <v>0.048858</v>
+        <v>0.049443</v>
       </c>
     </row>
     <row r="1134">
@@ -15159,7 +15159,7 @@
         <v>489</v>
       </c>
       <c r="C1134" t="n">
-        <v>0.049425</v>
+        <v>0.049646</v>
       </c>
     </row>
     <row r="1135">
@@ -15172,7 +15172,7 @@
         <v>490</v>
       </c>
       <c r="C1135" t="n">
-        <v>0.049632</v>
+        <v>0.049676</v>
       </c>
     </row>
     <row r="1136">
@@ -15185,7 +15185,7 @@
         <v>491</v>
       </c>
       <c r="C1136" t="n">
-        <v>0.049676</v>
+        <v>0.050142</v>
       </c>
     </row>
     <row r="1137">
@@ -15198,7 +15198,7 @@
         <v>492</v>
       </c>
       <c r="C1137" t="n">
-        <v>0.050137</v>
+        <v>0.050345</v>
       </c>
     </row>
     <row r="1138">
@@ -15211,7 +15211,7 @@
         <v>493</v>
       </c>
       <c r="C1138" t="n">
-        <v>0.050343</v>
+        <v>0.050962</v>
       </c>
     </row>
     <row r="1139">
@@ -15224,7 +15224,7 @@
         <v>494</v>
       </c>
       <c r="C1139" t="n">
-        <v>0.050938</v>
+        <v>0.051195</v>
       </c>
     </row>
     <row r="1140">
@@ -15237,7 +15237,7 @@
         <v>495</v>
       </c>
       <c r="C1140" t="n">
-        <v>0.051196</v>
+        <v>0.051244</v>
       </c>
     </row>
     <row r="1141">
@@ -15250,7 +15250,7 @@
         <v>496</v>
       </c>
       <c r="C1141" t="n">
-        <v>0.051226</v>
+        <v>0.051278</v>
       </c>
     </row>
     <row r="1142">
@@ -15263,7 +15263,7 @@
         <v>497</v>
       </c>
       <c r="C1142" t="n">
-        <v>0.051279</v>
+        <v>0.051762</v>
       </c>
     </row>
     <row r="1143">
@@ -15276,7 +15276,7 @@
         <v>498</v>
       </c>
       <c r="C1143" t="n">
-        <v>0.051756</v>
+        <v>0.052705</v>
       </c>
     </row>
     <row r="1144">
@@ -15289,7 +15289,7 @@
         <v>499</v>
       </c>
       <c r="C1144" t="n">
-        <v>0.052695</v>
+        <v>0.053305</v>
       </c>
     </row>
     <row r="1145">
@@ -15302,7 +15302,7 @@
         <v>500</v>
       </c>
       <c r="C1145" t="n">
-        <v>0.053302</v>
+        <v>0.053324</v>
       </c>
     </row>
     <row r="1146">
@@ -15315,7 +15315,7 @@
         <v>501</v>
       </c>
       <c r="C1146" t="n">
-        <v>0.053321</v>
+        <v>0.053468</v>
       </c>
     </row>
     <row r="1147">
@@ -15328,7 +15328,7 @@
         <v>502</v>
       </c>
       <c r="C1147" t="n">
-        <v>0.053465</v>
+        <v>0.053677</v>
       </c>
     </row>
     <row r="1148">
@@ -15341,7 +15341,7 @@
         <v>503</v>
       </c>
       <c r="C1148" t="n">
-        <v>0.053677</v>
+        <v>0.054093</v>
       </c>
     </row>
     <row r="1149">
@@ -15354,7 +15354,7 @@
         <v>504</v>
       </c>
       <c r="C1149" t="n">
-        <v>0.054033</v>
+        <v>0.054231</v>
       </c>
     </row>
     <row r="1150">
@@ -15367,7 +15367,7 @@
         <v>505</v>
       </c>
       <c r="C1150" t="n">
-        <v>0.054233</v>
+        <v>0.054237</v>
       </c>
     </row>
     <row r="1151">
@@ -15380,7 +15380,7 @@
         <v>506</v>
       </c>
       <c r="C1151" t="n">
-        <v>0.055209</v>
+        <v>0.05521</v>
       </c>
     </row>
     <row r="1152">
@@ -15393,7 +15393,7 @@
         <v>507</v>
       </c>
       <c r="C1152" t="n">
-        <v>0.055392</v>
+        <v>0.055401</v>
       </c>
     </row>
     <row r="1153">
@@ -15406,7 +15406,7 @@
         <v>508</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.05592</v>
+        <v>0.055919</v>
       </c>
     </row>
     <row r="1154">
@@ -15419,7 +15419,7 @@
         <v>509</v>
       </c>
       <c r="C1154" t="n">
-        <v>0.056552</v>
+        <v>0.056557</v>
       </c>
     </row>
     <row r="1155">
@@ -15432,7 +15432,7 @@
         <v>510</v>
       </c>
       <c r="C1155" t="n">
-        <v>0.056623</v>
+        <v>0.05663</v>
       </c>
     </row>
     <row r="1156">
@@ -15458,7 +15458,7 @@
         <v>512</v>
       </c>
       <c r="C1157" t="n">
-        <v>0.057532</v>
+        <v>0.057534</v>
       </c>
     </row>
     <row r="1158">
@@ -15484,7 +15484,7 @@
         <v>514</v>
       </c>
       <c r="C1159" t="n">
-        <v>0.058446</v>
+        <v>0.058447</v>
       </c>
     </row>
     <row r="1160">
@@ -15497,7 +15497,7 @@
         <v>515</v>
       </c>
       <c r="C1160" t="n">
-        <v>0.058723</v>
+        <v>0.058722</v>
       </c>
     </row>
     <row r="1161">
@@ -15510,7 +15510,7 @@
         <v>516</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.058868</v>
+        <v>0.05887</v>
       </c>
     </row>
     <row r="1162">
@@ -15523,7 +15523,7 @@
         <v>517</v>
       </c>
       <c r="C1162" t="n">
-        <v>0.060037</v>
+        <v>0.060043</v>
       </c>
     </row>
     <row r="1163">
@@ -15536,7 +15536,7 @@
         <v>518</v>
       </c>
       <c r="C1163" t="n">
-        <v>0.060651</v>
+        <v>0.060691</v>
       </c>
     </row>
     <row r="1164">
@@ -15562,7 +15562,7 @@
         <v>520</v>
       </c>
       <c r="C1165" t="n">
-        <v>0.061079</v>
+        <v>0.061083</v>
       </c>
     </row>
     <row r="1166">
@@ -15575,7 +15575,7 @@
         <v>521</v>
       </c>
       <c r="C1166" t="n">
-        <v>0.061414</v>
+        <v>0.061425</v>
       </c>
     </row>
     <row r="1167">
@@ -15588,7 +15588,7 @@
         <v>522</v>
       </c>
       <c r="C1167" t="n">
-        <v>0.061734</v>
+        <v>0.061739</v>
       </c>
     </row>
     <row r="1168">
@@ -15601,7 +15601,7 @@
         <v>523</v>
       </c>
       <c r="C1168" t="n">
-        <v>0.061762</v>
+        <v>0.061782</v>
       </c>
     </row>
     <row r="1169">
@@ -15614,7 +15614,7 @@
         <v>524</v>
       </c>
       <c r="C1169" t="n">
-        <v>0.061976</v>
+        <v>0.061983</v>
       </c>
     </row>
     <row r="1170">
@@ -15627,7 +15627,7 @@
         <v>525</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.062601</v>
+        <v>0.062621</v>
       </c>
     </row>
     <row r="1171">
@@ -15653,7 +15653,7 @@
         <v>527</v>
       </c>
       <c r="C1172" t="n">
-        <v>0.063205</v>
+        <v>0.063204</v>
       </c>
     </row>
     <row r="1173">
@@ -15666,7 +15666,7 @@
         <v>528</v>
       </c>
       <c r="C1173" t="n">
-        <v>0.063261</v>
+        <v>0.063289</v>
       </c>
     </row>
     <row r="1174">
@@ -15679,7 +15679,7 @@
         <v>529</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.06351</v>
+        <v>0.063509</v>
       </c>
     </row>
     <row r="1175">
@@ -15692,7 +15692,7 @@
         <v>530</v>
       </c>
       <c r="C1175" t="n">
-        <v>0.064373</v>
+        <v>0.064372</v>
       </c>
     </row>
     <row r="1176">
@@ -15705,7 +15705,7 @@
         <v>531</v>
       </c>
       <c r="C1176" t="n">
-        <v>0.064441</v>
+        <v>0.064442</v>
       </c>
     </row>
     <row r="1177">
@@ -15718,7 +15718,7 @@
         <v>532</v>
       </c>
       <c r="C1177" t="n">
-        <v>0.064918</v>
+        <v>0.064926</v>
       </c>
     </row>
     <row r="1178">
@@ -15731,7 +15731,7 @@
         <v>533</v>
       </c>
       <c r="C1178" t="n">
-        <v>0.064958</v>
+        <v>0.06496300000000001</v>
       </c>
     </row>
     <row r="1179">
@@ -15744,7 +15744,7 @@
         <v>534</v>
       </c>
       <c r="C1179" t="n">
-        <v>0.065875</v>
+        <v>0.06587800000000001</v>
       </c>
     </row>
     <row r="1180">
@@ -15757,7 +15757,7 @@
         <v>535</v>
       </c>
       <c r="C1180" t="n">
-        <v>0.066374</v>
+        <v>0.066404</v>
       </c>
     </row>
     <row r="1181">
@@ -15770,7 +15770,7 @@
         <v>536</v>
       </c>
       <c r="C1181" t="n">
-        <v>0.066581</v>
+        <v>0.06658699999999999</v>
       </c>
     </row>
     <row r="1182">
@@ -15783,7 +15783,7 @@
         <v>537</v>
       </c>
       <c r="C1182" t="n">
-        <v>0.066769</v>
+        <v>0.06678099999999999</v>
       </c>
     </row>
     <row r="1183">
@@ -15796,7 +15796,7 @@
         <v>538</v>
       </c>
       <c r="C1183" t="n">
-        <v>0.067022</v>
+        <v>0.067021</v>
       </c>
     </row>
     <row r="1184">
@@ -15809,7 +15809,7 @@
         <v>539</v>
       </c>
       <c r="C1184" t="n">
-        <v>0.067264</v>
+        <v>0.06726799999999999</v>
       </c>
     </row>
     <row r="1185">
@@ -15848,7 +15848,7 @@
         <v>542</v>
       </c>
       <c r="C1187" t="n">
-        <v>0.069947</v>
+        <v>0.070033</v>
       </c>
     </row>
     <row r="1188">
@@ -15861,7 +15861,7 @@
         <v>543</v>
       </c>
       <c r="C1188" t="n">
-        <v>0.070212</v>
+        <v>0.070217</v>
       </c>
     </row>
     <row r="1189">
@@ -15874,7 +15874,7 @@
         <v>544</v>
       </c>
       <c r="C1189" t="n">
-        <v>0.07033499999999999</v>
+        <v>0.070345</v>
       </c>
     </row>
     <row r="1190">
@@ -15887,7 +15887,7 @@
         <v>545</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.070754</v>
+        <v>0.07076</v>
       </c>
     </row>
     <row r="1191">
@@ -15900,7 +15900,7 @@
         <v>546</v>
       </c>
       <c r="C1191" t="n">
-        <v>0.071073</v>
+        <v>0.071076</v>
       </c>
     </row>
     <row r="1192">
@@ -15913,7 +15913,7 @@
         <v>547</v>
       </c>
       <c r="C1192" t="n">
-        <v>0.071516</v>
+        <v>0.071521</v>
       </c>
     </row>
     <row r="1193">
@@ -15926,7 +15926,7 @@
         <v>548</v>
       </c>
       <c r="C1193" t="n">
-        <v>0.07202600000000001</v>
+        <v>0.072051</v>
       </c>
     </row>
     <row r="1194">
@@ -15939,7 +15939,7 @@
         <v>549</v>
       </c>
       <c r="C1194" t="n">
-        <v>0.07278999999999999</v>
+        <v>0.072851</v>
       </c>
     </row>
     <row r="1195">
@@ -15952,7 +15952,7 @@
         <v>550</v>
       </c>
       <c r="C1195" t="n">
-        <v>0.073036</v>
+        <v>0.073044</v>
       </c>
     </row>
     <row r="1196">
@@ -15965,7 +15965,7 @@
         <v>551</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.07349899999999999</v>
+        <v>0.073532</v>
       </c>
     </row>
     <row r="1197">
@@ -15991,7 +15991,7 @@
         <v>553</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.074494</v>
+        <v>0.074499</v>
       </c>
     </row>
     <row r="1199">
@@ -16004,7 +16004,7 @@
         <v>554</v>
       </c>
       <c r="C1199" t="n">
-        <v>0.07475800000000001</v>
+        <v>0.07481500000000001</v>
       </c>
     </row>
     <row r="1200">
@@ -16017,7 +16017,7 @@
         <v>555</v>
       </c>
       <c r="C1200" t="n">
-        <v>0.07522</v>
+        <v>0.07538400000000001</v>
       </c>
     </row>
     <row r="1201">
@@ -16030,7 +16030,7 @@
         <v>556</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.075507</v>
+        <v>0.075512</v>
       </c>
     </row>
     <row r="1202">
@@ -16043,7 +16043,7 @@
         <v>557</v>
       </c>
       <c r="C1202" t="n">
-        <v>0.07553799999999999</v>
+        <v>0.07554</v>
       </c>
     </row>
     <row r="1203">
@@ -16069,7 +16069,7 @@
         <v>559</v>
       </c>
       <c r="C1204" t="n">
-        <v>0.07713</v>
+        <v>0.077138</v>
       </c>
     </row>
     <row r="1205">
@@ -16082,7 +16082,7 @@
         <v>560</v>
       </c>
       <c r="C1205" t="n">
-        <v>0.078503</v>
+        <v>0.07850799999999999</v>
       </c>
     </row>
     <row r="1206">
@@ -16095,7 +16095,7 @@
         <v>561</v>
       </c>
       <c r="C1206" t="n">
-        <v>0.078792</v>
+        <v>0.07882500000000001</v>
       </c>
     </row>
     <row r="1207">
@@ -16108,7 +16108,7 @@
         <v>562</v>
       </c>
       <c r="C1207" t="n">
-        <v>0.079126</v>
+        <v>0.079128</v>
       </c>
     </row>
     <row r="1208">
@@ -16121,7 +16121,7 @@
         <v>563</v>
       </c>
       <c r="C1208" t="n">
-        <v>0.079155</v>
+        <v>0.079161</v>
       </c>
     </row>
     <row r="1209">
@@ -16134,7 +16134,7 @@
         <v>564</v>
       </c>
       <c r="C1209" t="n">
-        <v>0.081662</v>
+        <v>0.08169800000000001</v>
       </c>
     </row>
     <row r="1210">
@@ -16147,7 +16147,7 @@
         <v>565</v>
       </c>
       <c r="C1210" t="n">
-        <v>0.081969</v>
+        <v>0.081968</v>
       </c>
     </row>
     <row r="1211">
@@ -16160,7 +16160,7 @@
         <v>566</v>
       </c>
       <c r="C1211" t="n">
-        <v>0.082567</v>
+        <v>0.08257</v>
       </c>
     </row>
     <row r="1212">
@@ -16173,7 +16173,7 @@
         <v>567</v>
       </c>
       <c r="C1212" t="n">
-        <v>0.082842</v>
+        <v>0.082869</v>
       </c>
     </row>
     <row r="1213">
@@ -16186,7 +16186,7 @@
         <v>568</v>
       </c>
       <c r="C1213" t="n">
-        <v>0.08301799999999999</v>
+        <v>0.083095</v>
       </c>
     </row>
     <row r="1214">
@@ -16199,7 +16199,7 @@
         <v>569</v>
       </c>
       <c r="C1214" t="n">
-        <v>0.084955</v>
+        <v>0.084954</v>
       </c>
     </row>
     <row r="1215">
@@ -16212,7 +16212,7 @@
         <v>570</v>
       </c>
       <c r="C1215" t="n">
-        <v>0.085524</v>
+        <v>0.08555400000000001</v>
       </c>
     </row>
     <row r="1216">
@@ -16225,7 +16225,7 @@
         <v>571</v>
       </c>
       <c r="C1216" t="n">
-        <v>0.085893</v>
+        <v>0.085979</v>
       </c>
     </row>
     <row r="1217">
@@ -16238,7 +16238,7 @@
         <v>572</v>
       </c>
       <c r="C1217" t="n">
-        <v>0.085941</v>
+        <v>0.08609899999999999</v>
       </c>
     </row>
     <row r="1218">
@@ -16251,7 +16251,7 @@
         <v>573</v>
       </c>
       <c r="C1218" t="n">
-        <v>0.0861</v>
+        <v>0.08613899999999999</v>
       </c>
     </row>
     <row r="1219">
@@ -16264,7 +16264,7 @@
         <v>574</v>
       </c>
       <c r="C1219" t="n">
-        <v>0.086534</v>
+        <v>0.08656</v>
       </c>
     </row>
     <row r="1220">
@@ -16290,7 +16290,7 @@
         <v>576</v>
       </c>
       <c r="C1221" t="n">
-        <v>0.088127</v>
+        <v>0.08817999999999999</v>
       </c>
     </row>
     <row r="1222">
@@ -16303,7 +16303,7 @@
         <v>577</v>
       </c>
       <c r="C1222" t="n">
-        <v>0.089202</v>
+        <v>0.089217</v>
       </c>
     </row>
     <row r="1223">
@@ -16316,7 +16316,7 @@
         <v>578</v>
       </c>
       <c r="C1223" t="n">
-        <v>0.08930399999999999</v>
+        <v>0.089305</v>
       </c>
     </row>
     <row r="1224">
@@ -16329,7 +16329,7 @@
         <v>579</v>
       </c>
       <c r="C1224" t="n">
-        <v>0.089619</v>
+        <v>0.089627</v>
       </c>
     </row>
     <row r="1225">
@@ -16342,7 +16342,7 @@
         <v>580</v>
       </c>
       <c r="C1225" t="n">
-        <v>0.08984399999999999</v>
+        <v>0.089978</v>
       </c>
     </row>
     <row r="1226">
@@ -16355,7 +16355,7 @@
         <v>581</v>
       </c>
       <c r="C1226" t="n">
-        <v>0.09003700000000001</v>
+        <v>0.090036</v>
       </c>
     </row>
     <row r="1227">
@@ -16368,7 +16368,7 @@
         <v>582</v>
       </c>
       <c r="C1227" t="n">
-        <v>0.091041</v>
+        <v>0.091042</v>
       </c>
     </row>
     <row r="1228">
@@ -16381,7 +16381,7 @@
         <v>583</v>
       </c>
       <c r="C1228" t="n">
-        <v>0.091463</v>
+        <v>0.091479</v>
       </c>
     </row>
     <row r="1229">
@@ -16394,7 +16394,7 @@
         <v>584</v>
       </c>
       <c r="C1229" t="n">
-        <v>0.09292599999999999</v>
+        <v>0.092945</v>
       </c>
     </row>
     <row r="1230">
@@ -16407,7 +16407,7 @@
         <v>585</v>
       </c>
       <c r="C1230" t="n">
-        <v>0.097275</v>
+        <v>0.097278</v>
       </c>
     </row>
     <row r="1231">
@@ -16420,7 +16420,7 @@
         <v>586</v>
       </c>
       <c r="C1231" t="n">
-        <v>0.097507</v>
+        <v>0.09751</v>
       </c>
     </row>
     <row r="1232">
@@ -16433,7 +16433,7 @@
         <v>587</v>
       </c>
       <c r="C1232" t="n">
-        <v>0.097826</v>
+        <v>0.09783799999999999</v>
       </c>
     </row>
     <row r="1233">
@@ -16446,7 +16446,7 @@
         <v>588</v>
       </c>
       <c r="C1233" t="n">
-        <v>0.097995</v>
+        <v>0.09801799999999999</v>
       </c>
     </row>
     <row r="1234">
@@ -16472,7 +16472,7 @@
         <v>590</v>
       </c>
       <c r="C1235" t="n">
-        <v>0.09876799999999999</v>
+        <v>0.098829</v>
       </c>
     </row>
     <row r="1236">
@@ -16485,7 +16485,7 @@
         <v>591</v>
       </c>
       <c r="C1236" t="n">
-        <v>0.101953</v>
+        <v>0.101976</v>
       </c>
     </row>
     <row r="1237">
@@ -16498,7 +16498,7 @@
         <v>592</v>
       </c>
       <c r="C1237" t="n">
-        <v>0.10302</v>
+        <v>0.103019</v>
       </c>
     </row>
     <row r="1238">
@@ -16511,7 +16511,7 @@
         <v>593</v>
       </c>
       <c r="C1238" t="n">
-        <v>0.104909</v>
+        <v>0.10492</v>
       </c>
     </row>
     <row r="1239">
@@ -16524,7 +16524,7 @@
         <v>594</v>
       </c>
       <c r="C1239" t="n">
-        <v>0.106534</v>
+        <v>0.106538</v>
       </c>
     </row>
     <row r="1240">
@@ -16537,7 +16537,7 @@
         <v>595</v>
       </c>
       <c r="C1240" t="n">
-        <v>0.107283</v>
+        <v>0.107282</v>
       </c>
     </row>
     <row r="1241">
@@ -16550,7 +16550,7 @@
         <v>596</v>
       </c>
       <c r="C1241" t="n">
-        <v>0.108572</v>
+        <v>0.10859</v>
       </c>
     </row>
     <row r="1242">
@@ -16576,7 +16576,7 @@
         <v>598</v>
       </c>
       <c r="C1243" t="n">
-        <v>0.111182</v>
+        <v>0.111305</v>
       </c>
     </row>
     <row r="1244">
@@ -16589,7 +16589,7 @@
         <v>599</v>
       </c>
       <c r="C1244" t="n">
-        <v>0.111584</v>
+        <v>0.111598</v>
       </c>
     </row>
     <row r="1245">
@@ -16602,7 +16602,7 @@
         <v>600</v>
       </c>
       <c r="C1245" t="n">
-        <v>0.112155</v>
+        <v>0.112156</v>
       </c>
     </row>
     <row r="1246">
@@ -16615,7 +16615,7 @@
         <v>601</v>
       </c>
       <c r="C1246" t="n">
-        <v>0.112425</v>
+        <v>0.112433</v>
       </c>
     </row>
     <row r="1247">
@@ -16628,7 +16628,7 @@
         <v>602</v>
       </c>
       <c r="C1247" t="n">
-        <v>0.116591</v>
+        <v>0.116592</v>
       </c>
     </row>
     <row r="1248">
@@ -16641,7 +16641,7 @@
         <v>603</v>
       </c>
       <c r="C1248" t="n">
-        <v>0.117226</v>
+        <v>0.117238</v>
       </c>
     </row>
     <row r="1249">
@@ -16654,7 +16654,7 @@
         <v>604</v>
       </c>
       <c r="C1249" t="n">
-        <v>0.118562</v>
+        <v>0.118569</v>
       </c>
     </row>
     <row r="1250">
@@ -16667,7 +16667,7 @@
         <v>605</v>
       </c>
       <c r="C1250" t="n">
-        <v>0.121243</v>
+        <v>0.121246</v>
       </c>
     </row>
     <row r="1251">
@@ -16680,7 +16680,7 @@
         <v>606</v>
       </c>
       <c r="C1251" t="n">
-        <v>0.121545</v>
+        <v>0.121555</v>
       </c>
     </row>
     <row r="1252">
@@ -16693,7 +16693,7 @@
         <v>607</v>
       </c>
       <c r="C1252" t="n">
-        <v>0.121801</v>
+        <v>0.121804</v>
       </c>
     </row>
     <row r="1253">
@@ -16706,7 +16706,7 @@
         <v>608</v>
       </c>
       <c r="C1253" t="n">
-        <v>0.122361</v>
+        <v>0.122419</v>
       </c>
     </row>
     <row r="1254">
@@ -16719,7 +16719,7 @@
         <v>609</v>
       </c>
       <c r="C1254" t="n">
-        <v>0.125265</v>
+        <v>0.125348</v>
       </c>
     </row>
     <row r="1255">
@@ -16732,7 +16732,7 @@
         <v>610</v>
       </c>
       <c r="C1255" t="n">
-        <v>0.125837</v>
+        <v>0.125845</v>
       </c>
     </row>
     <row r="1256">
@@ -16745,7 +16745,7 @@
         <v>611</v>
       </c>
       <c r="C1256" t="n">
-        <v>0.126641</v>
+        <v>0.126642</v>
       </c>
     </row>
     <row r="1257">
@@ -16758,7 +16758,7 @@
         <v>612</v>
       </c>
       <c r="C1257" t="n">
-        <v>0.127341</v>
+        <v>0.127351</v>
       </c>
     </row>
     <row r="1258">
@@ -16771,7 +16771,7 @@
         <v>613</v>
       </c>
       <c r="C1258" t="n">
-        <v>0.128279</v>
+        <v>0.128301</v>
       </c>
     </row>
     <row r="1259">
@@ -16784,7 +16784,7 @@
         <v>614</v>
       </c>
       <c r="C1259" t="n">
-        <v>0.130403</v>
+        <v>0.130473</v>
       </c>
     </row>
     <row r="1260">
@@ -16797,7 +16797,7 @@
         <v>615</v>
       </c>
       <c r="C1260" t="n">
-        <v>0.136657</v>
+        <v>0.136662</v>
       </c>
     </row>
     <row r="1261">
@@ -16810,7 +16810,7 @@
         <v>616</v>
       </c>
       <c r="C1261" t="n">
-        <v>0.138886</v>
+        <v>0.138887</v>
       </c>
     </row>
     <row r="1262">
@@ -16823,7 +16823,7 @@
         <v>617</v>
       </c>
       <c r="C1262" t="n">
-        <v>0.141838</v>
+        <v>0.141836</v>
       </c>
     </row>
     <row r="1263">
@@ -16836,7 +16836,7 @@
         <v>618</v>
       </c>
       <c r="C1263" t="n">
-        <v>0.14361</v>
+        <v>0.143616</v>
       </c>
     </row>
     <row r="1264">
@@ -16849,7 +16849,7 @@
         <v>619</v>
       </c>
       <c r="C1264" t="n">
-        <v>0.143743</v>
+        <v>0.143794</v>
       </c>
     </row>
     <row r="1265">
@@ -16862,7 +16862,7 @@
         <v>620</v>
       </c>
       <c r="C1265" t="n">
-        <v>0.152406</v>
+        <v>0.152424</v>
       </c>
     </row>
     <row r="1266">
@@ -16875,7 +16875,7 @@
         <v>621</v>
       </c>
       <c r="C1266" t="n">
-        <v>0.157475</v>
+        <v>0.157527</v>
       </c>
     </row>
     <row r="1267">
@@ -16888,7 +16888,7 @@
         <v>622</v>
       </c>
       <c r="C1267" t="n">
-        <v>0.160569</v>
+        <v>0.160567</v>
       </c>
     </row>
     <row r="1268">
@@ -16901,7 +16901,7 @@
         <v>623</v>
       </c>
       <c r="C1268" t="n">
-        <v>0.162333</v>
+        <v>0.162366</v>
       </c>
     </row>
     <row r="1269">
@@ -16914,7 +16914,7 @@
         <v>624</v>
       </c>
       <c r="C1269" t="n">
-        <v>0.163296</v>
+        <v>0.163329</v>
       </c>
     </row>
     <row r="1270">
@@ -16927,7 +16927,7 @@
         <v>625</v>
       </c>
       <c r="C1270" t="n">
-        <v>0.163831</v>
+        <v>0.164173</v>
       </c>
     </row>
     <row r="1271">
@@ -16940,7 +16940,7 @@
         <v>626</v>
       </c>
       <c r="C1271" t="n">
-        <v>0.167144</v>
+        <v>0.167141</v>
       </c>
     </row>
     <row r="1272">
@@ -16953,7 +16953,7 @@
         <v>627</v>
       </c>
       <c r="C1272" t="n">
-        <v>0.167394</v>
+        <v>0.167478</v>
       </c>
     </row>
     <row r="1273">
@@ -16979,7 +16979,7 @@
         <v>629</v>
       </c>
       <c r="C1274" t="n">
-        <v>0.168508</v>
+        <v>0.168657</v>
       </c>
     </row>
     <row r="1275">
@@ -16992,7 +16992,7 @@
         <v>630</v>
       </c>
       <c r="C1275" t="n">
-        <v>0.176925</v>
+        <v>0.176933</v>
       </c>
     </row>
     <row r="1276">
@@ -17005,7 +17005,7 @@
         <v>631</v>
       </c>
       <c r="C1276" t="n">
-        <v>0.177722</v>
+        <v>0.177857</v>
       </c>
     </row>
     <row r="1277">
@@ -17018,7 +17018,7 @@
         <v>632</v>
       </c>
       <c r="C1277" t="n">
-        <v>0.185227</v>
+        <v>0.185235</v>
       </c>
     </row>
     <row r="1278">
@@ -17031,7 +17031,7 @@
         <v>633</v>
       </c>
       <c r="C1278" t="n">
-        <v>0.22032</v>
+        <v>0.220319</v>
       </c>
     </row>
     <row r="1279">
@@ -17044,7 +17044,7 @@
         <v>634</v>
       </c>
       <c r="C1279" t="n">
-        <v>0.220321</v>
+        <v>0.220454</v>
       </c>
     </row>
     <row r="1280">
@@ -17057,7 +17057,7 @@
         <v>635</v>
       </c>
       <c r="C1280" t="n">
-        <v>0.234939</v>
+        <v>0.235207</v>
       </c>
     </row>
     <row r="1281">
@@ -17070,7 +17070,7 @@
         <v>636</v>
       </c>
       <c r="C1281" t="n">
-        <v>0.237935</v>
+        <v>0.23821</v>
       </c>
     </row>
     <row r="1282">
@@ -17083,7 +17083,7 @@
         <v>637</v>
       </c>
       <c r="C1282" t="n">
-        <v>0.241259</v>
+        <v>0.241696</v>
       </c>
     </row>
     <row r="1283">
@@ -17096,7 +17096,7 @@
         <v>638</v>
       </c>
       <c r="C1283" t="n">
-        <v>0.246236</v>
+        <v>0.246351</v>
       </c>
     </row>
     <row r="1284">
@@ -17109,7 +17109,7 @@
         <v>639</v>
       </c>
       <c r="C1284" t="n">
-        <v>0.297704</v>
+        <v>0.297977</v>
       </c>
     </row>
     <row r="1285">
@@ -17122,7 +17122,7 @@
         <v>640</v>
       </c>
       <c r="C1285" t="n">
-        <v>0.311319</v>
+        <v>0.311394</v>
       </c>
     </row>
     <row r="1286">
@@ -17135,7 +17135,7 @@
         <v>641</v>
       </c>
       <c r="C1286" t="n">
-        <v>0.323199</v>
+        <v>0.32341</v>
       </c>
     </row>
     <row r="1287">
@@ -17148,7 +17148,7 @@
         <v>642</v>
       </c>
       <c r="C1287" t="n">
-        <v>0.451949</v>
+        <v>0.452141</v>
       </c>
     </row>
     <row r="1288">
@@ -17161,7 +17161,7 @@
         <v>0</v>
       </c>
       <c r="C1288" t="n">
-        <v>-0.256965</v>
+        <v>-0.257151</v>
       </c>
     </row>
     <row r="1289">
@@ -17174,7 +17174,7 @@
         <v>1</v>
       </c>
       <c r="C1289" t="n">
-        <v>-0.162631</v>
+        <v>-0.162653</v>
       </c>
     </row>
     <row r="1290">
@@ -17187,7 +17187,7 @@
         <v>2</v>
       </c>
       <c r="C1290" t="n">
-        <v>-0.159561</v>
+        <v>-0.159558</v>
       </c>
     </row>
     <row r="1291">
@@ -17200,7 +17200,7 @@
         <v>3</v>
       </c>
       <c r="C1291" t="n">
-        <v>-0.134415</v>
+        <v>-0.134433</v>
       </c>
     </row>
     <row r="1292">
@@ -17213,7 +17213,7 @@
         <v>4</v>
       </c>
       <c r="C1292" t="n">
-        <v>-0.115851</v>
+        <v>-0.115881</v>
       </c>
     </row>
     <row r="1293">
@@ -17226,7 +17226,7 @@
         <v>5</v>
       </c>
       <c r="C1293" t="n">
-        <v>-0.111594</v>
+        <v>-0.111607</v>
       </c>
     </row>
     <row r="1294">
@@ -17239,7 +17239,7 @@
         <v>6</v>
       </c>
       <c r="C1294" t="n">
-        <v>-0.108984</v>
+        <v>-0.10898</v>
       </c>
     </row>
     <row r="1295">
@@ -17252,7 +17252,7 @@
         <v>7</v>
       </c>
       <c r="C1295" t="n">
-        <v>-0.105602</v>
+        <v>-0.105614</v>
       </c>
     </row>
     <row r="1296">
@@ -17265,7 +17265,7 @@
         <v>8</v>
       </c>
       <c r="C1296" t="n">
-        <v>-0.104797</v>
+        <v>-0.104796</v>
       </c>
     </row>
     <row r="1297">
@@ -17278,7 +17278,7 @@
         <v>9</v>
       </c>
       <c r="C1297" t="n">
-        <v>-0.101475</v>
+        <v>-0.101479</v>
       </c>
     </row>
     <row r="1298">
@@ -17291,7 +17291,7 @@
         <v>10</v>
       </c>
       <c r="C1298" t="n">
-        <v>-0.09939000000000001</v>
+        <v>-0.099387</v>
       </c>
     </row>
     <row r="1299">
@@ -17304,7 +17304,7 @@
         <v>11</v>
       </c>
       <c r="C1299" t="n">
-        <v>-0.098998</v>
+        <v>-0.098996</v>
       </c>
     </row>
     <row r="1300">
@@ -17317,7 +17317,7 @@
         <v>12</v>
       </c>
       <c r="C1300" t="n">
-        <v>-0.098727</v>
+        <v>-0.098733</v>
       </c>
     </row>
     <row r="1301">
@@ -17330,7 +17330,7 @@
         <v>13</v>
       </c>
       <c r="C1301" t="n">
-        <v>-0.097708</v>
+        <v>-0.09771199999999999</v>
       </c>
     </row>
     <row r="1302">
@@ -17343,7 +17343,7 @@
         <v>14</v>
       </c>
       <c r="C1302" t="n">
-        <v>-0.097396</v>
+        <v>-0.097395</v>
       </c>
     </row>
     <row r="1303">
@@ -17356,7 +17356,7 @@
         <v>15</v>
       </c>
       <c r="C1303" t="n">
-        <v>-0.09726700000000001</v>
+        <v>-0.097362</v>
       </c>
     </row>
     <row r="1304">
@@ -17369,7 +17369,7 @@
         <v>16</v>
       </c>
       <c r="C1304" t="n">
-        <v>-0.094736</v>
+        <v>-0.094762</v>
       </c>
     </row>
     <row r="1305">
@@ -17382,7 +17382,7 @@
         <v>17</v>
       </c>
       <c r="C1305" t="n">
-        <v>-0.09152299999999999</v>
+        <v>-0.09152</v>
       </c>
     </row>
     <row r="1306">
@@ -17395,7 +17395,7 @@
         <v>18</v>
       </c>
       <c r="C1306" t="n">
-        <v>-0.091518</v>
+        <v>-0.091517</v>
       </c>
     </row>
     <row r="1307">
@@ -17408,7 +17408,7 @@
         <v>19</v>
       </c>
       <c r="C1307" t="n">
-        <v>-0.09035799999999999</v>
+        <v>-0.09035700000000001</v>
       </c>
     </row>
     <row r="1308">
@@ -17421,7 +17421,7 @@
         <v>20</v>
       </c>
       <c r="C1308" t="n">
-        <v>-0.088988</v>
+        <v>-0.088989</v>
       </c>
     </row>
     <row r="1309">
@@ -17434,7 +17434,7 @@
         <v>21</v>
       </c>
       <c r="C1309" t="n">
-        <v>-0.088727</v>
+        <v>-0.088759</v>
       </c>
     </row>
     <row r="1310">
@@ -17447,7 +17447,7 @@
         <v>22</v>
       </c>
       <c r="C1310" t="n">
-        <v>-0.088617</v>
+        <v>-0.088614</v>
       </c>
     </row>
     <row r="1311">
@@ -17460,7 +17460,7 @@
         <v>23</v>
       </c>
       <c r="C1311" t="n">
-        <v>-0.087959</v>
+        <v>-0.08795799999999999</v>
       </c>
     </row>
     <row r="1312">
@@ -17473,7 +17473,7 @@
         <v>24</v>
       </c>
       <c r="C1312" t="n">
-        <v>-0.08647299999999999</v>
+        <v>-0.08656700000000001</v>
       </c>
     </row>
     <row r="1313">
@@ -17486,7 +17486,7 @@
         <v>25</v>
       </c>
       <c r="C1313" t="n">
-        <v>-0.08580500000000001</v>
+        <v>-0.08590100000000001</v>
       </c>
     </row>
     <row r="1314">
@@ -17499,7 +17499,7 @@
         <v>26</v>
       </c>
       <c r="C1314" t="n">
-        <v>-0.08514099999999999</v>
+        <v>-0.08513999999999999</v>
       </c>
     </row>
     <row r="1315">
@@ -17512,7 +17512,7 @@
         <v>27</v>
       </c>
       <c r="C1315" t="n">
-        <v>-0.08438900000000001</v>
+        <v>-0.08439099999999999</v>
       </c>
     </row>
     <row r="1316">
@@ -17525,7 +17525,7 @@
         <v>28</v>
       </c>
       <c r="C1316" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.08400299999999999</v>
       </c>
     </row>
     <row r="1317">
@@ -17538,7 +17538,7 @@
         <v>29</v>
       </c>
       <c r="C1317" t="n">
-        <v>-0.082264</v>
+        <v>-0.082358</v>
       </c>
     </row>
     <row r="1318">
@@ -17551,7 +17551,7 @@
         <v>30</v>
       </c>
       <c r="C1318" t="n">
-        <v>-0.08058899999999999</v>
+        <v>-0.08058700000000001</v>
       </c>
     </row>
     <row r="1319">
@@ -17564,7 +17564,7 @@
         <v>31</v>
       </c>
       <c r="C1319" t="n">
-        <v>-0.079926</v>
+        <v>-0.080015</v>
       </c>
     </row>
     <row r="1320">
@@ -17577,7 +17577,7 @@
         <v>32</v>
       </c>
       <c r="C1320" t="n">
-        <v>-0.078726</v>
+        <v>-0.07881299999999999</v>
       </c>
     </row>
     <row r="1321">
@@ -17590,7 +17590,7 @@
         <v>33</v>
       </c>
       <c r="C1321" t="n">
-        <v>-0.07849399999999999</v>
+        <v>-0.078496</v>
       </c>
     </row>
     <row r="1322">
@@ -17603,7 +17603,7 @@
         <v>34</v>
       </c>
       <c r="C1322" t="n">
-        <v>-0.075089</v>
+        <v>-0.075113</v>
       </c>
     </row>
     <row r="1323">
@@ -17616,7 +17616,7 @@
         <v>35</v>
       </c>
       <c r="C1323" t="n">
-        <v>-0.074721</v>
+        <v>-0.074754</v>
       </c>
     </row>
     <row r="1324">
@@ -17629,7 +17629,7 @@
         <v>36</v>
       </c>
       <c r="C1324" t="n">
-        <v>-0.07424</v>
+        <v>-0.07428</v>
       </c>
     </row>
     <row r="1325">
@@ -17642,7 +17642,7 @@
         <v>37</v>
       </c>
       <c r="C1325" t="n">
-        <v>-0.072893</v>
+        <v>-0.072926</v>
       </c>
     </row>
     <row r="1326">
@@ -17655,7 +17655,7 @@
         <v>38</v>
       </c>
       <c r="C1326" t="n">
-        <v>-0.070937</v>
+        <v>-0.070946</v>
       </c>
     </row>
     <row r="1327">
@@ -17668,7 +17668,7 @@
         <v>39</v>
       </c>
       <c r="C1327" t="n">
-        <v>-0.068485</v>
+        <v>-0.068483</v>
       </c>
     </row>
     <row r="1328">
@@ -17681,7 +17681,7 @@
         <v>40</v>
       </c>
       <c r="C1328" t="n">
-        <v>-0.068122</v>
+        <v>-0.068192</v>
       </c>
     </row>
     <row r="1329">
@@ -17707,7 +17707,7 @@
         <v>42</v>
       </c>
       <c r="C1330" t="n">
-        <v>-0.066084</v>
+        <v>-0.066109</v>
       </c>
     </row>
     <row r="1331">
@@ -17733,7 +17733,7 @@
         <v>44</v>
       </c>
       <c r="C1332" t="n">
-        <v>-0.06494999999999999</v>
+        <v>-0.064981</v>
       </c>
     </row>
     <row r="1333">
@@ -17746,7 +17746,7 @@
         <v>45</v>
       </c>
       <c r="C1333" t="n">
-        <v>-0.063471</v>
+        <v>-0.063473</v>
       </c>
     </row>
     <row r="1334">
@@ -17759,7 +17759,7 @@
         <v>46</v>
       </c>
       <c r="C1334" t="n">
-        <v>-0.063182</v>
+        <v>-0.063181</v>
       </c>
     </row>
     <row r="1335">
@@ -17772,7 +17772,7 @@
         <v>47</v>
       </c>
       <c r="C1335" t="n">
-        <v>-0.062865</v>
+        <v>-0.062863</v>
       </c>
     </row>
     <row r="1336">
@@ -17785,7 +17785,7 @@
         <v>48</v>
       </c>
       <c r="C1336" t="n">
-        <v>-0.06271599999999999</v>
+        <v>-0.062735</v>
       </c>
     </row>
     <row r="1337">
@@ -17798,7 +17798,7 @@
         <v>49</v>
       </c>
       <c r="C1337" t="n">
-        <v>-0.062668</v>
+        <v>-0.06271400000000001</v>
       </c>
     </row>
     <row r="1338">
@@ -17811,7 +17811,7 @@
         <v>50</v>
       </c>
       <c r="C1338" t="n">
-        <v>-0.061791</v>
+        <v>-0.061835</v>
       </c>
     </row>
     <row r="1339">
@@ -17824,7 +17824,7 @@
         <v>51</v>
       </c>
       <c r="C1339" t="n">
-        <v>-0.061</v>
+        <v>-0.061027</v>
       </c>
     </row>
     <row r="1340">
@@ -17837,7 +17837,7 @@
         <v>52</v>
       </c>
       <c r="C1340" t="n">
-        <v>-0.060548</v>
+        <v>-0.060671</v>
       </c>
     </row>
     <row r="1341">
@@ -17863,7 +17863,7 @@
         <v>54</v>
       </c>
       <c r="C1342" t="n">
-        <v>-0.059512</v>
+        <v>-0.059515</v>
       </c>
     </row>
     <row r="1343">
@@ -17876,7 +17876,7 @@
         <v>55</v>
       </c>
       <c r="C1343" t="n">
-        <v>-0.059182</v>
+        <v>-0.05919</v>
       </c>
     </row>
     <row r="1344">
@@ -17889,7 +17889,7 @@
         <v>56</v>
       </c>
       <c r="C1344" t="n">
-        <v>-0.058286</v>
+        <v>-0.058287</v>
       </c>
     </row>
     <row r="1345">
@@ -17902,7 +17902,7 @@
         <v>57</v>
       </c>
       <c r="C1345" t="n">
-        <v>-0.058119</v>
+        <v>-0.058127</v>
       </c>
     </row>
     <row r="1346">
@@ -17915,7 +17915,7 @@
         <v>58</v>
       </c>
       <c r="C1346" t="n">
-        <v>-0.057724</v>
+        <v>-0.057722</v>
       </c>
     </row>
     <row r="1347">
@@ -17928,7 +17928,7 @@
         <v>59</v>
       </c>
       <c r="C1347" t="n">
-        <v>-0.057124</v>
+        <v>-0.057125</v>
       </c>
     </row>
     <row r="1348">
@@ -17941,7 +17941,7 @@
         <v>60</v>
       </c>
       <c r="C1348" t="n">
-        <v>-0.056853</v>
+        <v>-0.056877</v>
       </c>
     </row>
     <row r="1349">
@@ -17954,7 +17954,7 @@
         <v>61</v>
       </c>
       <c r="C1349" t="n">
-        <v>-0.056659</v>
+        <v>-0.056663</v>
       </c>
     </row>
     <row r="1350">
@@ -17967,7 +17967,7 @@
         <v>62</v>
       </c>
       <c r="C1350" t="n">
-        <v>-0.056143</v>
+        <v>-0.056149</v>
       </c>
     </row>
     <row r="1351">
@@ -17980,7 +17980,7 @@
         <v>63</v>
       </c>
       <c r="C1351" t="n">
-        <v>-0.055994</v>
+        <v>-0.055993</v>
       </c>
     </row>
     <row r="1352">
@@ -17993,7 +17993,7 @@
         <v>64</v>
       </c>
       <c r="C1352" t="n">
-        <v>-0.055893</v>
+        <v>-0.055915</v>
       </c>
     </row>
     <row r="1353">
@@ -18006,7 +18006,7 @@
         <v>65</v>
       </c>
       <c r="C1353" t="n">
-        <v>-0.054319</v>
+        <v>-0.054317</v>
       </c>
     </row>
     <row r="1354">
@@ -18019,7 +18019,7 @@
         <v>66</v>
       </c>
       <c r="C1354" t="n">
-        <v>-0.05356</v>
+        <v>-0.053558</v>
       </c>
     </row>
     <row r="1355">
@@ -18032,7 +18032,7 @@
         <v>67</v>
       </c>
       <c r="C1355" t="n">
-        <v>-0.052581</v>
+        <v>-0.05258</v>
       </c>
     </row>
     <row r="1356">
@@ -18045,7 +18045,7 @@
         <v>68</v>
       </c>
       <c r="C1356" t="n">
-        <v>-0.051908</v>
+        <v>-0.05194</v>
       </c>
     </row>
     <row r="1357">
@@ -18058,7 +18058,7 @@
         <v>69</v>
       </c>
       <c r="C1357" t="n">
-        <v>-0.05163</v>
+        <v>-0.051629</v>
       </c>
     </row>
     <row r="1358">
@@ -18071,7 +18071,7 @@
         <v>70</v>
       </c>
       <c r="C1358" t="n">
-        <v>-0.051501</v>
+        <v>-0.051513</v>
       </c>
     </row>
     <row r="1359">
@@ -18084,7 +18084,7 @@
         <v>71</v>
       </c>
       <c r="C1359" t="n">
-        <v>-0.051437</v>
+        <v>-0.051456</v>
       </c>
     </row>
     <row r="1360">
@@ -18110,7 +18110,7 @@
         <v>73</v>
       </c>
       <c r="C1361" t="n">
-        <v>-0.050315</v>
+        <v>-0.050326</v>
       </c>
     </row>
     <row r="1362">
@@ -18123,7 +18123,7 @@
         <v>74</v>
       </c>
       <c r="C1362" t="n">
-        <v>-0.049775</v>
+        <v>-0.049777</v>
       </c>
     </row>
     <row r="1363">
@@ -18136,7 +18136,7 @@
         <v>75</v>
       </c>
       <c r="C1363" t="n">
-        <v>-0.049578</v>
+        <v>-0.04959</v>
       </c>
     </row>
     <row r="1364">
@@ -18149,7 +18149,7 @@
         <v>76</v>
       </c>
       <c r="C1364" t="n">
-        <v>-0.049574</v>
+        <v>-0.049573</v>
       </c>
     </row>
     <row r="1365">
@@ -18162,7 +18162,7 @@
         <v>77</v>
       </c>
       <c r="C1365" t="n">
-        <v>-0.049229</v>
+        <v>-0.049228</v>
       </c>
     </row>
     <row r="1366">
@@ -18175,7 +18175,7 @@
         <v>78</v>
       </c>
       <c r="C1366" t="n">
-        <v>-0.048909</v>
+        <v>-0.048937</v>
       </c>
     </row>
     <row r="1367">
@@ -18188,7 +18188,7 @@
         <v>79</v>
       </c>
       <c r="C1367" t="n">
-        <v>-0.048477</v>
+        <v>-0.048508</v>
       </c>
     </row>
     <row r="1368">
@@ -18201,7 +18201,7 @@
         <v>80</v>
       </c>
       <c r="C1368" t="n">
-        <v>-0.048307</v>
+        <v>-0.048324</v>
       </c>
     </row>
     <row r="1369">
@@ -18214,7 +18214,7 @@
         <v>81</v>
       </c>
       <c r="C1369" t="n">
-        <v>-0.04798</v>
+        <v>-0.047978</v>
       </c>
     </row>
     <row r="1370">
@@ -18240,7 +18240,7 @@
         <v>83</v>
       </c>
       <c r="C1371" t="n">
-        <v>-0.047852</v>
+        <v>-0.04785</v>
       </c>
     </row>
     <row r="1372">
@@ -18253,7 +18253,7 @@
         <v>84</v>
       </c>
       <c r="C1372" t="n">
-        <v>-0.047724</v>
+        <v>-0.047745</v>
       </c>
     </row>
     <row r="1373">
@@ -18266,7 +18266,7 @@
         <v>85</v>
       </c>
       <c r="C1373" t="n">
-        <v>-0.047462</v>
+        <v>-0.04746</v>
       </c>
     </row>
     <row r="1374">
@@ -18279,7 +18279,7 @@
         <v>86</v>
       </c>
       <c r="C1374" t="n">
-        <v>-0.046897</v>
+        <v>-0.046943</v>
       </c>
     </row>
     <row r="1375">
@@ -18292,7 +18292,7 @@
         <v>87</v>
       </c>
       <c r="C1375" t="n">
-        <v>-0.046444</v>
+        <v>-0.046453</v>
       </c>
     </row>
     <row r="1376">
@@ -18318,7 +18318,7 @@
         <v>89</v>
       </c>
       <c r="C1377" t="n">
-        <v>-0.04596</v>
+        <v>-0.04603</v>
       </c>
     </row>
     <row r="1378">
@@ -18331,7 +18331,7 @@
         <v>90</v>
       </c>
       <c r="C1378" t="n">
-        <v>-0.045796</v>
+        <v>-0.045798</v>
       </c>
     </row>
     <row r="1379">
@@ -18344,7 +18344,7 @@
         <v>91</v>
       </c>
       <c r="C1379" t="n">
-        <v>-0.045412</v>
+        <v>-0.045417</v>
       </c>
     </row>
     <row r="1380">
@@ -18357,7 +18357,7 @@
         <v>92</v>
       </c>
       <c r="C1380" t="n">
-        <v>-0.045284</v>
+        <v>-0.045295</v>
       </c>
     </row>
     <row r="1381">
@@ -18383,7 +18383,7 @@
         <v>94</v>
       </c>
       <c r="C1382" t="n">
-        <v>-0.044607</v>
+        <v>-0.044617</v>
       </c>
     </row>
     <row r="1383">
@@ -18396,7 +18396,7 @@
         <v>95</v>
       </c>
       <c r="C1383" t="n">
-        <v>-0.044045</v>
+        <v>-0.044055</v>
       </c>
     </row>
     <row r="1384">
@@ -18409,7 +18409,7 @@
         <v>96</v>
       </c>
       <c r="C1384" t="n">
-        <v>-0.043967</v>
+        <v>-0.044019</v>
       </c>
     </row>
     <row r="1385">
@@ -18422,7 +18422,7 @@
         <v>97</v>
       </c>
       <c r="C1385" t="n">
-        <v>-0.043921</v>
+        <v>-0.043929</v>
       </c>
     </row>
     <row r="1386">
@@ -18435,7 +18435,7 @@
         <v>98</v>
       </c>
       <c r="C1386" t="n">
-        <v>-0.042905</v>
+        <v>-0.042941</v>
       </c>
     </row>
     <row r="1387">
@@ -18448,7 +18448,7 @@
         <v>99</v>
       </c>
       <c r="C1387" t="n">
-        <v>-0.042822</v>
+        <v>-0.042821</v>
       </c>
     </row>
     <row r="1388">
@@ -18461,7 +18461,7 @@
         <v>100</v>
       </c>
       <c r="C1388" t="n">
-        <v>-0.042664</v>
+        <v>-0.042666</v>
       </c>
     </row>
     <row r="1389">
@@ -18474,7 +18474,7 @@
         <v>101</v>
       </c>
       <c r="C1389" t="n">
-        <v>-0.042651</v>
+        <v>-0.042656</v>
       </c>
     </row>
     <row r="1390">
@@ -18487,7 +18487,7 @@
         <v>102</v>
       </c>
       <c r="C1390" t="n">
-        <v>-0.042621</v>
+        <v>-0.04262</v>
       </c>
     </row>
     <row r="1391">
@@ -18500,7 +18500,7 @@
         <v>103</v>
       </c>
       <c r="C1391" t="n">
-        <v>-0.042389</v>
+        <v>-0.04242</v>
       </c>
     </row>
     <row r="1392">
@@ -18513,7 +18513,7 @@
         <v>104</v>
       </c>
       <c r="C1392" t="n">
-        <v>-0.041712</v>
+        <v>-0.041721</v>
       </c>
     </row>
     <row r="1393">
@@ -18526,7 +18526,7 @@
         <v>105</v>
       </c>
       <c r="C1393" t="n">
-        <v>-0.041495</v>
+        <v>-0.041504</v>
       </c>
     </row>
     <row r="1394">
@@ -18539,7 +18539,7 @@
         <v>106</v>
       </c>
       <c r="C1394" t="n">
-        <v>-0.041424</v>
+        <v>-0.041423</v>
       </c>
     </row>
     <row r="1395">
@@ -18552,7 +18552,7 @@
         <v>107</v>
       </c>
       <c r="C1395" t="n">
-        <v>-0.041279</v>
+        <v>-0.041277</v>
       </c>
     </row>
     <row r="1396">
@@ -18565,7 +18565,7 @@
         <v>108</v>
       </c>
       <c r="C1396" t="n">
-        <v>-0.041186</v>
+        <v>-0.041187</v>
       </c>
     </row>
     <row r="1397">
@@ -18591,7 +18591,7 @@
         <v>110</v>
       </c>
       <c r="C1398" t="n">
-        <v>-0.037551</v>
+        <v>-0.037554</v>
       </c>
     </row>
     <row r="1399">
@@ -18604,7 +18604,7 @@
         <v>111</v>
       </c>
       <c r="C1399" t="n">
-        <v>-0.037549</v>
+        <v>-0.037547</v>
       </c>
     </row>
     <row r="1400">
@@ -18617,7 +18617,7 @@
         <v>112</v>
       </c>
       <c r="C1400" t="n">
-        <v>-0.037387</v>
+        <v>-0.037388</v>
       </c>
     </row>
     <row r="1401">
@@ -18630,7 +18630,7 @@
         <v>113</v>
       </c>
       <c r="C1401" t="n">
-        <v>-0.036059</v>
+        <v>-0.036058</v>
       </c>
     </row>
     <row r="1402">
@@ -18643,7 +18643,7 @@
         <v>114</v>
       </c>
       <c r="C1402" t="n">
-        <v>-0.03593</v>
+        <v>-0.035979</v>
       </c>
     </row>
     <row r="1403">
@@ -18656,7 +18656,7 @@
         <v>115</v>
       </c>
       <c r="C1403" t="n">
-        <v>-0.035613</v>
+        <v>-0.03562</v>
       </c>
     </row>
     <row r="1404">
@@ -18669,7 +18669,7 @@
         <v>116</v>
       </c>
       <c r="C1404" t="n">
-        <v>-0.035446</v>
+        <v>-0.035445</v>
       </c>
     </row>
     <row r="1405">
@@ -18682,7 +18682,7 @@
         <v>117</v>
       </c>
       <c r="C1405" t="n">
-        <v>-0.035022</v>
+        <v>-0.035035</v>
       </c>
     </row>
     <row r="1406">
@@ -18695,7 +18695,7 @@
         <v>118</v>
       </c>
       <c r="C1406" t="n">
-        <v>-0.034077</v>
+        <v>-0.034076</v>
       </c>
     </row>
     <row r="1407">
@@ -18708,7 +18708,7 @@
         <v>119</v>
       </c>
       <c r="C1407" t="n">
-        <v>-0.034036</v>
+        <v>-0.034065</v>
       </c>
     </row>
     <row r="1408">
@@ -18721,7 +18721,7 @@
         <v>120</v>
       </c>
       <c r="C1408" t="n">
-        <v>-0.03403</v>
+        <v>-0.034051</v>
       </c>
     </row>
     <row r="1409">
@@ -18734,7 +18734,7 @@
         <v>121</v>
       </c>
       <c r="C1409" t="n">
-        <v>-0.033881</v>
+        <v>-0.033902</v>
       </c>
     </row>
     <row r="1410">
@@ -18747,7 +18747,7 @@
         <v>122</v>
       </c>
       <c r="C1410" t="n">
-        <v>-0.033034</v>
+        <v>-0.033038</v>
       </c>
     </row>
     <row r="1411">
@@ -18760,7 +18760,7 @@
         <v>123</v>
       </c>
       <c r="C1411" t="n">
-        <v>-0.031986</v>
+        <v>-0.031996</v>
       </c>
     </row>
     <row r="1412">
@@ -18773,7 +18773,7 @@
         <v>124</v>
       </c>
       <c r="C1412" t="n">
-        <v>-0.03178</v>
+        <v>-0.031817</v>
       </c>
     </row>
     <row r="1413">
@@ -18786,7 +18786,7 @@
         <v>125</v>
       </c>
       <c r="C1413" t="n">
-        <v>-0.031628</v>
+        <v>-0.031661</v>
       </c>
     </row>
     <row r="1414">
@@ -18799,7 +18799,7 @@
         <v>126</v>
       </c>
       <c r="C1414" t="n">
-        <v>-0.031597</v>
+        <v>-0.031596</v>
       </c>
     </row>
     <row r="1415">
@@ -18812,7 +18812,7 @@
         <v>127</v>
       </c>
       <c r="C1415" t="n">
-        <v>-0.03079</v>
+        <v>-0.030799</v>
       </c>
     </row>
     <row r="1416">
@@ -18825,7 +18825,7 @@
         <v>128</v>
       </c>
       <c r="C1416" t="n">
-        <v>-0.030158</v>
+        <v>-0.030211</v>
       </c>
     </row>
     <row r="1417">
@@ -18838,7 +18838,7 @@
         <v>129</v>
       </c>
       <c r="C1417" t="n">
-        <v>-0.030135</v>
+        <v>-0.030134</v>
       </c>
     </row>
     <row r="1418">
@@ -18851,7 +18851,7 @@
         <v>130</v>
       </c>
       <c r="C1418" t="n">
-        <v>-0.029992</v>
+        <v>-0.029995</v>
       </c>
     </row>
     <row r="1419">
@@ -18864,7 +18864,7 @@
         <v>131</v>
       </c>
       <c r="C1419" t="n">
-        <v>-0.029704</v>
+        <v>-0.02971</v>
       </c>
     </row>
     <row r="1420">
@@ -18877,7 +18877,7 @@
         <v>132</v>
       </c>
       <c r="C1420" t="n">
-        <v>-0.029224</v>
+        <v>-0.029286</v>
       </c>
     </row>
     <row r="1421">
@@ -18890,7 +18890,7 @@
         <v>133</v>
       </c>
       <c r="C1421" t="n">
-        <v>-0.02863</v>
+        <v>-0.028649</v>
       </c>
     </row>
     <row r="1422">
@@ -18903,7 +18903,7 @@
         <v>134</v>
       </c>
       <c r="C1422" t="n">
-        <v>-0.028077</v>
+        <v>-0.028079</v>
       </c>
     </row>
     <row r="1423">
@@ -18916,7 +18916,7 @@
         <v>135</v>
       </c>
       <c r="C1423" t="n">
-        <v>-0.028058</v>
+        <v>-0.02806</v>
       </c>
     </row>
     <row r="1424">
@@ -18929,7 +18929,7 @@
         <v>136</v>
       </c>
       <c r="C1424" t="n">
-        <v>-0.027501</v>
+        <v>-0.027504</v>
       </c>
     </row>
     <row r="1425">
@@ -18942,7 +18942,7 @@
         <v>137</v>
       </c>
       <c r="C1425" t="n">
-        <v>-0.027214</v>
+        <v>-0.027228</v>
       </c>
     </row>
     <row r="1426">
@@ -18955,7 +18955,7 @@
         <v>138</v>
       </c>
       <c r="C1426" t="n">
-        <v>-0.026914</v>
+        <v>-0.026918</v>
       </c>
     </row>
     <row r="1427">
@@ -19007,7 +19007,7 @@
         <v>142</v>
       </c>
       <c r="C1430" t="n">
-        <v>-0.026209</v>
+        <v>-0.026208</v>
       </c>
     </row>
     <row r="1431">
@@ -19020,7 +19020,7 @@
         <v>143</v>
       </c>
       <c r="C1431" t="n">
-        <v>-0.025834</v>
+        <v>-0.025848</v>
       </c>
     </row>
     <row r="1432">
@@ -19033,7 +19033,7 @@
         <v>144</v>
       </c>
       <c r="C1432" t="n">
-        <v>-0.025788</v>
+        <v>-0.02579</v>
       </c>
     </row>
     <row r="1433">
@@ -19046,7 +19046,7 @@
         <v>145</v>
       </c>
       <c r="C1433" t="n">
-        <v>-0.024903</v>
+        <v>-0.024902</v>
       </c>
     </row>
     <row r="1434">
@@ -19072,7 +19072,7 @@
         <v>147</v>
       </c>
       <c r="C1435" t="n">
-        <v>-0.023794</v>
+        <v>-0.023793</v>
       </c>
     </row>
     <row r="1436">
@@ -19085,7 +19085,7 @@
         <v>148</v>
       </c>
       <c r="C1436" t="n">
-        <v>-0.02369</v>
+        <v>-0.023693</v>
       </c>
     </row>
     <row r="1437">
@@ -19111,7 +19111,7 @@
         <v>150</v>
       </c>
       <c r="C1438" t="n">
-        <v>-0.022588</v>
+        <v>-0.022589</v>
       </c>
     </row>
     <row r="1439">
@@ -19124,7 +19124,7 @@
         <v>151</v>
       </c>
       <c r="C1439" t="n">
-        <v>-0.022436</v>
+        <v>-0.022443</v>
       </c>
     </row>
     <row r="1440">
@@ -19137,7 +19137,7 @@
         <v>152</v>
       </c>
       <c r="C1440" t="n">
-        <v>-0.022433</v>
+        <v>-0.022432</v>
       </c>
     </row>
     <row r="1441">
@@ -19150,7 +19150,7 @@
         <v>153</v>
       </c>
       <c r="C1441" t="n">
-        <v>-0.022184</v>
+        <v>-0.022191</v>
       </c>
     </row>
     <row r="1442">
@@ -19163,7 +19163,7 @@
         <v>154</v>
       </c>
       <c r="C1442" t="n">
-        <v>-0.022052</v>
+        <v>-0.022057</v>
       </c>
     </row>
     <row r="1443">
@@ -19176,7 +19176,7 @@
         <v>155</v>
       </c>
       <c r="C1443" t="n">
-        <v>-0.020651</v>
+        <v>-0.020659</v>
       </c>
     </row>
     <row r="1444">
@@ -19189,7 +19189,7 @@
         <v>156</v>
       </c>
       <c r="C1444" t="n">
-        <v>-0.020579</v>
+        <v>-0.02058</v>
       </c>
     </row>
     <row r="1445">
@@ -19215,7 +19215,7 @@
         <v>158</v>
       </c>
       <c r="C1446" t="n">
-        <v>-0.020374</v>
+        <v>-0.020381</v>
       </c>
     </row>
     <row r="1447">
@@ -19228,7 +19228,7 @@
         <v>159</v>
       </c>
       <c r="C1447" t="n">
-        <v>-0.020107</v>
+        <v>-0.020108</v>
       </c>
     </row>
     <row r="1448">
@@ -19241,7 +19241,7 @@
         <v>160</v>
       </c>
       <c r="C1448" t="n">
-        <v>-0.019637</v>
+        <v>-0.019636</v>
       </c>
     </row>
     <row r="1449">
@@ -19254,7 +19254,7 @@
         <v>161</v>
       </c>
       <c r="C1449" t="n">
-        <v>-0.019492</v>
+        <v>-0.019491</v>
       </c>
     </row>
     <row r="1450">
@@ -19267,7 +19267,7 @@
         <v>162</v>
       </c>
       <c r="C1450" t="n">
-        <v>-0.019279</v>
+        <v>-0.019311</v>
       </c>
     </row>
     <row r="1451">
@@ -19293,7 +19293,7 @@
         <v>164</v>
       </c>
       <c r="C1452" t="n">
-        <v>-0.018649</v>
+        <v>-0.018648</v>
       </c>
     </row>
     <row r="1453">
@@ -19332,7 +19332,7 @@
         <v>167</v>
       </c>
       <c r="C1455" t="n">
-        <v>-0.018118</v>
+        <v>-0.018122</v>
       </c>
     </row>
     <row r="1456">
@@ -19345,7 +19345,7 @@
         <v>168</v>
       </c>
       <c r="C1456" t="n">
-        <v>-0.018018</v>
+        <v>-0.018023</v>
       </c>
     </row>
     <row r="1457">
@@ -19358,7 +19358,7 @@
         <v>169</v>
       </c>
       <c r="C1457" t="n">
-        <v>-0.017968</v>
+        <v>-0.017969</v>
       </c>
     </row>
     <row r="1458">
@@ -19371,7 +19371,7 @@
         <v>170</v>
       </c>
       <c r="C1458" t="n">
-        <v>-0.01763</v>
+        <v>-0.017629</v>
       </c>
     </row>
     <row r="1459">
@@ -19410,7 +19410,7 @@
         <v>173</v>
       </c>
       <c r="C1461" t="n">
-        <v>-0.017156</v>
+        <v>-0.017159</v>
       </c>
     </row>
     <row r="1462">
@@ -19423,7 +19423,7 @@
         <v>174</v>
       </c>
       <c r="C1462" t="n">
-        <v>-0.016802</v>
+        <v>-0.016804</v>
       </c>
     </row>
     <row r="1463">
@@ -19436,7 +19436,7 @@
         <v>175</v>
       </c>
       <c r="C1463" t="n">
-        <v>-0.016687</v>
+        <v>-0.016686</v>
       </c>
     </row>
     <row r="1464">
@@ -19449,7 +19449,7 @@
         <v>176</v>
       </c>
       <c r="C1464" t="n">
-        <v>-0.016658</v>
+        <v>-0.016657</v>
       </c>
     </row>
     <row r="1465">
@@ -19462,7 +19462,7 @@
         <v>177</v>
       </c>
       <c r="C1465" t="n">
-        <v>-0.016222</v>
+        <v>-0.016226</v>
       </c>
     </row>
     <row r="1466">
@@ -19475,7 +19475,7 @@
         <v>178</v>
       </c>
       <c r="C1466" t="n">
-        <v>-0.016129</v>
+        <v>-0.01613</v>
       </c>
     </row>
     <row r="1467">
@@ -19488,7 +19488,7 @@
         <v>179</v>
       </c>
       <c r="C1467" t="n">
-        <v>-0.016054</v>
+        <v>-0.016067</v>
       </c>
     </row>
     <row r="1468">
@@ -19501,7 +19501,7 @@
         <v>180</v>
       </c>
       <c r="C1468" t="n">
-        <v>-0.015642</v>
+        <v>-0.015645</v>
       </c>
     </row>
     <row r="1469">
@@ -19527,7 +19527,7 @@
         <v>182</v>
       </c>
       <c r="C1470" t="n">
-        <v>-0.014012</v>
+        <v>-0.014011</v>
       </c>
     </row>
     <row r="1471">
@@ -19540,7 +19540,7 @@
         <v>183</v>
       </c>
       <c r="C1471" t="n">
-        <v>-0.013962</v>
+        <v>-0.013977</v>
       </c>
     </row>
     <row r="1472">
@@ -19553,7 +19553,7 @@
         <v>184</v>
       </c>
       <c r="C1472" t="n">
-        <v>-0.013764</v>
+        <v>-0.013776</v>
       </c>
     </row>
     <row r="1473">
@@ -19566,7 +19566,7 @@
         <v>185</v>
       </c>
       <c r="C1473" t="n">
-        <v>-0.012975</v>
+        <v>-0.01298</v>
       </c>
     </row>
     <row r="1474">
@@ -19579,7 +19579,7 @@
         <v>186</v>
       </c>
       <c r="C1474" t="n">
-        <v>-0.012874</v>
+        <v>-0.012879</v>
       </c>
     </row>
     <row r="1475">
@@ -19618,7 +19618,7 @@
         <v>189</v>
       </c>
       <c r="C1477" t="n">
-        <v>-0.012132</v>
+        <v>-0.012131</v>
       </c>
     </row>
     <row r="1478">
@@ -19631,7 +19631,7 @@
         <v>190</v>
       </c>
       <c r="C1478" t="n">
-        <v>-0.011761</v>
+        <v>-0.011763</v>
       </c>
     </row>
     <row r="1479">
@@ -19657,7 +19657,7 @@
         <v>192</v>
       </c>
       <c r="C1480" t="n">
-        <v>-0.01142</v>
+        <v>-0.011422</v>
       </c>
     </row>
     <row r="1481">
@@ -19670,7 +19670,7 @@
         <v>193</v>
       </c>
       <c r="C1481" t="n">
-        <v>-0.011396</v>
+        <v>-0.011398</v>
       </c>
     </row>
     <row r="1482">
@@ -19683,7 +19683,7 @@
         <v>194</v>
       </c>
       <c r="C1482" t="n">
-        <v>-0.01124</v>
+        <v>-0.011243</v>
       </c>
     </row>
     <row r="1483">
@@ -19696,7 +19696,7 @@
         <v>195</v>
       </c>
       <c r="C1483" t="n">
-        <v>-0.01104</v>
+        <v>-0.011047</v>
       </c>
     </row>
     <row r="1484">
@@ -19709,7 +19709,7 @@
         <v>196</v>
       </c>
       <c r="C1484" t="n">
-        <v>-0.010948</v>
+        <v>-0.010963</v>
       </c>
     </row>
     <row r="1485">
@@ -19722,7 +19722,7 @@
         <v>197</v>
       </c>
       <c r="C1485" t="n">
-        <v>-0.010742</v>
+        <v>-0.010749</v>
       </c>
     </row>
     <row r="1486">
@@ -19748,7 +19748,7 @@
         <v>199</v>
       </c>
       <c r="C1487" t="n">
-        <v>-0.009887</v>
+        <v>-0.009889</v>
       </c>
     </row>
     <row r="1488">
@@ -19774,7 +19774,7 @@
         <v>201</v>
       </c>
       <c r="C1489" t="n">
-        <v>-0.009035</v>
+        <v>-0.009051</v>
       </c>
     </row>
     <row r="1490">
@@ -19800,7 +19800,7 @@
         <v>203</v>
       </c>
       <c r="C1491" t="n">
-        <v>-0.008560999999999999</v>
+        <v>-0.008564</v>
       </c>
     </row>
     <row r="1492">
@@ -19813,7 +19813,7 @@
         <v>204</v>
       </c>
       <c r="C1492" t="n">
-        <v>-0.008528000000000001</v>
+        <v>-0.008531</v>
       </c>
     </row>
     <row r="1493">
@@ -19826,7 +19826,7 @@
         <v>205</v>
       </c>
       <c r="C1493" t="n">
-        <v>-0.008302</v>
+        <v>-0.008303</v>
       </c>
     </row>
     <row r="1494">
@@ -19865,7 +19865,7 @@
         <v>208</v>
       </c>
       <c r="C1496" t="n">
-        <v>-0.007393</v>
+        <v>-0.007396</v>
       </c>
     </row>
     <row r="1497">
@@ -19878,7 +19878,7 @@
         <v>209</v>
       </c>
       <c r="C1497" t="n">
-        <v>-0.007312</v>
+        <v>-0.007313</v>
       </c>
     </row>
     <row r="1498">
@@ -19891,7 +19891,7 @@
         <v>210</v>
       </c>
       <c r="C1498" t="n">
-        <v>-0.006949</v>
+        <v>-0.00695</v>
       </c>
     </row>
     <row r="1499">
@@ -19917,7 +19917,7 @@
         <v>212</v>
       </c>
       <c r="C1500" t="n">
-        <v>-0.006699</v>
+        <v>-0.006702</v>
       </c>
     </row>
     <row r="1501">
@@ -19930,7 +19930,7 @@
         <v>213</v>
       </c>
       <c r="C1501" t="n">
-        <v>-0.006589</v>
+        <v>-0.006591</v>
       </c>
     </row>
     <row r="1502">
@@ -19943,7 +19943,7 @@
         <v>214</v>
       </c>
       <c r="C1502" t="n">
-        <v>-0.006481</v>
+        <v>-0.006482</v>
       </c>
     </row>
     <row r="1503">
@@ -19956,7 +19956,7 @@
         <v>215</v>
       </c>
       <c r="C1503" t="n">
-        <v>-0.006014</v>
+        <v>-0.006022</v>
       </c>
     </row>
     <row r="1504">
@@ -19995,7 +19995,7 @@
         <v>218</v>
       </c>
       <c r="C1506" t="n">
-        <v>-0.005346</v>
+        <v>-0.005351</v>
       </c>
     </row>
     <row r="1507">
@@ -20008,7 +20008,7 @@
         <v>219</v>
       </c>
       <c r="C1507" t="n">
-        <v>-0.005296</v>
+        <v>-0.005297</v>
       </c>
     </row>
     <row r="1508">
@@ -20021,7 +20021,7 @@
         <v>220</v>
       </c>
       <c r="C1508" t="n">
-        <v>-0.005249</v>
+        <v>-0.00525</v>
       </c>
     </row>
     <row r="1509">
@@ -20047,7 +20047,7 @@
         <v>222</v>
       </c>
       <c r="C1510" t="n">
-        <v>-0.004497</v>
+        <v>-0.004499</v>
       </c>
     </row>
     <row r="1511">
@@ -20073,7 +20073,7 @@
         <v>224</v>
       </c>
       <c r="C1512" t="n">
-        <v>-0.004271</v>
+        <v>-0.004273</v>
       </c>
     </row>
     <row r="1513">
@@ -20086,7 +20086,7 @@
         <v>225</v>
       </c>
       <c r="C1513" t="n">
-        <v>-0.003988</v>
+        <v>-0.003989</v>
       </c>
     </row>
     <row r="1514">
@@ -20099,7 +20099,7 @@
         <v>226</v>
       </c>
       <c r="C1514" t="n">
-        <v>-0.003985</v>
+        <v>-0.003988</v>
       </c>
     </row>
     <row r="1515">
@@ -20112,7 +20112,7 @@
         <v>227</v>
       </c>
       <c r="C1515" t="n">
-        <v>-0.003957</v>
+        <v>-0.003958</v>
       </c>
     </row>
     <row r="1516">
@@ -20125,7 +20125,7 @@
         <v>228</v>
       </c>
       <c r="C1516" t="n">
-        <v>-0.00393</v>
+        <v>-0.003932</v>
       </c>
     </row>
     <row r="1517">
@@ -20138,7 +20138,7 @@
         <v>229</v>
       </c>
       <c r="C1517" t="n">
-        <v>-0.003825</v>
+        <v>-0.003826</v>
       </c>
     </row>
     <row r="1518">
@@ -20151,7 +20151,7 @@
         <v>230</v>
       </c>
       <c r="C1518" t="n">
-        <v>-0.003567</v>
+        <v>-0.003571</v>
       </c>
     </row>
     <row r="1519">
@@ -20164,7 +20164,7 @@
         <v>231</v>
       </c>
       <c r="C1519" t="n">
-        <v>-0.003066</v>
+        <v>-0.003067</v>
       </c>
     </row>
     <row r="1520">
@@ -20203,7 +20203,7 @@
         <v>234</v>
       </c>
       <c r="C1522" t="n">
-        <v>-0.002579</v>
+        <v>-0.002582</v>
       </c>
     </row>
     <row r="1523">
@@ -20242,7 +20242,7 @@
         <v>237</v>
       </c>
       <c r="C1525" t="n">
-        <v>-0.002086</v>
+        <v>-0.002091</v>
       </c>
     </row>
     <row r="1526">
@@ -20268,7 +20268,7 @@
         <v>239</v>
       </c>
       <c r="C1527" t="n">
-        <v>-0.001631</v>
+        <v>-0.001634</v>
       </c>
     </row>
     <row r="1528">
@@ -20307,7 +20307,7 @@
         <v>242</v>
       </c>
       <c r="C1530" t="n">
-        <v>-0.001437</v>
+        <v>-0.001438</v>
       </c>
     </row>
     <row r="1531">
@@ -20320,7 +20320,7 @@
         <v>243</v>
       </c>
       <c r="C1531" t="n">
-        <v>-0.001298</v>
+        <v>-0.001301</v>
       </c>
     </row>
     <row r="1532">
@@ -20463,7 +20463,7 @@
         <v>254</v>
       </c>
       <c r="C1542" t="n">
-        <v>0.001741</v>
+        <v>0.001742</v>
       </c>
     </row>
     <row r="1543">
@@ -20515,7 +20515,7 @@
         <v>258</v>
       </c>
       <c r="C1546" t="n">
-        <v>0.002384</v>
+        <v>0.002386</v>
       </c>
     </row>
     <row r="1547">
@@ -20528,7 +20528,7 @@
         <v>259</v>
       </c>
       <c r="C1547" t="n">
-        <v>0.002451</v>
+        <v>0.002453</v>
       </c>
     </row>
     <row r="1548">
@@ -20554,7 +20554,7 @@
         <v>261</v>
       </c>
       <c r="C1549" t="n">
-        <v>0.002682</v>
+        <v>0.002681</v>
       </c>
     </row>
     <row r="1550">
@@ -20567,7 +20567,7 @@
         <v>262</v>
       </c>
       <c r="C1550" t="n">
-        <v>0.003016</v>
+        <v>0.003017</v>
       </c>
     </row>
     <row r="1551">
@@ -20580,7 +20580,7 @@
         <v>263</v>
       </c>
       <c r="C1551" t="n">
-        <v>0.003162</v>
+        <v>0.003164</v>
       </c>
     </row>
     <row r="1552">
@@ -20606,7 +20606,7 @@
         <v>265</v>
       </c>
       <c r="C1553" t="n">
-        <v>0.00368</v>
+        <v>0.003683</v>
       </c>
     </row>
     <row r="1554">
@@ -20632,7 +20632,7 @@
         <v>267</v>
       </c>
       <c r="C1555" t="n">
-        <v>0.004318</v>
+        <v>0.004319</v>
       </c>
     </row>
     <row r="1556">
@@ -20671,7 +20671,7 @@
         <v>270</v>
       </c>
       <c r="C1558" t="n">
-        <v>0.004754</v>
+        <v>0.004753</v>
       </c>
     </row>
     <row r="1559">
@@ -20697,7 +20697,7 @@
         <v>272</v>
       </c>
       <c r="C1560" t="n">
-        <v>0.004912</v>
+        <v>0.004913</v>
       </c>
     </row>
     <row r="1561">
@@ -20723,7 +20723,7 @@
         <v>274</v>
       </c>
       <c r="C1562" t="n">
-        <v>0.0053</v>
+        <v>0.005309</v>
       </c>
     </row>
     <row r="1563">
@@ -20736,7 +20736,7 @@
         <v>275</v>
       </c>
       <c r="C1563" t="n">
-        <v>0.005322</v>
+        <v>0.005325</v>
       </c>
     </row>
     <row r="1564">
@@ -20749,7 +20749,7 @@
         <v>276</v>
       </c>
       <c r="C1564" t="n">
-        <v>0.005461</v>
+        <v>0.005463</v>
       </c>
     </row>
     <row r="1565">
@@ -20762,7 +20762,7 @@
         <v>277</v>
       </c>
       <c r="C1565" t="n">
-        <v>0.005637</v>
+        <v>0.005639</v>
       </c>
     </row>
     <row r="1566">
@@ -20775,7 +20775,7 @@
         <v>278</v>
       </c>
       <c r="C1566" t="n">
-        <v>0.005683</v>
+        <v>0.005693</v>
       </c>
     </row>
     <row r="1567">
@@ -20788,7 +20788,7 @@
         <v>279</v>
       </c>
       <c r="C1567" t="n">
-        <v>0.006184</v>
+        <v>0.006186</v>
       </c>
     </row>
     <row r="1568">
@@ -20801,7 +20801,7 @@
         <v>280</v>
       </c>
       <c r="C1568" t="n">
-        <v>0.006454</v>
+        <v>0.006456</v>
       </c>
     </row>
     <row r="1569">
@@ -20827,7 +20827,7 @@
         <v>282</v>
       </c>
       <c r="C1570" t="n">
-        <v>0.007830999999999999</v>
+        <v>0.007833</v>
       </c>
     </row>
     <row r="1571">
@@ -20866,7 +20866,7 @@
         <v>285</v>
       </c>
       <c r="C1573" t="n">
-        <v>0.008300999999999999</v>
+        <v>0.00831</v>
       </c>
     </row>
     <row r="1574">
@@ -20879,7 +20879,7 @@
         <v>286</v>
       </c>
       <c r="C1574" t="n">
-        <v>0.008408000000000001</v>
+        <v>0.008410000000000001</v>
       </c>
     </row>
     <row r="1575">
@@ -20905,7 +20905,7 @@
         <v>288</v>
       </c>
       <c r="C1576" t="n">
-        <v>0.008612</v>
+        <v>0.008613000000000001</v>
       </c>
     </row>
     <row r="1577">
@@ -20918,7 +20918,7 @@
         <v>289</v>
       </c>
       <c r="C1577" t="n">
-        <v>0.008741000000000001</v>
+        <v>0.008753</v>
       </c>
     </row>
     <row r="1578">
@@ -20931,7 +20931,7 @@
         <v>290</v>
       </c>
       <c r="C1578" t="n">
-        <v>0.008887000000000001</v>
+        <v>0.008888</v>
       </c>
     </row>
     <row r="1579">
@@ -20957,7 +20957,7 @@
         <v>292</v>
       </c>
       <c r="C1580" t="n">
-        <v>0.009252</v>
+        <v>0.009259</v>
       </c>
     </row>
     <row r="1581">
@@ -20970,7 +20970,7 @@
         <v>293</v>
       </c>
       <c r="C1581" t="n">
-        <v>0.009481</v>
+        <v>0.009494000000000001</v>
       </c>
     </row>
     <row r="1582">
@@ -20996,7 +20996,7 @@
         <v>295</v>
       </c>
       <c r="C1583" t="n">
-        <v>0.010258</v>
+        <v>0.010266</v>
       </c>
     </row>
     <row r="1584">
@@ -21009,7 +21009,7 @@
         <v>296</v>
       </c>
       <c r="C1584" t="n">
-        <v>0.010267</v>
+        <v>0.010271</v>
       </c>
     </row>
     <row r="1585">
@@ -21035,7 +21035,7 @@
         <v>298</v>
       </c>
       <c r="C1586" t="n">
-        <v>0.010504</v>
+        <v>0.010505</v>
       </c>
     </row>
     <row r="1587">
@@ -21048,7 +21048,7 @@
         <v>299</v>
       </c>
       <c r="C1587" t="n">
-        <v>0.010573</v>
+        <v>0.010576</v>
       </c>
     </row>
     <row r="1588">
@@ -21061,7 +21061,7 @@
         <v>300</v>
       </c>
       <c r="C1588" t="n">
-        <v>0.01076</v>
+        <v>0.010774</v>
       </c>
     </row>
     <row r="1589">
@@ -21074,7 +21074,7 @@
         <v>301</v>
       </c>
       <c r="C1589" t="n">
-        <v>0.010816</v>
+        <v>0.010817</v>
       </c>
     </row>
     <row r="1590">
@@ -21113,7 +21113,7 @@
         <v>304</v>
       </c>
       <c r="C1592" t="n">
-        <v>0.011573</v>
+        <v>0.011575</v>
       </c>
     </row>
     <row r="1593">
@@ -21139,7 +21139,7 @@
         <v>306</v>
       </c>
       <c r="C1594" t="n">
-        <v>0.011764</v>
+        <v>0.011765</v>
       </c>
     </row>
     <row r="1595">
@@ -21152,7 +21152,7 @@
         <v>307</v>
       </c>
       <c r="C1595" t="n">
-        <v>0.011835</v>
+        <v>0.011836</v>
       </c>
     </row>
     <row r="1596">
@@ -21165,7 +21165,7 @@
         <v>308</v>
       </c>
       <c r="C1596" t="n">
-        <v>0.012155</v>
+        <v>0.012156</v>
       </c>
     </row>
     <row r="1597">
@@ -21178,7 +21178,7 @@
         <v>309</v>
       </c>
       <c r="C1597" t="n">
-        <v>0.012257</v>
+        <v>0.012259</v>
       </c>
     </row>
     <row r="1598">
@@ -21204,7 +21204,7 @@
         <v>311</v>
       </c>
       <c r="C1599" t="n">
-        <v>0.012796</v>
+        <v>0.012802</v>
       </c>
     </row>
     <row r="1600">
@@ -21217,7 +21217,7 @@
         <v>312</v>
       </c>
       <c r="C1600" t="n">
-        <v>0.01292</v>
+        <v>0.012924</v>
       </c>
     </row>
     <row r="1601">
@@ -21230,7 +21230,7 @@
         <v>313</v>
       </c>
       <c r="C1601" t="n">
-        <v>0.013278</v>
+        <v>0.013279</v>
       </c>
     </row>
     <row r="1602">
@@ -21256,7 +21256,7 @@
         <v>315</v>
       </c>
       <c r="C1603" t="n">
-        <v>0.013395</v>
+        <v>0.013394</v>
       </c>
     </row>
     <row r="1604">
@@ -21269,7 +21269,7 @@
         <v>316</v>
       </c>
       <c r="C1604" t="n">
-        <v>0.013477</v>
+        <v>0.013481</v>
       </c>
     </row>
     <row r="1605">
@@ -21282,7 +21282,7 @@
         <v>317</v>
       </c>
       <c r="C1605" t="n">
-        <v>0.013558</v>
+        <v>0.013564</v>
       </c>
     </row>
     <row r="1606">
@@ -21295,7 +21295,7 @@
         <v>318</v>
       </c>
       <c r="C1606" t="n">
-        <v>0.013748</v>
+        <v>0.013756</v>
       </c>
     </row>
     <row r="1607">
@@ -21308,7 +21308,7 @@
         <v>319</v>
       </c>
       <c r="C1607" t="n">
-        <v>0.01406</v>
+        <v>0.014061</v>
       </c>
     </row>
     <row r="1608">
@@ -21347,7 +21347,7 @@
         <v>322</v>
       </c>
       <c r="C1610" t="n">
-        <v>0.014175</v>
+        <v>0.014199</v>
       </c>
     </row>
     <row r="1611">
@@ -21386,7 +21386,7 @@
         <v>325</v>
       </c>
       <c r="C1613" t="n">
-        <v>0.015405</v>
+        <v>0.015406</v>
       </c>
     </row>
     <row r="1614">
@@ -21399,7 +21399,7 @@
         <v>326</v>
       </c>
       <c r="C1614" t="n">
-        <v>0.01549</v>
+        <v>0.015489</v>
       </c>
     </row>
     <row r="1615">
@@ -21425,7 +21425,7 @@
         <v>328</v>
       </c>
       <c r="C1616" t="n">
-        <v>0.015681</v>
+        <v>0.015688</v>
       </c>
     </row>
     <row r="1617">
@@ -21438,7 +21438,7 @@
         <v>329</v>
       </c>
       <c r="C1617" t="n">
-        <v>0.015893</v>
+        <v>0.015894</v>
       </c>
     </row>
     <row r="1618">
@@ -21464,7 +21464,7 @@
         <v>331</v>
       </c>
       <c r="C1619" t="n">
-        <v>0.016173</v>
+        <v>0.016191</v>
       </c>
     </row>
     <row r="1620">
@@ -21477,7 +21477,7 @@
         <v>332</v>
       </c>
       <c r="C1620" t="n">
-        <v>0.016569</v>
+        <v>0.01657</v>
       </c>
     </row>
     <row r="1621">
@@ -21490,7 +21490,7 @@
         <v>333</v>
       </c>
       <c r="C1621" t="n">
-        <v>0.016631</v>
+        <v>0.016632</v>
       </c>
     </row>
     <row r="1622">
@@ -21503,7 +21503,7 @@
         <v>334</v>
       </c>
       <c r="C1622" t="n">
-        <v>0.016734</v>
+        <v>0.016743</v>
       </c>
     </row>
     <row r="1623">
@@ -21516,7 +21516,7 @@
         <v>335</v>
       </c>
       <c r="C1623" t="n">
-        <v>0.016983</v>
+        <v>0.016993</v>
       </c>
     </row>
     <row r="1624">
@@ -21529,7 +21529,7 @@
         <v>336</v>
       </c>
       <c r="C1624" t="n">
-        <v>0.017368</v>
+        <v>0.017367</v>
       </c>
     </row>
     <row r="1625">
@@ -21542,7 +21542,7 @@
         <v>337</v>
       </c>
       <c r="C1625" t="n">
-        <v>0.017644</v>
+        <v>0.017649</v>
       </c>
     </row>
     <row r="1626">
@@ -21555,7 +21555,7 @@
         <v>338</v>
       </c>
       <c r="C1626" t="n">
-        <v>0.017876</v>
+        <v>0.017883</v>
       </c>
     </row>
     <row r="1627">
@@ -21568,7 +21568,7 @@
         <v>339</v>
       </c>
       <c r="C1627" t="n">
-        <v>0.018157</v>
+        <v>0.018165</v>
       </c>
     </row>
     <row r="1628">
@@ -21581,7 +21581,7 @@
         <v>340</v>
       </c>
       <c r="C1628" t="n">
-        <v>0.01819</v>
+        <v>0.018193</v>
       </c>
     </row>
     <row r="1629">
@@ -21594,7 +21594,7 @@
         <v>341</v>
       </c>
       <c r="C1629" t="n">
-        <v>0.0182</v>
+        <v>0.018202</v>
       </c>
     </row>
     <row r="1630">
@@ -21607,7 +21607,7 @@
         <v>342</v>
       </c>
       <c r="C1630" t="n">
-        <v>0.018324</v>
+        <v>0.018326</v>
       </c>
     </row>
     <row r="1631">
@@ -21620,7 +21620,7 @@
         <v>343</v>
       </c>
       <c r="C1631" t="n">
-        <v>0.018422</v>
+        <v>0.018421</v>
       </c>
     </row>
     <row r="1632">
@@ -21633,7 +21633,7 @@
         <v>344</v>
       </c>
       <c r="C1632" t="n">
-        <v>0.018446</v>
+        <v>0.018449</v>
       </c>
     </row>
     <row r="1633">
@@ -21646,7 +21646,7 @@
         <v>345</v>
       </c>
       <c r="C1633" t="n">
-        <v>0.018924</v>
+        <v>0.018942</v>
       </c>
     </row>
     <row r="1634">
@@ -21659,7 +21659,7 @@
         <v>346</v>
       </c>
       <c r="C1634" t="n">
-        <v>0.019054</v>
+        <v>0.019063</v>
       </c>
     </row>
     <row r="1635">
@@ -21672,7 +21672,7 @@
         <v>347</v>
       </c>
       <c r="C1635" t="n">
-        <v>0.019655</v>
+        <v>0.019657</v>
       </c>
     </row>
     <row r="1636">
@@ -21698,7 +21698,7 @@
         <v>349</v>
       </c>
       <c r="C1637" t="n">
-        <v>0.020096</v>
+        <v>0.020099</v>
       </c>
     </row>
     <row r="1638">
@@ -21711,7 +21711,7 @@
         <v>350</v>
       </c>
       <c r="C1638" t="n">
-        <v>0.020117</v>
+        <v>0.020116</v>
       </c>
     </row>
     <row r="1639">
@@ -21737,7 +21737,7 @@
         <v>352</v>
       </c>
       <c r="C1640" t="n">
-        <v>0.020566</v>
+        <v>0.020565</v>
       </c>
     </row>
     <row r="1641">
@@ -21750,7 +21750,7 @@
         <v>353</v>
       </c>
       <c r="C1641" t="n">
-        <v>0.021326</v>
+        <v>0.021331</v>
       </c>
     </row>
     <row r="1642">
@@ -21763,7 +21763,7 @@
         <v>354</v>
       </c>
       <c r="C1642" t="n">
-        <v>0.021616</v>
+        <v>0.021629</v>
       </c>
     </row>
     <row r="1643">
@@ -21789,7 +21789,7 @@
         <v>356</v>
       </c>
       <c r="C1644" t="n">
-        <v>0.021733</v>
+        <v>0.021781</v>
       </c>
     </row>
     <row r="1645">
@@ -21815,7 +21815,7 @@
         <v>358</v>
       </c>
       <c r="C1646" t="n">
-        <v>0.022263</v>
+        <v>0.022267</v>
       </c>
     </row>
     <row r="1647">
@@ -21828,7 +21828,7 @@
         <v>359</v>
       </c>
       <c r="C1647" t="n">
-        <v>0.022364</v>
+        <v>0.022365</v>
       </c>
     </row>
     <row r="1648">
@@ -21867,7 +21867,7 @@
         <v>362</v>
       </c>
       <c r="C1650" t="n">
-        <v>0.022903</v>
+        <v>0.022912</v>
       </c>
     </row>
     <row r="1651">
@@ -21880,7 +21880,7 @@
         <v>363</v>
       </c>
       <c r="C1651" t="n">
-        <v>0.023063</v>
+        <v>0.023062</v>
       </c>
     </row>
     <row r="1652">
@@ -21893,7 +21893,7 @@
         <v>364</v>
       </c>
       <c r="C1652" t="n">
-        <v>0.02309</v>
+        <v>0.023091</v>
       </c>
     </row>
     <row r="1653">
@@ -21932,7 +21932,7 @@
         <v>367</v>
       </c>
       <c r="C1655" t="n">
-        <v>0.023707</v>
+        <v>0.023708</v>
       </c>
     </row>
     <row r="1656">
@@ -21945,7 +21945,7 @@
         <v>368</v>
       </c>
       <c r="C1656" t="n">
-        <v>0.024203</v>
+        <v>0.024205</v>
       </c>
     </row>
     <row r="1657">
@@ -21958,7 +21958,7 @@
         <v>369</v>
       </c>
       <c r="C1657" t="n">
-        <v>0.024276</v>
+        <v>0.024285</v>
       </c>
     </row>
     <row r="1658">
@@ -21971,7 +21971,7 @@
         <v>370</v>
       </c>
       <c r="C1658" t="n">
-        <v>0.024381</v>
+        <v>0.024383</v>
       </c>
     </row>
     <row r="1659">
@@ -21984,7 +21984,7 @@
         <v>371</v>
       </c>
       <c r="C1659" t="n">
-        <v>0.024461</v>
+        <v>0.024471</v>
       </c>
     </row>
     <row r="1660">
@@ -22010,7 +22010,7 @@
         <v>373</v>
       </c>
       <c r="C1661" t="n">
-        <v>0.024749</v>
+        <v>0.024748</v>
       </c>
     </row>
     <row r="1662">
@@ -22023,7 +22023,7 @@
         <v>374</v>
       </c>
       <c r="C1662" t="n">
-        <v>0.024815</v>
+        <v>0.024817</v>
       </c>
     </row>
     <row r="1663">
@@ -22049,7 +22049,7 @@
         <v>376</v>
       </c>
       <c r="C1664" t="n">
-        <v>0.025099</v>
+        <v>0.025098</v>
       </c>
     </row>
     <row r="1665">
@@ -22062,7 +22062,7 @@
         <v>377</v>
       </c>
       <c r="C1665" t="n">
-        <v>0.025323</v>
+        <v>0.02534</v>
       </c>
     </row>
     <row r="1666">
@@ -22075,7 +22075,7 @@
         <v>378</v>
       </c>
       <c r="C1666" t="n">
-        <v>0.026802</v>
+        <v>0.026805</v>
       </c>
     </row>
     <row r="1667">
@@ -22088,7 +22088,7 @@
         <v>379</v>
       </c>
       <c r="C1667" t="n">
-        <v>0.02687</v>
+        <v>0.026878</v>
       </c>
     </row>
     <row r="1668">
@@ -22101,7 +22101,7 @@
         <v>380</v>
       </c>
       <c r="C1668" t="n">
-        <v>0.027106</v>
+        <v>0.027123</v>
       </c>
     </row>
     <row r="1669">
@@ -22114,7 +22114,7 @@
         <v>381</v>
       </c>
       <c r="C1669" t="n">
-        <v>0.027218</v>
+        <v>0.027217</v>
       </c>
     </row>
     <row r="1670">
@@ -22127,7 +22127,7 @@
         <v>382</v>
       </c>
       <c r="C1670" t="n">
-        <v>0.027235</v>
+        <v>0.027234</v>
       </c>
     </row>
     <row r="1671">
@@ -22140,7 +22140,7 @@
         <v>383</v>
       </c>
       <c r="C1671" t="n">
-        <v>0.027283</v>
+        <v>0.027286</v>
       </c>
     </row>
     <row r="1672">
@@ -22153,7 +22153,7 @@
         <v>384</v>
       </c>
       <c r="C1672" t="n">
-        <v>0.027372</v>
+        <v>0.027383</v>
       </c>
     </row>
     <row r="1673">
@@ -22179,7 +22179,7 @@
         <v>386</v>
       </c>
       <c r="C1674" t="n">
-        <v>0.027985</v>
+        <v>0.027996</v>
       </c>
     </row>
     <row r="1675">
@@ -22192,7 +22192,7 @@
         <v>387</v>
       </c>
       <c r="C1675" t="n">
-        <v>0.028052</v>
+        <v>0.028051</v>
       </c>
     </row>
     <row r="1676">
@@ -22205,7 +22205,7 @@
         <v>388</v>
       </c>
       <c r="C1676" t="n">
-        <v>0.02842</v>
+        <v>0.028439</v>
       </c>
     </row>
     <row r="1677">
@@ -22218,7 +22218,7 @@
         <v>389</v>
       </c>
       <c r="C1677" t="n">
-        <v>0.028606</v>
+        <v>0.028611</v>
       </c>
     </row>
     <row r="1678">
@@ -22231,7 +22231,7 @@
         <v>390</v>
       </c>
       <c r="C1678" t="n">
-        <v>0.028782</v>
+        <v>0.028792</v>
       </c>
     </row>
     <row r="1679">
@@ -22257,7 +22257,7 @@
         <v>392</v>
       </c>
       <c r="C1680" t="n">
-        <v>0.029153</v>
+        <v>0.029155</v>
       </c>
     </row>
     <row r="1681">
@@ -22270,7 +22270,7 @@
         <v>393</v>
       </c>
       <c r="C1681" t="n">
-        <v>0.029292</v>
+        <v>0.029294</v>
       </c>
     </row>
     <row r="1682">
@@ -22283,7 +22283,7 @@
         <v>394</v>
       </c>
       <c r="C1682" t="n">
-        <v>0.029617</v>
+        <v>0.02962</v>
       </c>
     </row>
     <row r="1683">
@@ -22296,7 +22296,7 @@
         <v>395</v>
       </c>
       <c r="C1683" t="n">
-        <v>0.029928</v>
+        <v>0.029931</v>
       </c>
     </row>
     <row r="1684">
@@ -22309,7 +22309,7 @@
         <v>396</v>
       </c>
       <c r="C1684" t="n">
-        <v>0.030074</v>
+        <v>0.030122</v>
       </c>
     </row>
     <row r="1685">
@@ -22322,7 +22322,7 @@
         <v>397</v>
       </c>
       <c r="C1685" t="n">
-        <v>0.030394</v>
+        <v>0.030395</v>
       </c>
     </row>
     <row r="1686">
@@ -22335,7 +22335,7 @@
         <v>398</v>
       </c>
       <c r="C1686" t="n">
-        <v>0.030443</v>
+        <v>0.030442</v>
       </c>
     </row>
     <row r="1687">
@@ -22361,7 +22361,7 @@
         <v>400</v>
       </c>
       <c r="C1688" t="n">
-        <v>0.030941</v>
+        <v>0.03097</v>
       </c>
     </row>
     <row r="1689">
@@ -22374,7 +22374,7 @@
         <v>401</v>
       </c>
       <c r="C1689" t="n">
-        <v>0.031121</v>
+        <v>0.03112</v>
       </c>
     </row>
     <row r="1690">
@@ -22387,7 +22387,7 @@
         <v>402</v>
       </c>
       <c r="C1690" t="n">
-        <v>0.031125</v>
+        <v>0.031134</v>
       </c>
     </row>
     <row r="1691">
@@ -22400,7 +22400,7 @@
         <v>403</v>
       </c>
       <c r="C1691" t="n">
-        <v>0.031409</v>
+        <v>0.031408</v>
       </c>
     </row>
     <row r="1692">
@@ -22413,7 +22413,7 @@
         <v>404</v>
       </c>
       <c r="C1692" t="n">
-        <v>0.031628</v>
+        <v>0.031644</v>
       </c>
     </row>
     <row r="1693">
@@ -22426,7 +22426,7 @@
         <v>405</v>
       </c>
       <c r="C1693" t="n">
-        <v>0.03166</v>
+        <v>0.031658</v>
       </c>
     </row>
     <row r="1694">
@@ -22439,7 +22439,7 @@
         <v>406</v>
       </c>
       <c r="C1694" t="n">
-        <v>0.031696</v>
+        <v>0.031716</v>
       </c>
     </row>
     <row r="1695">
@@ -22452,7 +22452,7 @@
         <v>407</v>
       </c>
       <c r="C1695" t="n">
-        <v>0.031715</v>
+        <v>0.031717</v>
       </c>
     </row>
     <row r="1696">
@@ -22478,7 +22478,7 @@
         <v>409</v>
       </c>
       <c r="C1697" t="n">
-        <v>0.032251</v>
+        <v>0.032262</v>
       </c>
     </row>
     <row r="1698">
@@ -22491,7 +22491,7 @@
         <v>410</v>
       </c>
       <c r="C1698" t="n">
-        <v>0.032853</v>
+        <v>0.032852</v>
       </c>
     </row>
     <row r="1699">
@@ -22504,7 +22504,7 @@
         <v>411</v>
       </c>
       <c r="C1699" t="n">
-        <v>0.032912</v>
+        <v>0.032916</v>
       </c>
     </row>
     <row r="1700">
@@ -22517,7 +22517,7 @@
         <v>412</v>
       </c>
       <c r="C1700" t="n">
-        <v>0.033315</v>
+        <v>0.033322</v>
       </c>
     </row>
     <row r="1701">
@@ -22530,7 +22530,7 @@
         <v>413</v>
       </c>
       <c r="C1701" t="n">
-        <v>0.03356</v>
+        <v>0.033582</v>
       </c>
     </row>
     <row r="1702">
@@ -22543,7 +22543,7 @@
         <v>414</v>
       </c>
       <c r="C1702" t="n">
-        <v>0.03369</v>
+        <v>0.033692</v>
       </c>
     </row>
     <row r="1703">
@@ -22556,7 +22556,7 @@
         <v>415</v>
       </c>
       <c r="C1703" t="n">
-        <v>0.033779</v>
+        <v>0.033784</v>
       </c>
     </row>
     <row r="1704">
@@ -22569,7 +22569,7 @@
         <v>416</v>
       </c>
       <c r="C1704" t="n">
-        <v>0.033855</v>
+        <v>0.033879</v>
       </c>
     </row>
     <row r="1705">
@@ -22582,7 +22582,7 @@
         <v>417</v>
       </c>
       <c r="C1705" t="n">
-        <v>0.034132</v>
+        <v>0.034162</v>
       </c>
     </row>
     <row r="1706">
@@ -22595,7 +22595,7 @@
         <v>418</v>
       </c>
       <c r="C1706" t="n">
-        <v>0.034293</v>
+        <v>0.034292</v>
       </c>
     </row>
     <row r="1707">
@@ -22608,7 +22608,7 @@
         <v>419</v>
       </c>
       <c r="C1707" t="n">
-        <v>0.034634</v>
+        <v>0.034651</v>
       </c>
     </row>
     <row r="1708">
@@ -22621,7 +22621,7 @@
         <v>420</v>
       </c>
       <c r="C1708" t="n">
-        <v>0.034753</v>
+        <v>0.034778</v>
       </c>
     </row>
     <row r="1709">
@@ -22634,7 +22634,7 @@
         <v>421</v>
       </c>
       <c r="C1709" t="n">
-        <v>0.034826</v>
+        <v>0.034825</v>
       </c>
     </row>
     <row r="1710">
@@ -22647,7 +22647,7 @@
         <v>422</v>
       </c>
       <c r="C1710" t="n">
-        <v>0.034929</v>
+        <v>0.034931</v>
       </c>
     </row>
     <row r="1711">
@@ -22660,7 +22660,7 @@
         <v>423</v>
       </c>
       <c r="C1711" t="n">
-        <v>0.035695</v>
+        <v>0.035694</v>
       </c>
     </row>
     <row r="1712">
@@ -22673,7 +22673,7 @@
         <v>424</v>
       </c>
       <c r="C1712" t="n">
-        <v>0.036193</v>
+        <v>0.036196</v>
       </c>
     </row>
     <row r="1713">
@@ -22686,7 +22686,7 @@
         <v>425</v>
       </c>
       <c r="C1713" t="n">
-        <v>0.036239</v>
+        <v>0.036247</v>
       </c>
     </row>
     <row r="1714">
@@ -22699,7 +22699,7 @@
         <v>426</v>
       </c>
       <c r="C1714" t="n">
-        <v>0.036422</v>
+        <v>0.036423</v>
       </c>
     </row>
     <row r="1715">
@@ -22725,7 +22725,7 @@
         <v>428</v>
       </c>
       <c r="C1716" t="n">
-        <v>0.037236</v>
+        <v>0.037235</v>
       </c>
     </row>
     <row r="1717">
@@ -22738,7 +22738,7 @@
         <v>429</v>
       </c>
       <c r="C1717" t="n">
-        <v>0.037236</v>
+        <v>0.037238</v>
       </c>
     </row>
     <row r="1718">
@@ -22764,7 +22764,7 @@
         <v>431</v>
       </c>
       <c r="C1719" t="n">
-        <v>0.037475</v>
+        <v>0.037496</v>
       </c>
     </row>
     <row r="1720">
@@ -22777,7 +22777,7 @@
         <v>432</v>
       </c>
       <c r="C1720" t="n">
-        <v>0.037734</v>
+        <v>0.037748</v>
       </c>
     </row>
     <row r="1721">
@@ -22790,7 +22790,7 @@
         <v>433</v>
       </c>
       <c r="C1721" t="n">
-        <v>0.038129</v>
+        <v>0.038127</v>
       </c>
     </row>
     <row r="1722">
@@ -22803,7 +22803,7 @@
         <v>434</v>
       </c>
       <c r="C1722" t="n">
-        <v>0.038307</v>
+        <v>0.038309</v>
       </c>
     </row>
     <row r="1723">
@@ -22816,7 +22816,7 @@
         <v>435</v>
       </c>
       <c r="C1723" t="n">
-        <v>0.038484</v>
+        <v>0.038492</v>
       </c>
     </row>
     <row r="1724">
@@ -22829,7 +22829,7 @@
         <v>436</v>
       </c>
       <c r="C1724" t="n">
-        <v>0.038542</v>
+        <v>0.038557</v>
       </c>
     </row>
     <row r="1725">
@@ -22842,7 +22842,7 @@
         <v>437</v>
       </c>
       <c r="C1725" t="n">
-        <v>0.038604</v>
+        <v>0.038616</v>
       </c>
     </row>
     <row r="1726">
@@ -22868,7 +22868,7 @@
         <v>439</v>
       </c>
       <c r="C1727" t="n">
-        <v>0.040196</v>
+        <v>0.040219</v>
       </c>
     </row>
     <row r="1728">
@@ -22881,7 +22881,7 @@
         <v>440</v>
       </c>
       <c r="C1728" t="n">
-        <v>0.040404</v>
+        <v>0.040406</v>
       </c>
     </row>
     <row r="1729">
@@ -22894,7 +22894,7 @@
         <v>441</v>
       </c>
       <c r="C1729" t="n">
-        <v>0.040488</v>
+        <v>0.040486</v>
       </c>
     </row>
     <row r="1730">
@@ -22907,7 +22907,7 @@
         <v>442</v>
       </c>
       <c r="C1730" t="n">
-        <v>0.040815</v>
+        <v>0.040816</v>
       </c>
     </row>
     <row r="1731">
@@ -22920,7 +22920,7 @@
         <v>443</v>
       </c>
       <c r="C1731" t="n">
-        <v>0.040895</v>
+        <v>0.040897</v>
       </c>
     </row>
     <row r="1732">
@@ -22933,7 +22933,7 @@
         <v>444</v>
       </c>
       <c r="C1732" t="n">
-        <v>0.041069</v>
+        <v>0.041073</v>
       </c>
     </row>
     <row r="1733">
@@ -22946,7 +22946,7 @@
         <v>445</v>
       </c>
       <c r="C1733" t="n">
-        <v>0.041456</v>
+        <v>0.041478</v>
       </c>
     </row>
     <row r="1734">
@@ -22959,7 +22959,7 @@
         <v>446</v>
       </c>
       <c r="C1734" t="n">
-        <v>0.041475</v>
+        <v>0.041479</v>
       </c>
     </row>
     <row r="1735">
@@ -22972,7 +22972,7 @@
         <v>447</v>
       </c>
       <c r="C1735" t="n">
-        <v>0.041765</v>
+        <v>0.041764</v>
       </c>
     </row>
     <row r="1736">
@@ -22985,7 +22985,7 @@
         <v>448</v>
       </c>
       <c r="C1736" t="n">
-        <v>0.041854</v>
+        <v>0.041859</v>
       </c>
     </row>
     <row r="1737">
@@ -22998,7 +22998,7 @@
         <v>449</v>
       </c>
       <c r="C1737" t="n">
-        <v>0.042034</v>
+        <v>0.042056</v>
       </c>
     </row>
     <row r="1738">
@@ -23011,7 +23011,7 @@
         <v>450</v>
       </c>
       <c r="C1738" t="n">
-        <v>0.042035</v>
+        <v>0.04221</v>
       </c>
     </row>
     <row r="1739">
@@ -23024,7 +23024,7 @@
         <v>451</v>
       </c>
       <c r="C1739" t="n">
-        <v>0.042181</v>
+        <v>0.04241</v>
       </c>
     </row>
     <row r="1740">
@@ -23037,7 +23037,7 @@
         <v>452</v>
       </c>
       <c r="C1740" t="n">
-        <v>0.04239</v>
+        <v>0.042573</v>
       </c>
     </row>
     <row r="1741">
@@ -23050,7 +23050,7 @@
         <v>453</v>
       </c>
       <c r="C1741" t="n">
-        <v>0.04255</v>
+        <v>0.042602</v>
       </c>
     </row>
     <row r="1742">
@@ -23063,7 +23063,7 @@
         <v>454</v>
       </c>
       <c r="C1742" t="n">
-        <v>0.042595</v>
+        <v>0.04276</v>
       </c>
     </row>
     <row r="1743">
@@ -23076,7 +23076,7 @@
         <v>455</v>
       </c>
       <c r="C1743" t="n">
-        <v>0.042728</v>
+        <v>0.042853</v>
       </c>
     </row>
     <row r="1744">
@@ -23089,7 +23089,7 @@
         <v>456</v>
       </c>
       <c r="C1744" t="n">
-        <v>0.042849</v>
+        <v>0.042939</v>
       </c>
     </row>
     <row r="1745">
@@ -23102,7 +23102,7 @@
         <v>457</v>
       </c>
       <c r="C1745" t="n">
-        <v>0.042923</v>
+        <v>0.043366</v>
       </c>
     </row>
     <row r="1746">
@@ -23115,7 +23115,7 @@
         <v>458</v>
       </c>
       <c r="C1746" t="n">
-        <v>0.043359</v>
+        <v>0.043875</v>
       </c>
     </row>
     <row r="1747">
@@ -23128,7 +23128,7 @@
         <v>459</v>
       </c>
       <c r="C1747" t="n">
-        <v>0.043871</v>
+        <v>0.044075</v>
       </c>
     </row>
     <row r="1748">
@@ -23141,7 +23141,7 @@
         <v>460</v>
       </c>
       <c r="C1748" t="n">
-        <v>0.044028</v>
+        <v>0.044279</v>
       </c>
     </row>
     <row r="1749">
@@ -23154,7 +23154,7 @@
         <v>461</v>
       </c>
       <c r="C1749" t="n">
-        <v>0.044266</v>
+        <v>0.044431</v>
       </c>
     </row>
     <row r="1750">
@@ -23167,7 +23167,7 @@
         <v>462</v>
       </c>
       <c r="C1750" t="n">
-        <v>0.04439</v>
+        <v>0.044613</v>
       </c>
     </row>
     <row r="1751">
@@ -23180,7 +23180,7 @@
         <v>463</v>
       </c>
       <c r="C1751" t="n">
-        <v>0.044611</v>
+        <v>0.044749</v>
       </c>
     </row>
     <row r="1752">
@@ -23193,7 +23193,7 @@
         <v>464</v>
       </c>
       <c r="C1752" t="n">
-        <v>0.044737</v>
+        <v>0.045636</v>
       </c>
     </row>
     <row r="1753">
@@ -23206,7 +23206,7 @@
         <v>465</v>
       </c>
       <c r="C1753" t="n">
-        <v>0.045631</v>
+        <v>0.046029</v>
       </c>
     </row>
     <row r="1754">
@@ -23219,7 +23219,7 @@
         <v>466</v>
       </c>
       <c r="C1754" t="n">
-        <v>0.046011</v>
+        <v>0.046051</v>
       </c>
     </row>
     <row r="1755">
@@ -23232,7 +23232,7 @@
         <v>467</v>
       </c>
       <c r="C1755" t="n">
-        <v>0.04605</v>
+        <v>0.046771</v>
       </c>
     </row>
     <row r="1756">
@@ -23245,7 +23245,7 @@
         <v>468</v>
       </c>
       <c r="C1756" t="n">
-        <v>0.046766</v>
+        <v>0.046797</v>
       </c>
     </row>
     <row r="1757">
@@ -23258,7 +23258,7 @@
         <v>469</v>
       </c>
       <c r="C1757" t="n">
-        <v>0.046795</v>
+        <v>0.047039</v>
       </c>
     </row>
     <row r="1758">
@@ -23271,7 +23271,7 @@
         <v>470</v>
       </c>
       <c r="C1758" t="n">
-        <v>0.047038</v>
+        <v>0.047385</v>
       </c>
     </row>
     <row r="1759">
@@ -23284,7 +23284,7 @@
         <v>471</v>
       </c>
       <c r="C1759" t="n">
-        <v>0.047357</v>
+        <v>0.047652</v>
       </c>
     </row>
     <row r="1760">
@@ -23297,7 +23297,7 @@
         <v>472</v>
       </c>
       <c r="C1760" t="n">
-        <v>0.04765</v>
+        <v>0.047964</v>
       </c>
     </row>
     <row r="1761">
@@ -23310,7 +23310,7 @@
         <v>473</v>
       </c>
       <c r="C1761" t="n">
-        <v>0.047946</v>
+        <v>0.048106</v>
       </c>
     </row>
     <row r="1762">
@@ -23323,7 +23323,7 @@
         <v>474</v>
       </c>
       <c r="C1762" t="n">
-        <v>0.048104</v>
+        <v>0.049309</v>
       </c>
     </row>
     <row r="1763">
@@ -23336,7 +23336,7 @@
         <v>475</v>
       </c>
       <c r="C1763" t="n">
-        <v>0.049311</v>
+        <v>0.049407</v>
       </c>
     </row>
     <row r="1764">
@@ -23349,7 +23349,7 @@
         <v>476</v>
       </c>
       <c r="C1764" t="n">
-        <v>0.049409</v>
+        <v>0.04956</v>
       </c>
     </row>
     <row r="1765">
@@ -23362,7 +23362,7 @@
         <v>477</v>
       </c>
       <c r="C1765" t="n">
-        <v>0.04956</v>
+        <v>0.04973</v>
       </c>
     </row>
     <row r="1766">
@@ -23375,7 +23375,7 @@
         <v>478</v>
       </c>
       <c r="C1766" t="n">
-        <v>0.049691</v>
+        <v>0.049761</v>
       </c>
     </row>
     <row r="1767">
@@ -23388,7 +23388,7 @@
         <v>479</v>
       </c>
       <c r="C1767" t="n">
-        <v>0.049758</v>
+        <v>0.050449</v>
       </c>
     </row>
     <row r="1768">
@@ -23401,7 +23401,7 @@
         <v>480</v>
       </c>
       <c r="C1768" t="n">
-        <v>0.050443</v>
+        <v>0.050568</v>
       </c>
     </row>
     <row r="1769">
@@ -23414,7 +23414,7 @@
         <v>481</v>
       </c>
       <c r="C1769" t="n">
-        <v>0.050569</v>
+        <v>0.050598</v>
       </c>
     </row>
     <row r="1770">
@@ -23427,7 +23427,7 @@
         <v>482</v>
       </c>
       <c r="C1770" t="n">
-        <v>0.050595</v>
+        <v>0.050924</v>
       </c>
     </row>
     <row r="1771">
@@ -23440,7 +23440,7 @@
         <v>483</v>
       </c>
       <c r="C1771" t="n">
-        <v>0.050924</v>
+        <v>0.050957</v>
       </c>
     </row>
     <row r="1772">
@@ -23453,7 +23453,7 @@
         <v>484</v>
       </c>
       <c r="C1772" t="n">
-        <v>0.050958</v>
+        <v>0.051111</v>
       </c>
     </row>
     <row r="1773">
@@ -23466,7 +23466,7 @@
         <v>485</v>
       </c>
       <c r="C1773" t="n">
-        <v>0.05111</v>
+        <v>0.051233</v>
       </c>
     </row>
     <row r="1774">
@@ -23479,7 +23479,7 @@
         <v>486</v>
       </c>
       <c r="C1774" t="n">
-        <v>0.051215</v>
+        <v>0.05127</v>
       </c>
     </row>
     <row r="1775">
@@ -23492,7 +23492,7 @@
         <v>487</v>
       </c>
       <c r="C1775" t="n">
-        <v>0.051246</v>
+        <v>0.051306</v>
       </c>
     </row>
     <row r="1776">
@@ -23505,7 +23505,7 @@
         <v>488</v>
       </c>
       <c r="C1776" t="n">
-        <v>0.051302</v>
+        <v>0.051915</v>
       </c>
     </row>
     <row r="1777">
@@ -23518,7 +23518,7 @@
         <v>489</v>
       </c>
       <c r="C1777" t="n">
-        <v>0.051898</v>
+        <v>0.052128</v>
       </c>
     </row>
     <row r="1778">
@@ -23531,7 +23531,7 @@
         <v>490</v>
       </c>
       <c r="C1778" t="n">
-        <v>0.052115</v>
+        <v>0.052159</v>
       </c>
     </row>
     <row r="1779">
@@ -23544,7 +23544,7 @@
         <v>491</v>
       </c>
       <c r="C1779" t="n">
-        <v>0.052161</v>
+        <v>0.052649</v>
       </c>
     </row>
     <row r="1780">
@@ -23557,7 +23557,7 @@
         <v>492</v>
       </c>
       <c r="C1780" t="n">
-        <v>0.052645</v>
+        <v>0.052862</v>
       </c>
     </row>
     <row r="1781">
@@ -23570,7 +23570,7 @@
         <v>493</v>
       </c>
       <c r="C1781" t="n">
-        <v>0.052862</v>
+        <v>0.05351</v>
       </c>
     </row>
     <row r="1782">
@@ -23583,7 +23583,7 @@
         <v>494</v>
       </c>
       <c r="C1782" t="n">
-        <v>0.053486</v>
+        <v>0.053755</v>
       </c>
     </row>
     <row r="1783">
@@ -23596,7 +23596,7 @@
         <v>495</v>
       </c>
       <c r="C1783" t="n">
-        <v>0.053757</v>
+        <v>0.053806</v>
       </c>
     </row>
     <row r="1784">
@@ -23609,7 +23609,7 @@
         <v>496</v>
       </c>
       <c r="C1784" t="n">
-        <v>0.053789</v>
+        <v>0.053842</v>
       </c>
     </row>
     <row r="1785">
@@ -23622,7 +23622,7 @@
         <v>497</v>
       </c>
       <c r="C1785" t="n">
-        <v>0.053844</v>
+        <v>0.054349</v>
       </c>
     </row>
     <row r="1786">
@@ -23635,7 +23635,7 @@
         <v>498</v>
       </c>
       <c r="C1786" t="n">
-        <v>0.054344</v>
+        <v>0.05534</v>
       </c>
     </row>
     <row r="1787">
@@ -23648,7 +23648,7 @@
         <v>499</v>
       </c>
       <c r="C1787" t="n">
-        <v>0.055331</v>
+        <v>0.05597</v>
       </c>
     </row>
     <row r="1788">
@@ -23661,7 +23661,7 @@
         <v>500</v>
       </c>
       <c r="C1788" t="n">
-        <v>0.055968</v>
+        <v>0.05599</v>
       </c>
     </row>
     <row r="1789">
@@ -23674,7 +23674,7 @@
         <v>501</v>
       </c>
       <c r="C1789" t="n">
-        <v>0.055988</v>
+        <v>0.056141</v>
       </c>
     </row>
     <row r="1790">
@@ -23687,7 +23687,7 @@
         <v>502</v>
       </c>
       <c r="C1790" t="n">
-        <v>0.056139</v>
+        <v>0.056361</v>
       </c>
     </row>
     <row r="1791">
@@ -23700,7 +23700,7 @@
         <v>503</v>
       </c>
       <c r="C1791" t="n">
-        <v>0.056362</v>
+        <v>0.056798</v>
       </c>
     </row>
     <row r="1792">
@@ -23713,7 +23713,7 @@
         <v>504</v>
       </c>
       <c r="C1792" t="n">
-        <v>0.056736</v>
+        <v>0.056943</v>
       </c>
     </row>
     <row r="1793">
@@ -23726,7 +23726,7 @@
         <v>505</v>
       </c>
       <c r="C1793" t="n">
-        <v>0.056946</v>
+        <v>0.056949</v>
       </c>
     </row>
     <row r="1794">
@@ -23739,7 +23739,7 @@
         <v>506</v>
       </c>
       <c r="C1794" t="n">
-        <v>0.05797</v>
+        <v>0.057971</v>
       </c>
     </row>
     <row r="1795">
@@ -23752,7 +23752,7 @@
         <v>507</v>
       </c>
       <c r="C1795" t="n">
-        <v>0.058163</v>
+        <v>0.05817</v>
       </c>
     </row>
     <row r="1796">
@@ -23765,7 +23765,7 @@
         <v>508</v>
       </c>
       <c r="C1796" t="n">
-        <v>0.058717</v>
+        <v>0.058715</v>
       </c>
     </row>
     <row r="1797">
@@ -23778,7 +23778,7 @@
         <v>509</v>
       </c>
       <c r="C1797" t="n">
-        <v>0.059381</v>
+        <v>0.059384</v>
       </c>
     </row>
     <row r="1798">
@@ -23791,7 +23791,7 @@
         <v>510</v>
       </c>
       <c r="C1798" t="n">
-        <v>0.059455</v>
+        <v>0.059461</v>
       </c>
     </row>
     <row r="1799">
@@ -23804,7 +23804,7 @@
         <v>511</v>
       </c>
       <c r="C1799" t="n">
-        <v>0.059848</v>
+        <v>0.059847</v>
       </c>
     </row>
     <row r="1800">
@@ -23817,7 +23817,7 @@
         <v>512</v>
       </c>
       <c r="C1800" t="n">
-        <v>0.06041</v>
+        <v>0.060411</v>
       </c>
     </row>
     <row r="1801">
@@ -23830,7 +23830,7 @@
         <v>513</v>
       </c>
       <c r="C1801" t="n">
-        <v>0.060854</v>
+        <v>0.060852</v>
       </c>
     </row>
     <row r="1802">
@@ -23856,7 +23856,7 @@
         <v>515</v>
       </c>
       <c r="C1803" t="n">
-        <v>0.06166</v>
+        <v>0.061658</v>
       </c>
     </row>
     <row r="1804">
@@ -23882,7 +23882,7 @@
         <v>517</v>
       </c>
       <c r="C1805" t="n">
-        <v>0.06304</v>
+        <v>0.063045</v>
       </c>
     </row>
     <row r="1806">
@@ -23895,7 +23895,7 @@
         <v>518</v>
       </c>
       <c r="C1806" t="n">
-        <v>0.06368500000000001</v>
+        <v>0.063726</v>
       </c>
     </row>
     <row r="1807">
@@ -23908,7 +23908,7 @@
         <v>519</v>
       </c>
       <c r="C1807" t="n">
-        <v>0.06393</v>
+        <v>0.063929</v>
       </c>
     </row>
     <row r="1808">
@@ -23921,7 +23921,7 @@
         <v>520</v>
       </c>
       <c r="C1808" t="n">
-        <v>0.064134</v>
+        <v>0.064137</v>
       </c>
     </row>
     <row r="1809">
@@ -23934,7 +23934,7 @@
         <v>521</v>
       </c>
       <c r="C1809" t="n">
-        <v>0.064486</v>
+        <v>0.064496</v>
       </c>
     </row>
     <row r="1810">
@@ -23947,7 +23947,7 @@
         <v>522</v>
       </c>
       <c r="C1810" t="n">
-        <v>0.064822</v>
+        <v>0.06482599999999999</v>
       </c>
     </row>
     <row r="1811">
@@ -23960,7 +23960,7 @@
         <v>523</v>
       </c>
       <c r="C1811" t="n">
-        <v>0.06485200000000001</v>
+        <v>0.064871</v>
       </c>
     </row>
     <row r="1812">
@@ -23973,7 +23973,7 @@
         <v>524</v>
       </c>
       <c r="C1812" t="n">
-        <v>0.06507599999999999</v>
+        <v>0.065082</v>
       </c>
     </row>
     <row r="1813">
@@ -23986,7 +23986,7 @@
         <v>525</v>
       </c>
       <c r="C1813" t="n">
-        <v>0.065733</v>
+        <v>0.065752</v>
       </c>
     </row>
     <row r="1814">
@@ -23999,7 +23999,7 @@
         <v>526</v>
       </c>
       <c r="C1814" t="n">
-        <v>0.065818</v>
+        <v>0.065815</v>
       </c>
     </row>
     <row r="1815">
@@ -24012,7 +24012,7 @@
         <v>527</v>
       </c>
       <c r="C1815" t="n">
-        <v>0.06636599999999999</v>
+        <v>0.06636400000000001</v>
       </c>
     </row>
     <row r="1816">
@@ -24025,7 +24025,7 @@
         <v>528</v>
       </c>
       <c r="C1816" t="n">
-        <v>0.066425</v>
+        <v>0.066454</v>
       </c>
     </row>
     <row r="1817">
@@ -24038,7 +24038,7 @@
         <v>529</v>
       </c>
       <c r="C1817" t="n">
-        <v>0.066686</v>
+        <v>0.06668499999999999</v>
       </c>
     </row>
     <row r="1818">
@@ -24051,7 +24051,7 @@
         <v>530</v>
       </c>
       <c r="C1818" t="n">
-        <v>0.067593</v>
+        <v>0.06759</v>
       </c>
     </row>
     <row r="1819">
@@ -24064,7 +24064,7 @@
         <v>531</v>
       </c>
       <c r="C1819" t="n">
-        <v>0.067665</v>
+        <v>0.067664</v>
       </c>
     </row>
     <row r="1820">
@@ -24077,7 +24077,7 @@
         <v>532</v>
       </c>
       <c r="C1820" t="n">
-        <v>0.068166</v>
+        <v>0.068172</v>
       </c>
     </row>
     <row r="1821">
@@ -24090,7 +24090,7 @@
         <v>533</v>
       </c>
       <c r="C1821" t="n">
-        <v>0.068207</v>
+        <v>0.06821099999999999</v>
       </c>
     </row>
     <row r="1822">
@@ -24103,7 +24103,7 @@
         <v>534</v>
       </c>
       <c r="C1822" t="n">
-        <v>0.06917</v>
+        <v>0.069172</v>
       </c>
     </row>
     <row r="1823">
@@ -24116,7 +24116,7 @@
         <v>535</v>
       </c>
       <c r="C1823" t="n">
-        <v>0.06969400000000001</v>
+        <v>0.06972399999999999</v>
       </c>
     </row>
     <row r="1824">
@@ -24129,7 +24129,7 @@
         <v>536</v>
       </c>
       <c r="C1824" t="n">
-        <v>0.069911</v>
+        <v>0.06991600000000001</v>
       </c>
     </row>
     <row r="1825">
@@ -24142,7 +24142,7 @@
         <v>537</v>
       </c>
       <c r="C1825" t="n">
-        <v>0.070109</v>
+        <v>0.07012</v>
       </c>
     </row>
     <row r="1826">
@@ -24155,7 +24155,7 @@
         <v>538</v>
       </c>
       <c r="C1826" t="n">
-        <v>0.07037400000000001</v>
+        <v>0.070372</v>
       </c>
     </row>
     <row r="1827">
@@ -24168,7 +24168,7 @@
         <v>539</v>
       </c>
       <c r="C1827" t="n">
-        <v>0.070629</v>
+        <v>0.070631</v>
       </c>
     </row>
     <row r="1828">
@@ -24181,7 +24181,7 @@
         <v>540</v>
       </c>
       <c r="C1828" t="n">
-        <v>0.07071</v>
+        <v>0.07070799999999999</v>
       </c>
     </row>
     <row r="1829">
@@ -24194,7 +24194,7 @@
         <v>541</v>
       </c>
       <c r="C1829" t="n">
-        <v>0.071491</v>
+        <v>0.07149</v>
       </c>
     </row>
     <row r="1830">
@@ -24207,7 +24207,7 @@
         <v>542</v>
       </c>
       <c r="C1830" t="n">
-        <v>0.073446</v>
+        <v>0.073534</v>
       </c>
     </row>
     <row r="1831">
@@ -24220,7 +24220,7 @@
         <v>543</v>
       </c>
       <c r="C1831" t="n">
-        <v>0.073724</v>
+        <v>0.073727</v>
       </c>
     </row>
     <row r="1832">
@@ -24233,7 +24233,7 @@
         <v>544</v>
       </c>
       <c r="C1832" t="n">
-        <v>0.073853</v>
+        <v>0.073862</v>
       </c>
     </row>
     <row r="1833">
@@ -24246,7 +24246,7 @@
         <v>545</v>
       </c>
       <c r="C1833" t="n">
-        <v>0.074293</v>
+        <v>0.074298</v>
       </c>
     </row>
     <row r="1834">
@@ -24259,7 +24259,7 @@
         <v>546</v>
       </c>
       <c r="C1834" t="n">
-        <v>0.074628</v>
+        <v>0.074629</v>
       </c>
     </row>
     <row r="1835">
@@ -24272,7 +24272,7 @@
         <v>547</v>
       </c>
       <c r="C1835" t="n">
-        <v>0.07509299999999999</v>
+        <v>0.075097</v>
       </c>
     </row>
     <row r="1836">
@@ -24285,7 +24285,7 @@
         <v>548</v>
       </c>
       <c r="C1836" t="n">
-        <v>0.075629</v>
+        <v>0.075653</v>
       </c>
     </row>
     <row r="1837">
@@ -24298,7 +24298,7 @@
         <v>549</v>
       </c>
       <c r="C1837" t="n">
-        <v>0.076431</v>
+        <v>0.07649400000000001</v>
       </c>
     </row>
     <row r="1838">
@@ -24311,7 +24311,7 @@
         <v>550</v>
       </c>
       <c r="C1838" t="n">
-        <v>0.07668899999999999</v>
+        <v>0.076696</v>
       </c>
     </row>
     <row r="1839">
@@ -24324,7 +24324,7 @@
         <v>551</v>
       </c>
       <c r="C1839" t="n">
-        <v>0.07717599999999999</v>
+        <v>0.077209</v>
       </c>
     </row>
     <row r="1840">
@@ -24337,7 +24337,7 @@
         <v>552</v>
       </c>
       <c r="C1840" t="n">
-        <v>0.07803400000000001</v>
+        <v>0.078032</v>
       </c>
     </row>
     <row r="1841">
@@ -24350,7 +24350,7 @@
         <v>553</v>
       </c>
       <c r="C1841" t="n">
-        <v>0.078221</v>
+        <v>0.078223</v>
       </c>
     </row>
     <row r="1842">
@@ -24363,7 +24363,7 @@
         <v>554</v>
       </c>
       <c r="C1842" t="n">
-        <v>0.078498</v>
+        <v>0.078556</v>
       </c>
     </row>
     <row r="1843">
@@ -24376,7 +24376,7 @@
         <v>555</v>
       </c>
       <c r="C1843" t="n">
-        <v>0.078983</v>
+        <v>0.079153</v>
       </c>
     </row>
     <row r="1844">
@@ -24389,7 +24389,7 @@
         <v>556</v>
       </c>
       <c r="C1844" t="n">
-        <v>0.07928399999999999</v>
+        <v>0.079287</v>
       </c>
     </row>
     <row r="1845">
@@ -24415,7 +24415,7 @@
         <v>558</v>
       </c>
       <c r="C1846" t="n">
-        <v>0.08033999999999999</v>
+        <v>0.08033899999999999</v>
       </c>
     </row>
     <row r="1847">
@@ -24428,7 +24428,7 @@
         <v>559</v>
       </c>
       <c r="C1847" t="n">
-        <v>0.08098900000000001</v>
+        <v>0.080995</v>
       </c>
     </row>
     <row r="1848">
@@ -24441,7 +24441,7 @@
         <v>560</v>
       </c>
       <c r="C1848" t="n">
-        <v>0.082429</v>
+        <v>0.08243300000000001</v>
       </c>
     </row>
     <row r="1849">
@@ -24454,7 +24454,7 @@
         <v>561</v>
       </c>
       <c r="C1849" t="n">
-        <v>0.082733</v>
+        <v>0.08276600000000001</v>
       </c>
     </row>
     <row r="1850">
@@ -24480,7 +24480,7 @@
         <v>563</v>
       </c>
       <c r="C1851" t="n">
-        <v>0.08311499999999999</v>
+        <v>0.083119</v>
       </c>
     </row>
     <row r="1852">
@@ -24493,7 +24493,7 @@
         <v>564</v>
       </c>
       <c r="C1852" t="n">
-        <v>0.085747</v>
+        <v>0.085783</v>
       </c>
     </row>
     <row r="1853">
@@ -24506,7 +24506,7 @@
         <v>565</v>
       </c>
       <c r="C1853" t="n">
-        <v>0.08606900000000001</v>
+        <v>0.086067</v>
       </c>
     </row>
     <row r="1854">
@@ -24519,7 +24519,7 @@
         <v>566</v>
       </c>
       <c r="C1854" t="n">
-        <v>0.086697</v>
+        <v>0.086698</v>
       </c>
     </row>
     <row r="1855">
@@ -24532,7 +24532,7 @@
         <v>567</v>
       </c>
       <c r="C1855" t="n">
-        <v>0.08698599999999999</v>
+        <v>0.08701200000000001</v>
       </c>
     </row>
     <row r="1856">
@@ -24545,7 +24545,7 @@
         <v>568</v>
       </c>
       <c r="C1856" t="n">
-        <v>0.08717</v>
+        <v>0.08724999999999999</v>
       </c>
     </row>
     <row r="1857">
@@ -24558,7 +24558,7 @@
         <v>569</v>
       </c>
       <c r="C1857" t="n">
-        <v>0.08920500000000001</v>
+        <v>0.089201</v>
       </c>
     </row>
     <row r="1858">
@@ -24571,7 +24571,7 @@
         <v>570</v>
       </c>
       <c r="C1858" t="n">
-        <v>0.08980200000000001</v>
+        <v>0.08983099999999999</v>
       </c>
     </row>
     <row r="1859">
@@ -24584,7 +24584,7 @@
         <v>571</v>
       </c>
       <c r="C1859" t="n">
-        <v>0.09018900000000001</v>
+        <v>0.090277</v>
       </c>
     </row>
     <row r="1860">
@@ -24597,7 +24597,7 @@
         <v>572</v>
       </c>
       <c r="C1860" t="n">
-        <v>0.090239</v>
+        <v>0.090404</v>
       </c>
     </row>
     <row r="1861">
@@ -24610,7 +24610,7 @@
         <v>573</v>
       </c>
       <c r="C1861" t="n">
-        <v>0.090407</v>
+        <v>0.090446</v>
       </c>
     </row>
     <row r="1862">
@@ -24623,7 +24623,7 @@
         <v>574</v>
       </c>
       <c r="C1862" t="n">
-        <v>0.090862</v>
+        <v>0.090888</v>
       </c>
     </row>
     <row r="1863">
@@ -24636,7 +24636,7 @@
         <v>575</v>
       </c>
       <c r="C1863" t="n">
-        <v>0.091262</v>
+        <v>0.09125999999999999</v>
       </c>
     </row>
     <row r="1864">
@@ -24649,7 +24649,7 @@
         <v>576</v>
       </c>
       <c r="C1864" t="n">
-        <v>0.09253500000000001</v>
+        <v>0.092589</v>
       </c>
     </row>
     <row r="1865">
@@ -24662,7 +24662,7 @@
         <v>577</v>
       </c>
       <c r="C1865" t="n">
-        <v>0.093664</v>
+        <v>0.093678</v>
       </c>
     </row>
     <row r="1866">
@@ -24675,7 +24675,7 @@
         <v>578</v>
       </c>
       <c r="C1866" t="n">
-        <v>0.09377099999999999</v>
+        <v>0.09377000000000001</v>
       </c>
     </row>
     <row r="1867">
@@ -24688,7 +24688,7 @@
         <v>579</v>
       </c>
       <c r="C1867" t="n">
-        <v>0.09410200000000001</v>
+        <v>0.094108</v>
       </c>
     </row>
     <row r="1868">
@@ -24701,7 +24701,7 @@
         <v>580</v>
       </c>
       <c r="C1868" t="n">
-        <v>0.09433800000000001</v>
+        <v>0.094476</v>
       </c>
     </row>
     <row r="1869">
@@ -24714,7 +24714,7 @@
         <v>581</v>
       </c>
       <c r="C1869" t="n">
-        <v>0.094541</v>
+        <v>0.094538</v>
       </c>
     </row>
     <row r="1870">
@@ -24727,7 +24727,7 @@
         <v>582</v>
       </c>
       <c r="C1870" t="n">
-        <v>0.095595</v>
+        <v>0.095594</v>
       </c>
     </row>
     <row r="1871">
@@ -24740,7 +24740,7 @@
         <v>583</v>
       </c>
       <c r="C1871" t="n">
-        <v>0.096038</v>
+        <v>0.096052</v>
       </c>
     </row>
     <row r="1872">
@@ -24753,7 +24753,7 @@
         <v>584</v>
       </c>
       <c r="C1872" t="n">
-        <v>0.09757399999999999</v>
+        <v>0.097592</v>
       </c>
     </row>
     <row r="1873">
@@ -24766,7 +24766,7 @@
         <v>585</v>
       </c>
       <c r="C1873" t="n">
-        <v>0.10214</v>
+        <v>0.102142</v>
       </c>
     </row>
     <row r="1874">
@@ -24792,7 +24792,7 @@
         <v>587</v>
       </c>
       <c r="C1875" t="n">
-        <v>0.102719</v>
+        <v>0.10273</v>
       </c>
     </row>
     <row r="1876">
@@ -24805,7 +24805,7 @@
         <v>588</v>
       </c>
       <c r="C1876" t="n">
-        <v>0.102897</v>
+        <v>0.102918</v>
       </c>
     </row>
     <row r="1877">
@@ -24818,7 +24818,7 @@
         <v>589</v>
       </c>
       <c r="C1877" t="n">
-        <v>0.103164</v>
+        <v>0.103162</v>
       </c>
     </row>
     <row r="1878">
@@ -24831,7 +24831,7 @@
         <v>590</v>
       </c>
       <c r="C1878" t="n">
-        <v>0.103709</v>
+        <v>0.10377</v>
       </c>
     </row>
     <row r="1879">
@@ -24844,7 +24844,7 @@
         <v>591</v>
       </c>
       <c r="C1879" t="n">
-        <v>0.107053</v>
+        <v>0.107074</v>
       </c>
     </row>
     <row r="1880">
@@ -24857,7 +24857,7 @@
         <v>592</v>
       </c>
       <c r="C1880" t="n">
-        <v>0.108173</v>
+        <v>0.108169</v>
       </c>
     </row>
     <row r="1881">
@@ -24870,7 +24870,7 @@
         <v>593</v>
       </c>
       <c r="C1881" t="n">
-        <v>0.110156</v>
+        <v>0.110166</v>
       </c>
     </row>
     <row r="1882">
@@ -24883,7 +24883,7 @@
         <v>594</v>
       </c>
       <c r="C1882" t="n">
-        <v>0.111863</v>
+        <v>0.111864</v>
       </c>
     </row>
     <row r="1883">
@@ -24896,7 +24896,7 @@
         <v>595</v>
       </c>
       <c r="C1883" t="n">
-        <v>0.11265</v>
+        <v>0.112646</v>
       </c>
     </row>
     <row r="1884">
@@ -24909,7 +24909,7 @@
         <v>596</v>
       </c>
       <c r="C1884" t="n">
-        <v>0.114003</v>
+        <v>0.114019</v>
       </c>
     </row>
     <row r="1885">
@@ -24922,7 +24922,7 @@
         <v>597</v>
       </c>
       <c r="C1885" t="n">
-        <v>0.115314</v>
+        <v>0.115312</v>
       </c>
     </row>
     <row r="1886">
@@ -24935,7 +24935,7 @@
         <v>598</v>
       </c>
       <c r="C1886" t="n">
-        <v>0.116743</v>
+        <v>0.11687</v>
       </c>
     </row>
     <row r="1887">
@@ -24948,7 +24948,7 @@
         <v>599</v>
       </c>
       <c r="C1887" t="n">
-        <v>0.117165</v>
+        <v>0.117177</v>
       </c>
     </row>
     <row r="1888">
@@ -24961,7 +24961,7 @@
         <v>600</v>
       </c>
       <c r="C1888" t="n">
-        <v>0.117765</v>
+        <v>0.117763</v>
       </c>
     </row>
     <row r="1889">
@@ -24974,7 +24974,7 @@
         <v>601</v>
       </c>
       <c r="C1889" t="n">
-        <v>0.118048</v>
+        <v>0.118054</v>
       </c>
     </row>
     <row r="1890">
@@ -24987,7 +24987,7 @@
         <v>602</v>
       </c>
       <c r="C1890" t="n">
-        <v>0.122422</v>
+        <v>0.122421</v>
       </c>
     </row>
     <row r="1891">
@@ -25000,7 +25000,7 @@
         <v>603</v>
       </c>
       <c r="C1891" t="n">
-        <v>0.123089</v>
+        <v>0.1231</v>
       </c>
     </row>
     <row r="1892">
@@ -25013,7 +25013,7 @@
         <v>604</v>
       </c>
       <c r="C1892" t="n">
-        <v>0.124492</v>
+        <v>0.124497</v>
       </c>
     </row>
     <row r="1893">
@@ -25039,7 +25039,7 @@
         <v>606</v>
       </c>
       <c r="C1894" t="n">
-        <v>0.127625</v>
+        <v>0.127632</v>
       </c>
     </row>
     <row r="1895">
@@ -25065,7 +25065,7 @@
         <v>608</v>
       </c>
       <c r="C1896" t="n">
-        <v>0.128481</v>
+        <v>0.12854</v>
       </c>
     </row>
     <row r="1897">
@@ -25078,7 +25078,7 @@
         <v>609</v>
       </c>
       <c r="C1897" t="n">
-        <v>0.131531</v>
+        <v>0.131615</v>
       </c>
     </row>
     <row r="1898">
@@ -25091,7 +25091,7 @@
         <v>610</v>
       </c>
       <c r="C1898" t="n">
-        <v>0.132132</v>
+        <v>0.132137</v>
       </c>
     </row>
     <row r="1899">
@@ -25104,7 +25104,7 @@
         <v>611</v>
       </c>
       <c r="C1899" t="n">
-        <v>0.132976</v>
+        <v>0.132974</v>
       </c>
     </row>
     <row r="1900">
@@ -25117,7 +25117,7 @@
         <v>612</v>
       </c>
       <c r="C1900" t="n">
-        <v>0.13371</v>
+        <v>0.133718</v>
       </c>
     </row>
     <row r="1901">
@@ -25130,7 +25130,7 @@
         <v>613</v>
       </c>
       <c r="C1901" t="n">
-        <v>0.134695</v>
+        <v>0.134716</v>
       </c>
     </row>
     <row r="1902">
@@ -25143,7 +25143,7 @@
         <v>614</v>
       </c>
       <c r="C1902" t="n">
-        <v>0.136925</v>
+        <v>0.136996</v>
       </c>
     </row>
     <row r="1903">
@@ -25156,7 +25156,7 @@
         <v>615</v>
       </c>
       <c r="C1903" t="n">
-        <v>0.143493</v>
+        <v>0.143494</v>
       </c>
     </row>
     <row r="1904">
@@ -25169,7 +25169,7 @@
         <v>616</v>
       </c>
       <c r="C1904" t="n">
-        <v>0.145833</v>
+        <v>0.14583</v>
       </c>
     </row>
     <row r="1905">
@@ -25182,7 +25182,7 @@
         <v>617</v>
       </c>
       <c r="C1905" t="n">
-        <v>0.148933</v>
+        <v>0.148928</v>
       </c>
     </row>
     <row r="1906">
@@ -25195,7 +25195,7 @@
         <v>618</v>
       </c>
       <c r="C1906" t="n">
-        <v>0.150793</v>
+        <v>0.150796</v>
       </c>
     </row>
     <row r="1907">
@@ -25208,7 +25208,7 @@
         <v>619</v>
       </c>
       <c r="C1907" t="n">
-        <v>0.150933</v>
+        <v>0.150984</v>
       </c>
     </row>
     <row r="1908">
@@ -25221,7 +25221,7 @@
         <v>620</v>
       </c>
       <c r="C1908" t="n">
-        <v>0.160029</v>
+        <v>0.160045</v>
       </c>
     </row>
     <row r="1909">
@@ -25234,7 +25234,7 @@
         <v>621</v>
       </c>
       <c r="C1909" t="n">
-        <v>0.165352</v>
+        <v>0.165403</v>
       </c>
     </row>
     <row r="1910">
@@ -25247,7 +25247,7 @@
         <v>622</v>
       </c>
       <c r="C1910" t="n">
-        <v>0.1686</v>
+        <v>0.168595</v>
       </c>
     </row>
     <row r="1911">
@@ -25260,7 +25260,7 @@
         <v>623</v>
       </c>
       <c r="C1911" t="n">
-        <v>0.170453</v>
+        <v>0.170484</v>
       </c>
     </row>
     <row r="1912">
@@ -25273,7 +25273,7 @@
         <v>624</v>
       </c>
       <c r="C1912" t="n">
-        <v>0.171464</v>
+        <v>0.171494</v>
       </c>
     </row>
     <row r="1913">
@@ -25286,7 +25286,7 @@
         <v>625</v>
       </c>
       <c r="C1913" t="n">
-        <v>0.172026</v>
+        <v>0.172381</v>
       </c>
     </row>
     <row r="1914">
@@ -25299,7 +25299,7 @@
         <v>626</v>
       </c>
       <c r="C1914" t="n">
-        <v>0.175504</v>
+        <v>0.175498</v>
       </c>
     </row>
     <row r="1915">
@@ -25312,7 +25312,7 @@
         <v>627</v>
       </c>
       <c r="C1915" t="n">
-        <v>0.175767</v>
+        <v>0.175851</v>
       </c>
     </row>
     <row r="1916">
@@ -25325,7 +25325,7 @@
         <v>628</v>
       </c>
       <c r="C1916" t="n">
-        <v>0.176386</v>
+        <v>0.176382</v>
       </c>
     </row>
     <row r="1917">
@@ -25338,7 +25338,7 @@
         <v>629</v>
       </c>
       <c r="C1917" t="n">
-        <v>0.176937</v>
+        <v>0.177089</v>
       </c>
     </row>
     <row r="1918">
@@ -25351,7 +25351,7 @@
         <v>630</v>
       </c>
       <c r="C1918" t="n">
-        <v>0.185775</v>
+        <v>0.185779</v>
       </c>
     </row>
     <row r="1919">
@@ -25364,7 +25364,7 @@
         <v>631</v>
       </c>
       <c r="C1919" t="n">
-        <v>0.186611</v>
+        <v>0.186749</v>
       </c>
     </row>
     <row r="1920">
@@ -25377,7 +25377,7 @@
         <v>632</v>
       </c>
       <c r="C1920" t="n">
-        <v>0.194492</v>
+        <v>0.194497</v>
       </c>
     </row>
     <row r="1921">
@@ -25390,7 +25390,7 @@
         <v>633</v>
       </c>
       <c r="C1921" t="n">
-        <v>0.231341</v>
+        <v>0.231334</v>
       </c>
     </row>
     <row r="1922">
@@ -25403,7 +25403,7 @@
         <v>634</v>
       </c>
       <c r="C1922" t="n">
-        <v>0.231341</v>
+        <v>0.231476</v>
       </c>
     </row>
     <row r="1923">
@@ -25416,7 +25416,7 @@
         <v>635</v>
       </c>
       <c r="C1923" t="n">
-        <v>0.246691</v>
+        <v>0.246966</v>
       </c>
     </row>
     <row r="1924">
@@ -25429,7 +25429,7 @@
         <v>636</v>
       </c>
       <c r="C1924" t="n">
-        <v>0.249837</v>
+        <v>0.250119</v>
       </c>
     </row>
     <row r="1925">
@@ -25442,7 +25442,7 @@
         <v>637</v>
       </c>
       <c r="C1925" t="n">
-        <v>0.253327</v>
+        <v>0.25378</v>
       </c>
     </row>
     <row r="1926">
@@ -25455,7 +25455,7 @@
         <v>638</v>
       </c>
       <c r="C1926" t="n">
-        <v>0.258553</v>
+        <v>0.258667</v>
       </c>
     </row>
     <row r="1927">
@@ -25468,7 +25468,7 @@
         <v>639</v>
       </c>
       <c r="C1927" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
     </row>
     <row r="1928">
@@ -25481,7 +25481,7 @@
         <v>640</v>
       </c>
       <c r="C1928" t="n">
-        <v>0.326891</v>
+        <v>0.326962</v>
       </c>
     </row>
     <row r="1929">
@@ -25494,7 +25494,7 @@
         <v>641</v>
       </c>
       <c r="C1929" t="n">
-        <v>0.339365</v>
+        <v>0.33958</v>
       </c>
     </row>
     <row r="1930">
@@ -25507,7 +25507,7 @@
         <v>642</v>
       </c>
       <c r="C1930" t="n">
-        <v>0.474555</v>
+        <v>0.474746</v>
       </c>
     </row>
   </sheetData>
